--- a/bk-monatsreview/assets/Monatsreview Arbeitspapier.xlsx
+++ b/bk-monatsreview/assets/Monatsreview Arbeitspapier.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Übersicht" sheetId="1" r:id="R633a1af2e12e42cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prüfergebnisse" sheetId="2" r:id="Rebc1b19be1c6442f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Auszifferungsliste" sheetId="3" r:id="Rec33b62b47e14a27"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Umbuchungsvorschläge" sheetId="4" r:id="Ra65be2b50e7c447a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1590 Klärungsliste" sheetId="5" r:id="R14b042b14cb14111"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Geprüfte Bereiche" sheetId="6" r:id="R8e17ac20559e4c9e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Übersicht" sheetId="1" r:id="Re8b2f67010744a9c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prüfergebnisse" sheetId="2" r:id="Rd4ce9073141f4bc5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Auszifferungsliste" sheetId="3" r:id="R6fffa2ffb1784884"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Umbuchungsvorschläge" sheetId="4" r:id="Re6a4a2b7876a49b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Geprüfte Bereiche" sheetId="6" r:id="Rdd4e9b35c0f04143"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1590 Klärungsliste" sheetId="7" r:id="Rb3171a89337c436f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,12 +18,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="3">
+  <x:numFmts count="5">
     <x:numFmt numFmtId="200" formatCode="dd.mm.yyyy"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00 &quot;€&quot;"/>
     <x:numFmt numFmtId="202" formatCode="#,##0.00 [$€-407]"/>
+    <x:numFmt numFmtId="203" formatCode="#,##0.00 &quot;EUR&quot;"/>
+    <x:numFmt numFmtId="204" formatCode="0"/>
   </x:numFmts>
-  <x:fonts count="9">
+  <x:fonts count="10">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -74,8 +76,13 @@
       <x:color rgb="FF60497A"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF1F1F1F"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="30">
+  <x:fills count="34">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -222,8 +229,28 @@
         <x:fgColor rgb="FFE4DFEC"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="32">
+  <x:borders count="41">
     <x:border/>
     <x:border/>
     <x:border>
@@ -502,11 +529,101 @@
         <x:color rgb="FFD9D9D9"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFE7E6E6"/>
+      </x:right>
+      <x:bottom style="thin">
+        <x:color rgb="FFE7E6E6"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE7E6E6"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFE7E6E6"/>
+      </x:right>
+      <x:bottom style="thin">
+        <x:color rgb="FFE7E6E6"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE7E6E6"/>
+      </x:left>
+      <x:bottom style="thin">
+        <x:color rgb="FFE7E6E6"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFE7E6E6"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFE7E6E6"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFE7E6E6"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE7E6E6"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFE7E6E6"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFE7E6E6"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFE7E6E6"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE7E6E6"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFE7E6E6"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFE7E6E6"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFE7E6E6"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFE7E6E6"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE7E6E6"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFE7E6E6"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFE7E6E6"/>
+      </x:top>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE7E6E6"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFE7E6E6"/>
+      </x:top>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="146">
+  <x:cellXfs count="209">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -779,11 +896,168 @@
     <x:xf numFmtId="0" fontId="6" fillId="27" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="7" fillId="28" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="8" fillId="29" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="30" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="30" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="30" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="30" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="30" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="30" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="31" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="31" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="32" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="32" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="32" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="32" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="32" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="9" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="9" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="9" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="9" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="9" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="9" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="9" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="9" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="9" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="33" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="33" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="33" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="93">
+  <x:dxfs count="97">
     <x:dxf>
       <x:font>
         <x:b/>
@@ -1767,6 +2041,46 @@
         </x:patternFill>
       </x:fill>
     </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF9C0006"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFC7CE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF9C6500"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFEB9C"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF006100"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFC6EFCE"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FF5F497A"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFE4DFEC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
   </x:dxfs>
 </x:styleSheet>
 </file>
@@ -26664,6279 +26978,6 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="13" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="34" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="42" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="60" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="18" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="30" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="139" t="str">
-        <x:v>Ampel</x:v>
-      </x:c>
-      <x:c r="B1" s="139" t="str">
-        <x:v>Datum</x:v>
-      </x:c>
-      <x:c r="C1" s="139" t="str">
-        <x:v>Betrag</x:v>
-      </x:c>
-      <x:c r="D1" s="139" t="str">
-        <x:v>Alter in Monaten</x:v>
-      </x:c>
-      <x:c r="E1" s="139" t="str">
-        <x:v>Konto</x:v>
-      </x:c>
-      <x:c r="F1" s="139" t="str">
-        <x:v>Gegenkonto</x:v>
-      </x:c>
-      <x:c r="G1" s="139" t="str">
-        <x:v>Buchungstext</x:v>
-      </x:c>
-      <x:c r="H1" s="139" t="str">
-        <x:v>Beanstandung</x:v>
-      </x:c>
-      <x:c r="I1" s="139" t="str">
-        <x:v>Konkrete Mandantenfrage</x:v>
-      </x:c>
-      <x:c r="J1" s="139" t="str">
-        <x:v>Bearbeitungsstatus</x:v>
-      </x:c>
-      <x:c r="K1" s="139" t="str">
-        <x:v>Kommentar</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="82" t="str"/>
-      <x:c r="B2" s="84" t="str"/>
-      <x:c r="C2" s="96" t="str"/>
-      <x:c r="D2" s="82" t="str"/>
-      <x:c r="E2" s="82" t="str"/>
-      <x:c r="F2" s="82" t="str"/>
-      <x:c r="G2" s="82" t="str"/>
-      <x:c r="H2" s="82" t="str"/>
-      <x:c r="I2" s="82" t="str"/>
-      <x:c r="J2" s="82" t="str"/>
-      <x:c r="K2" s="141" t="str"/>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="82" t="str"/>
-      <x:c r="B3" s="84" t="str"/>
-      <x:c r="C3" s="96" t="str"/>
-      <x:c r="D3" s="82" t="str"/>
-      <x:c r="E3" s="82" t="str"/>
-      <x:c r="F3" s="82" t="str"/>
-      <x:c r="G3" s="82" t="str"/>
-      <x:c r="H3" s="82" t="str"/>
-      <x:c r="I3" s="82" t="str"/>
-      <x:c r="J3" s="82" t="str"/>
-      <x:c r="K3" s="141" t="str"/>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="82" t="str"/>
-      <x:c r="B4" s="84" t="str"/>
-      <x:c r="C4" s="96" t="str"/>
-      <x:c r="D4" s="82" t="str"/>
-      <x:c r="E4" s="82" t="str"/>
-      <x:c r="F4" s="82" t="str"/>
-      <x:c r="G4" s="82" t="str"/>
-      <x:c r="H4" s="82" t="str"/>
-      <x:c r="I4" s="82" t="str"/>
-      <x:c r="J4" s="82" t="str"/>
-      <x:c r="K4" s="141" t="str"/>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="82" t="str"/>
-      <x:c r="B5" s="84" t="str"/>
-      <x:c r="C5" s="96" t="str"/>
-      <x:c r="D5" s="82" t="str"/>
-      <x:c r="E5" s="82" t="str"/>
-      <x:c r="F5" s="82" t="str"/>
-      <x:c r="G5" s="82" t="str"/>
-      <x:c r="H5" s="82" t="str"/>
-      <x:c r="I5" s="82" t="str"/>
-      <x:c r="J5" s="82" t="str"/>
-      <x:c r="K5" s="141" t="str"/>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="82" t="str"/>
-      <x:c r="B6" s="84" t="str"/>
-      <x:c r="C6" s="96" t="str"/>
-      <x:c r="D6" s="82" t="str"/>
-      <x:c r="E6" s="82" t="str"/>
-      <x:c r="F6" s="82" t="str"/>
-      <x:c r="G6" s="82" t="str"/>
-      <x:c r="H6" s="82" t="str"/>
-      <x:c r="I6" s="82" t="str"/>
-      <x:c r="J6" s="82" t="str"/>
-      <x:c r="K6" s="141" t="str"/>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="82" t="str"/>
-      <x:c r="B7" s="84" t="str"/>
-      <x:c r="C7" s="96" t="str"/>
-      <x:c r="D7" s="82" t="str"/>
-      <x:c r="E7" s="82" t="str"/>
-      <x:c r="F7" s="82" t="str"/>
-      <x:c r="G7" s="82" t="str"/>
-      <x:c r="H7" s="82" t="str"/>
-      <x:c r="I7" s="82" t="str"/>
-      <x:c r="J7" s="82" t="str"/>
-      <x:c r="K7" s="141" t="str"/>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="82" t="str"/>
-      <x:c r="B8" s="84" t="str"/>
-      <x:c r="C8" s="96" t="str"/>
-      <x:c r="D8" s="82" t="str"/>
-      <x:c r="E8" s="82" t="str"/>
-      <x:c r="F8" s="82" t="str"/>
-      <x:c r="G8" s="82" t="str"/>
-      <x:c r="H8" s="82" t="str"/>
-      <x:c r="I8" s="82" t="str"/>
-      <x:c r="J8" s="82" t="str"/>
-      <x:c r="K8" s="141" t="str"/>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="82" t="str"/>
-      <x:c r="B9" s="84" t="str"/>
-      <x:c r="C9" s="96" t="str"/>
-      <x:c r="D9" s="82" t="str"/>
-      <x:c r="E9" s="82" t="str"/>
-      <x:c r="F9" s="82" t="str"/>
-      <x:c r="G9" s="82" t="str"/>
-      <x:c r="H9" s="82" t="str"/>
-      <x:c r="I9" s="82" t="str"/>
-      <x:c r="J9" s="82" t="str"/>
-      <x:c r="K9" s="141" t="str"/>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="82" t="str"/>
-      <x:c r="B10" s="84" t="str"/>
-      <x:c r="C10" s="96" t="str"/>
-      <x:c r="D10" s="82" t="str"/>
-      <x:c r="E10" s="82" t="str"/>
-      <x:c r="F10" s="82" t="str"/>
-      <x:c r="G10" s="82" t="str"/>
-      <x:c r="H10" s="82" t="str"/>
-      <x:c r="I10" s="82" t="str"/>
-      <x:c r="J10" s="82" t="str"/>
-      <x:c r="K10" s="141" t="str"/>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="82" t="str"/>
-      <x:c r="B11" s="84" t="str"/>
-      <x:c r="C11" s="96" t="str"/>
-      <x:c r="D11" s="82" t="str"/>
-      <x:c r="E11" s="82" t="str"/>
-      <x:c r="F11" s="82" t="str"/>
-      <x:c r="G11" s="82" t="str"/>
-      <x:c r="H11" s="82" t="str"/>
-      <x:c r="I11" s="82" t="str"/>
-      <x:c r="J11" s="82" t="str"/>
-      <x:c r="K11" s="141" t="str"/>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="82" t="str"/>
-      <x:c r="B12" s="84" t="str"/>
-      <x:c r="C12" s="96" t="str"/>
-      <x:c r="D12" s="82" t="str"/>
-      <x:c r="E12" s="82" t="str"/>
-      <x:c r="F12" s="82" t="str"/>
-      <x:c r="G12" s="82" t="str"/>
-      <x:c r="H12" s="82" t="str"/>
-      <x:c r="I12" s="82" t="str"/>
-      <x:c r="J12" s="82" t="str"/>
-      <x:c r="K12" s="141" t="str"/>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="82" t="str"/>
-      <x:c r="B13" s="84" t="str"/>
-      <x:c r="C13" s="96" t="str"/>
-      <x:c r="D13" s="82" t="str"/>
-      <x:c r="E13" s="82" t="str"/>
-      <x:c r="F13" s="82" t="str"/>
-      <x:c r="G13" s="82" t="str"/>
-      <x:c r="H13" s="82" t="str"/>
-      <x:c r="I13" s="82" t="str"/>
-      <x:c r="J13" s="82" t="str"/>
-      <x:c r="K13" s="141" t="str"/>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="82" t="str"/>
-      <x:c r="B14" s="84" t="str"/>
-      <x:c r="C14" s="96" t="str"/>
-      <x:c r="D14" s="82" t="str"/>
-      <x:c r="E14" s="82" t="str"/>
-      <x:c r="F14" s="82" t="str"/>
-      <x:c r="G14" s="82" t="str"/>
-      <x:c r="H14" s="82" t="str"/>
-      <x:c r="I14" s="82" t="str"/>
-      <x:c r="J14" s="82" t="str"/>
-      <x:c r="K14" s="141" t="str"/>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="82" t="str"/>
-      <x:c r="B15" s="84" t="str"/>
-      <x:c r="C15" s="96" t="str"/>
-      <x:c r="D15" s="82" t="str"/>
-      <x:c r="E15" s="82" t="str"/>
-      <x:c r="F15" s="82" t="str"/>
-      <x:c r="G15" s="82" t="str"/>
-      <x:c r="H15" s="82" t="str"/>
-      <x:c r="I15" s="82" t="str"/>
-      <x:c r="J15" s="82" t="str"/>
-      <x:c r="K15" s="141" t="str"/>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="82" t="str"/>
-      <x:c r="B16" s="84" t="str"/>
-      <x:c r="C16" s="96" t="str"/>
-      <x:c r="D16" s="82" t="str"/>
-      <x:c r="E16" s="82" t="str"/>
-      <x:c r="F16" s="82" t="str"/>
-      <x:c r="G16" s="82" t="str"/>
-      <x:c r="H16" s="82" t="str"/>
-      <x:c r="I16" s="82" t="str"/>
-      <x:c r="J16" s="82" t="str"/>
-      <x:c r="K16" s="141" t="str"/>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="82" t="str"/>
-      <x:c r="B17" s="84" t="str"/>
-      <x:c r="C17" s="96" t="str"/>
-      <x:c r="D17" s="82" t="str"/>
-      <x:c r="E17" s="82" t="str"/>
-      <x:c r="F17" s="82" t="str"/>
-      <x:c r="G17" s="82" t="str"/>
-      <x:c r="H17" s="82" t="str"/>
-      <x:c r="I17" s="82" t="str"/>
-      <x:c r="J17" s="82" t="str"/>
-      <x:c r="K17" s="141" t="str"/>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="82" t="str"/>
-      <x:c r="B18" s="84" t="str"/>
-      <x:c r="C18" s="96" t="str"/>
-      <x:c r="D18" s="82" t="str"/>
-      <x:c r="E18" s="82" t="str"/>
-      <x:c r="F18" s="82" t="str"/>
-      <x:c r="G18" s="82" t="str"/>
-      <x:c r="H18" s="82" t="str"/>
-      <x:c r="I18" s="82" t="str"/>
-      <x:c r="J18" s="82" t="str"/>
-      <x:c r="K18" s="141" t="str"/>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="82" t="str"/>
-      <x:c r="B19" s="84" t="str"/>
-      <x:c r="C19" s="96" t="str"/>
-      <x:c r="D19" s="82" t="str"/>
-      <x:c r="E19" s="82" t="str"/>
-      <x:c r="F19" s="82" t="str"/>
-      <x:c r="G19" s="82" t="str"/>
-      <x:c r="H19" s="82" t="str"/>
-      <x:c r="I19" s="82" t="str"/>
-      <x:c r="J19" s="82" t="str"/>
-      <x:c r="K19" s="141" t="str"/>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="82" t="str"/>
-      <x:c r="B20" s="84" t="str"/>
-      <x:c r="C20" s="96" t="str"/>
-      <x:c r="D20" s="82" t="str"/>
-      <x:c r="E20" s="82" t="str"/>
-      <x:c r="F20" s="82" t="str"/>
-      <x:c r="G20" s="82" t="str"/>
-      <x:c r="H20" s="82" t="str"/>
-      <x:c r="I20" s="82" t="str"/>
-      <x:c r="J20" s="82" t="str"/>
-      <x:c r="K20" s="141" t="str"/>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" s="82" t="str"/>
-      <x:c r="B21" s="84" t="str"/>
-      <x:c r="C21" s="96" t="str"/>
-      <x:c r="D21" s="82" t="str"/>
-      <x:c r="E21" s="82" t="str"/>
-      <x:c r="F21" s="82" t="str"/>
-      <x:c r="G21" s="82" t="str"/>
-      <x:c r="H21" s="82" t="str"/>
-      <x:c r="I21" s="82" t="str"/>
-      <x:c r="J21" s="82" t="str"/>
-      <x:c r="K21" s="141" t="str"/>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" s="82" t="str"/>
-      <x:c r="B22" s="84" t="str"/>
-      <x:c r="C22" s="96" t="str"/>
-      <x:c r="D22" s="82" t="str"/>
-      <x:c r="E22" s="82" t="str"/>
-      <x:c r="F22" s="82" t="str"/>
-      <x:c r="G22" s="82" t="str"/>
-      <x:c r="H22" s="82" t="str"/>
-      <x:c r="I22" s="82" t="str"/>
-      <x:c r="J22" s="82" t="str"/>
-      <x:c r="K22" s="141" t="str"/>
-    </x:row>
-    <x:row r="23">
-      <x:c r="A23" s="82" t="str"/>
-      <x:c r="B23" s="84" t="str"/>
-      <x:c r="C23" s="96" t="str"/>
-      <x:c r="D23" s="82" t="str"/>
-      <x:c r="E23" s="82" t="str"/>
-      <x:c r="F23" s="82" t="str"/>
-      <x:c r="G23" s="82" t="str"/>
-      <x:c r="H23" s="82" t="str"/>
-      <x:c r="I23" s="82" t="str"/>
-      <x:c r="J23" s="82" t="str"/>
-      <x:c r="K23" s="141" t="str"/>
-    </x:row>
-    <x:row r="24">
-      <x:c r="A24" s="82" t="str"/>
-      <x:c r="B24" s="84" t="str"/>
-      <x:c r="C24" s="96" t="str"/>
-      <x:c r="D24" s="82" t="str"/>
-      <x:c r="E24" s="82" t="str"/>
-      <x:c r="F24" s="82" t="str"/>
-      <x:c r="G24" s="82" t="str"/>
-      <x:c r="H24" s="82" t="str"/>
-      <x:c r="I24" s="82" t="str"/>
-      <x:c r="J24" s="82" t="str"/>
-      <x:c r="K24" s="141" t="str"/>
-    </x:row>
-    <x:row r="25">
-      <x:c r="A25" s="82" t="str"/>
-      <x:c r="B25" s="84" t="str"/>
-      <x:c r="C25" s="96" t="str"/>
-      <x:c r="D25" s="82" t="str"/>
-      <x:c r="E25" s="82" t="str"/>
-      <x:c r="F25" s="82" t="str"/>
-      <x:c r="G25" s="82" t="str"/>
-      <x:c r="H25" s="82" t="str"/>
-      <x:c r="I25" s="82" t="str"/>
-      <x:c r="J25" s="82" t="str"/>
-      <x:c r="K25" s="141" t="str"/>
-    </x:row>
-    <x:row r="26">
-      <x:c r="A26" s="82" t="str"/>
-      <x:c r="B26" s="84" t="str"/>
-      <x:c r="C26" s="96" t="str"/>
-      <x:c r="D26" s="82" t="str"/>
-      <x:c r="E26" s="82" t="str"/>
-      <x:c r="F26" s="82" t="str"/>
-      <x:c r="G26" s="82" t="str"/>
-      <x:c r="H26" s="82" t="str"/>
-      <x:c r="I26" s="82" t="str"/>
-      <x:c r="J26" s="82" t="str"/>
-      <x:c r="K26" s="141" t="str"/>
-    </x:row>
-    <x:row r="27">
-      <x:c r="A27" s="82" t="str"/>
-      <x:c r="B27" s="84" t="str"/>
-      <x:c r="C27" s="96" t="str"/>
-      <x:c r="D27" s="82" t="str"/>
-      <x:c r="E27" s="82" t="str"/>
-      <x:c r="F27" s="82" t="str"/>
-      <x:c r="G27" s="82" t="str"/>
-      <x:c r="H27" s="82" t="str"/>
-      <x:c r="I27" s="82" t="str"/>
-      <x:c r="J27" s="82" t="str"/>
-      <x:c r="K27" s="141" t="str"/>
-    </x:row>
-    <x:row r="28">
-      <x:c r="A28" s="82" t="str"/>
-      <x:c r="B28" s="84" t="str"/>
-      <x:c r="C28" s="96" t="str"/>
-      <x:c r="D28" s="82" t="str"/>
-      <x:c r="E28" s="82" t="str"/>
-      <x:c r="F28" s="82" t="str"/>
-      <x:c r="G28" s="82" t="str"/>
-      <x:c r="H28" s="82" t="str"/>
-      <x:c r="I28" s="82" t="str"/>
-      <x:c r="J28" s="82" t="str"/>
-      <x:c r="K28" s="141" t="str"/>
-    </x:row>
-    <x:row r="29">
-      <x:c r="A29" s="82" t="str"/>
-      <x:c r="B29" s="84" t="str"/>
-      <x:c r="C29" s="96" t="str"/>
-      <x:c r="D29" s="82" t="str"/>
-      <x:c r="E29" s="82" t="str"/>
-      <x:c r="F29" s="82" t="str"/>
-      <x:c r="G29" s="82" t="str"/>
-      <x:c r="H29" s="82" t="str"/>
-      <x:c r="I29" s="82" t="str"/>
-      <x:c r="J29" s="82" t="str"/>
-      <x:c r="K29" s="141" t="str"/>
-    </x:row>
-    <x:row r="30">
-      <x:c r="A30" s="82" t="str"/>
-      <x:c r="B30" s="84" t="str"/>
-      <x:c r="C30" s="96" t="str"/>
-      <x:c r="D30" s="82" t="str"/>
-      <x:c r="E30" s="82" t="str"/>
-      <x:c r="F30" s="82" t="str"/>
-      <x:c r="G30" s="82" t="str"/>
-      <x:c r="H30" s="82" t="str"/>
-      <x:c r="I30" s="82" t="str"/>
-      <x:c r="J30" s="82" t="str"/>
-      <x:c r="K30" s="141" t="str"/>
-    </x:row>
-    <x:row r="31">
-      <x:c r="A31" s="82" t="str"/>
-      <x:c r="B31" s="84" t="str"/>
-      <x:c r="C31" s="96" t="str"/>
-      <x:c r="D31" s="82" t="str"/>
-      <x:c r="E31" s="82" t="str"/>
-      <x:c r="F31" s="82" t="str"/>
-      <x:c r="G31" s="82" t="str"/>
-      <x:c r="H31" s="82" t="str"/>
-      <x:c r="I31" s="82" t="str"/>
-      <x:c r="J31" s="82" t="str"/>
-      <x:c r="K31" s="141" t="str"/>
-    </x:row>
-    <x:row r="32">
-      <x:c r="A32" s="82" t="str"/>
-      <x:c r="B32" s="84" t="str"/>
-      <x:c r="C32" s="96" t="str"/>
-      <x:c r="D32" s="82" t="str"/>
-      <x:c r="E32" s="82" t="str"/>
-      <x:c r="F32" s="82" t="str"/>
-      <x:c r="G32" s="82" t="str"/>
-      <x:c r="H32" s="82" t="str"/>
-      <x:c r="I32" s="82" t="str"/>
-      <x:c r="J32" s="82" t="str"/>
-      <x:c r="K32" s="141" t="str"/>
-    </x:row>
-    <x:row r="33">
-      <x:c r="A33" s="82" t="str"/>
-      <x:c r="B33" s="84" t="str"/>
-      <x:c r="C33" s="96" t="str"/>
-      <x:c r="D33" s="82" t="str"/>
-      <x:c r="E33" s="82" t="str"/>
-      <x:c r="F33" s="82" t="str"/>
-      <x:c r="G33" s="82" t="str"/>
-      <x:c r="H33" s="82" t="str"/>
-      <x:c r="I33" s="82" t="str"/>
-      <x:c r="J33" s="82" t="str"/>
-      <x:c r="K33" s="141" t="str"/>
-    </x:row>
-    <x:row r="34">
-      <x:c r="A34" s="82" t="str"/>
-      <x:c r="B34" s="84" t="str"/>
-      <x:c r="C34" s="96" t="str"/>
-      <x:c r="D34" s="82" t="str"/>
-      <x:c r="E34" s="82" t="str"/>
-      <x:c r="F34" s="82" t="str"/>
-      <x:c r="G34" s="82" t="str"/>
-      <x:c r="H34" s="82" t="str"/>
-      <x:c r="I34" s="82" t="str"/>
-      <x:c r="J34" s="82" t="str"/>
-      <x:c r="K34" s="141" t="str"/>
-    </x:row>
-    <x:row r="35">
-      <x:c r="A35" s="82" t="str"/>
-      <x:c r="B35" s="84" t="str"/>
-      <x:c r="C35" s="96" t="str"/>
-      <x:c r="D35" s="82" t="str"/>
-      <x:c r="E35" s="82" t="str"/>
-      <x:c r="F35" s="82" t="str"/>
-      <x:c r="G35" s="82" t="str"/>
-      <x:c r="H35" s="82" t="str"/>
-      <x:c r="I35" s="82" t="str"/>
-      <x:c r="J35" s="82" t="str"/>
-      <x:c r="K35" s="141" t="str"/>
-    </x:row>
-    <x:row r="36">
-      <x:c r="A36" s="82" t="str"/>
-      <x:c r="B36" s="84" t="str"/>
-      <x:c r="C36" s="96" t="str"/>
-      <x:c r="D36" s="82" t="str"/>
-      <x:c r="E36" s="82" t="str"/>
-      <x:c r="F36" s="82" t="str"/>
-      <x:c r="G36" s="82" t="str"/>
-      <x:c r="H36" s="82" t="str"/>
-      <x:c r="I36" s="82" t="str"/>
-      <x:c r="J36" s="82" t="str"/>
-      <x:c r="K36" s="141" t="str"/>
-    </x:row>
-    <x:row r="37">
-      <x:c r="A37" s="82" t="str"/>
-      <x:c r="B37" s="84" t="str"/>
-      <x:c r="C37" s="96" t="str"/>
-      <x:c r="D37" s="82" t="str"/>
-      <x:c r="E37" s="82" t="str"/>
-      <x:c r="F37" s="82" t="str"/>
-      <x:c r="G37" s="82" t="str"/>
-      <x:c r="H37" s="82" t="str"/>
-      <x:c r="I37" s="82" t="str"/>
-      <x:c r="J37" s="82" t="str"/>
-      <x:c r="K37" s="141" t="str"/>
-    </x:row>
-    <x:row r="38">
-      <x:c r="A38" s="82" t="str"/>
-      <x:c r="B38" s="84" t="str"/>
-      <x:c r="C38" s="96" t="str"/>
-      <x:c r="D38" s="82" t="str"/>
-      <x:c r="E38" s="82" t="str"/>
-      <x:c r="F38" s="82" t="str"/>
-      <x:c r="G38" s="82" t="str"/>
-      <x:c r="H38" s="82" t="str"/>
-      <x:c r="I38" s="82" t="str"/>
-      <x:c r="J38" s="82" t="str"/>
-      <x:c r="K38" s="141" t="str"/>
-    </x:row>
-    <x:row r="39">
-      <x:c r="A39" s="82" t="str"/>
-      <x:c r="B39" s="84" t="str"/>
-      <x:c r="C39" s="96" t="str"/>
-      <x:c r="D39" s="82" t="str"/>
-      <x:c r="E39" s="82" t="str"/>
-      <x:c r="F39" s="82" t="str"/>
-      <x:c r="G39" s="82" t="str"/>
-      <x:c r="H39" s="82" t="str"/>
-      <x:c r="I39" s="82" t="str"/>
-      <x:c r="J39" s="82" t="str"/>
-      <x:c r="K39" s="141" t="str"/>
-    </x:row>
-    <x:row r="40">
-      <x:c r="A40" s="82" t="str"/>
-      <x:c r="B40" s="84" t="str"/>
-      <x:c r="C40" s="96" t="str"/>
-      <x:c r="D40" s="82" t="str"/>
-      <x:c r="E40" s="82" t="str"/>
-      <x:c r="F40" s="82" t="str"/>
-      <x:c r="G40" s="82" t="str"/>
-      <x:c r="H40" s="82" t="str"/>
-      <x:c r="I40" s="82" t="str"/>
-      <x:c r="J40" s="82" t="str"/>
-      <x:c r="K40" s="141" t="str"/>
-    </x:row>
-    <x:row r="41">
-      <x:c r="A41" s="82" t="str"/>
-      <x:c r="B41" s="84" t="str"/>
-      <x:c r="C41" s="96" t="str"/>
-      <x:c r="D41" s="82" t="str"/>
-      <x:c r="E41" s="82" t="str"/>
-      <x:c r="F41" s="82" t="str"/>
-      <x:c r="G41" s="82" t="str"/>
-      <x:c r="H41" s="82" t="str"/>
-      <x:c r="I41" s="82" t="str"/>
-      <x:c r="J41" s="82" t="str"/>
-      <x:c r="K41" s="141" t="str"/>
-    </x:row>
-    <x:row r="42">
-      <x:c r="A42" s="82" t="str"/>
-      <x:c r="B42" s="84" t="str"/>
-      <x:c r="C42" s="96" t="str"/>
-      <x:c r="D42" s="82" t="str"/>
-      <x:c r="E42" s="82" t="str"/>
-      <x:c r="F42" s="82" t="str"/>
-      <x:c r="G42" s="82" t="str"/>
-      <x:c r="H42" s="82" t="str"/>
-      <x:c r="I42" s="82" t="str"/>
-      <x:c r="J42" s="82" t="str"/>
-      <x:c r="K42" s="141" t="str"/>
-    </x:row>
-    <x:row r="43">
-      <x:c r="A43" s="82" t="str"/>
-      <x:c r="B43" s="84" t="str"/>
-      <x:c r="C43" s="96" t="str"/>
-      <x:c r="D43" s="82" t="str"/>
-      <x:c r="E43" s="82" t="str"/>
-      <x:c r="F43" s="82" t="str"/>
-      <x:c r="G43" s="82" t="str"/>
-      <x:c r="H43" s="82" t="str"/>
-      <x:c r="I43" s="82" t="str"/>
-      <x:c r="J43" s="82" t="str"/>
-      <x:c r="K43" s="141" t="str"/>
-    </x:row>
-    <x:row r="44">
-      <x:c r="A44" s="82" t="str"/>
-      <x:c r="B44" s="84" t="str"/>
-      <x:c r="C44" s="96" t="str"/>
-      <x:c r="D44" s="82" t="str"/>
-      <x:c r="E44" s="82" t="str"/>
-      <x:c r="F44" s="82" t="str"/>
-      <x:c r="G44" s="82" t="str"/>
-      <x:c r="H44" s="82" t="str"/>
-      <x:c r="I44" s="82" t="str"/>
-      <x:c r="J44" s="82" t="str"/>
-      <x:c r="K44" s="141" t="str"/>
-    </x:row>
-    <x:row r="45">
-      <x:c r="A45" s="82" t="str"/>
-      <x:c r="B45" s="84" t="str"/>
-      <x:c r="C45" s="96" t="str"/>
-      <x:c r="D45" s="82" t="str"/>
-      <x:c r="E45" s="82" t="str"/>
-      <x:c r="F45" s="82" t="str"/>
-      <x:c r="G45" s="82" t="str"/>
-      <x:c r="H45" s="82" t="str"/>
-      <x:c r="I45" s="82" t="str"/>
-      <x:c r="J45" s="82" t="str"/>
-      <x:c r="K45" s="141" t="str"/>
-    </x:row>
-    <x:row r="46">
-      <x:c r="A46" s="82" t="str"/>
-      <x:c r="B46" s="84" t="str"/>
-      <x:c r="C46" s="96" t="str"/>
-      <x:c r="D46" s="82" t="str"/>
-      <x:c r="E46" s="82" t="str"/>
-      <x:c r="F46" s="82" t="str"/>
-      <x:c r="G46" s="82" t="str"/>
-      <x:c r="H46" s="82" t="str"/>
-      <x:c r="I46" s="82" t="str"/>
-      <x:c r="J46" s="82" t="str"/>
-      <x:c r="K46" s="141" t="str"/>
-    </x:row>
-    <x:row r="47">
-      <x:c r="A47" s="82" t="str"/>
-      <x:c r="B47" s="84" t="str"/>
-      <x:c r="C47" s="96" t="str"/>
-      <x:c r="D47" s="82" t="str"/>
-      <x:c r="E47" s="82" t="str"/>
-      <x:c r="F47" s="82" t="str"/>
-      <x:c r="G47" s="82" t="str"/>
-      <x:c r="H47" s="82" t="str"/>
-      <x:c r="I47" s="82" t="str"/>
-      <x:c r="J47" s="82" t="str"/>
-      <x:c r="K47" s="141" t="str"/>
-    </x:row>
-    <x:row r="48">
-      <x:c r="A48" s="82" t="str"/>
-      <x:c r="B48" s="84" t="str"/>
-      <x:c r="C48" s="96" t="str"/>
-      <x:c r="D48" s="82" t="str"/>
-      <x:c r="E48" s="82" t="str"/>
-      <x:c r="F48" s="82" t="str"/>
-      <x:c r="G48" s="82" t="str"/>
-      <x:c r="H48" s="82" t="str"/>
-      <x:c r="I48" s="82" t="str"/>
-      <x:c r="J48" s="82" t="str"/>
-      <x:c r="K48" s="141" t="str"/>
-    </x:row>
-    <x:row r="49">
-      <x:c r="A49" s="82" t="str"/>
-      <x:c r="B49" s="84" t="str"/>
-      <x:c r="C49" s="96" t="str"/>
-      <x:c r="D49" s="82" t="str"/>
-      <x:c r="E49" s="82" t="str"/>
-      <x:c r="F49" s="82" t="str"/>
-      <x:c r="G49" s="82" t="str"/>
-      <x:c r="H49" s="82" t="str"/>
-      <x:c r="I49" s="82" t="str"/>
-      <x:c r="J49" s="82" t="str"/>
-      <x:c r="K49" s="141" t="str"/>
-    </x:row>
-    <x:row r="50">
-      <x:c r="A50" s="82" t="str"/>
-      <x:c r="B50" s="84" t="str"/>
-      <x:c r="C50" s="96" t="str"/>
-      <x:c r="D50" s="82" t="str"/>
-      <x:c r="E50" s="82" t="str"/>
-      <x:c r="F50" s="82" t="str"/>
-      <x:c r="G50" s="82" t="str"/>
-      <x:c r="H50" s="82" t="str"/>
-      <x:c r="I50" s="82" t="str"/>
-      <x:c r="J50" s="82" t="str"/>
-      <x:c r="K50" s="141" t="str"/>
-    </x:row>
-    <x:row r="51">
-      <x:c r="A51" s="82" t="str"/>
-      <x:c r="B51" s="84" t="str"/>
-      <x:c r="C51" s="96" t="str"/>
-      <x:c r="D51" s="82" t="str"/>
-      <x:c r="E51" s="82" t="str"/>
-      <x:c r="F51" s="82" t="str"/>
-      <x:c r="G51" s="82" t="str"/>
-      <x:c r="H51" s="82" t="str"/>
-      <x:c r="I51" s="82" t="str"/>
-      <x:c r="J51" s="82" t="str"/>
-      <x:c r="K51" s="141" t="str"/>
-    </x:row>
-    <x:row r="52">
-      <x:c r="A52" s="82" t="str"/>
-      <x:c r="B52" s="84" t="str"/>
-      <x:c r="C52" s="96" t="str"/>
-      <x:c r="D52" s="82" t="str"/>
-      <x:c r="E52" s="82" t="str"/>
-      <x:c r="F52" s="82" t="str"/>
-      <x:c r="G52" s="82" t="str"/>
-      <x:c r="H52" s="82" t="str"/>
-      <x:c r="I52" s="82" t="str"/>
-      <x:c r="J52" s="82" t="str"/>
-      <x:c r="K52" s="141" t="str"/>
-    </x:row>
-    <x:row r="53">
-      <x:c r="A53" s="82" t="str"/>
-      <x:c r="B53" s="84" t="str"/>
-      <x:c r="C53" s="96" t="str"/>
-      <x:c r="D53" s="82" t="str"/>
-      <x:c r="E53" s="82" t="str"/>
-      <x:c r="F53" s="82" t="str"/>
-      <x:c r="G53" s="82" t="str"/>
-      <x:c r="H53" s="82" t="str"/>
-      <x:c r="I53" s="82" t="str"/>
-      <x:c r="J53" s="82" t="str"/>
-      <x:c r="K53" s="141" t="str"/>
-    </x:row>
-    <x:row r="54">
-      <x:c r="A54" s="82" t="str"/>
-      <x:c r="B54" s="84" t="str"/>
-      <x:c r="C54" s="96" t="str"/>
-      <x:c r="D54" s="82" t="str"/>
-      <x:c r="E54" s="82" t="str"/>
-      <x:c r="F54" s="82" t="str"/>
-      <x:c r="G54" s="82" t="str"/>
-      <x:c r="H54" s="82" t="str"/>
-      <x:c r="I54" s="82" t="str"/>
-      <x:c r="J54" s="82" t="str"/>
-      <x:c r="K54" s="141" t="str"/>
-    </x:row>
-    <x:row r="55">
-      <x:c r="A55" s="82" t="str"/>
-      <x:c r="B55" s="84" t="str"/>
-      <x:c r="C55" s="96" t="str"/>
-      <x:c r="D55" s="82" t="str"/>
-      <x:c r="E55" s="82" t="str"/>
-      <x:c r="F55" s="82" t="str"/>
-      <x:c r="G55" s="82" t="str"/>
-      <x:c r="H55" s="82" t="str"/>
-      <x:c r="I55" s="82" t="str"/>
-      <x:c r="J55" s="82" t="str"/>
-      <x:c r="K55" s="141" t="str"/>
-    </x:row>
-    <x:row r="56">
-      <x:c r="A56" s="82" t="str"/>
-      <x:c r="B56" s="84" t="str"/>
-      <x:c r="C56" s="96" t="str"/>
-      <x:c r="D56" s="82" t="str"/>
-      <x:c r="E56" s="82" t="str"/>
-      <x:c r="F56" s="82" t="str"/>
-      <x:c r="G56" s="82" t="str"/>
-      <x:c r="H56" s="82" t="str"/>
-      <x:c r="I56" s="82" t="str"/>
-      <x:c r="J56" s="82" t="str"/>
-      <x:c r="K56" s="141" t="str"/>
-    </x:row>
-    <x:row r="57">
-      <x:c r="A57" s="82" t="str"/>
-      <x:c r="B57" s="84" t="str"/>
-      <x:c r="C57" s="96" t="str"/>
-      <x:c r="D57" s="82" t="str"/>
-      <x:c r="E57" s="82" t="str"/>
-      <x:c r="F57" s="82" t="str"/>
-      <x:c r="G57" s="82" t="str"/>
-      <x:c r="H57" s="82" t="str"/>
-      <x:c r="I57" s="82" t="str"/>
-      <x:c r="J57" s="82" t="str"/>
-      <x:c r="K57" s="141" t="str"/>
-    </x:row>
-    <x:row r="58">
-      <x:c r="A58" s="82" t="str"/>
-      <x:c r="B58" s="84" t="str"/>
-      <x:c r="C58" s="96" t="str"/>
-      <x:c r="D58" s="82" t="str"/>
-      <x:c r="E58" s="82" t="str"/>
-      <x:c r="F58" s="82" t="str"/>
-      <x:c r="G58" s="82" t="str"/>
-      <x:c r="H58" s="82" t="str"/>
-      <x:c r="I58" s="82" t="str"/>
-      <x:c r="J58" s="82" t="str"/>
-      <x:c r="K58" s="141" t="str"/>
-    </x:row>
-    <x:row r="59">
-      <x:c r="A59" s="82" t="str"/>
-      <x:c r="B59" s="84" t="str"/>
-      <x:c r="C59" s="96" t="str"/>
-      <x:c r="D59" s="82" t="str"/>
-      <x:c r="E59" s="82" t="str"/>
-      <x:c r="F59" s="82" t="str"/>
-      <x:c r="G59" s="82" t="str"/>
-      <x:c r="H59" s="82" t="str"/>
-      <x:c r="I59" s="82" t="str"/>
-      <x:c r="J59" s="82" t="str"/>
-      <x:c r="K59" s="141" t="str"/>
-    </x:row>
-    <x:row r="60">
-      <x:c r="A60" s="82" t="str"/>
-      <x:c r="B60" s="84" t="str"/>
-      <x:c r="C60" s="96" t="str"/>
-      <x:c r="D60" s="82" t="str"/>
-      <x:c r="E60" s="82" t="str"/>
-      <x:c r="F60" s="82" t="str"/>
-      <x:c r="G60" s="82" t="str"/>
-      <x:c r="H60" s="82" t="str"/>
-      <x:c r="I60" s="82" t="str"/>
-      <x:c r="J60" s="82" t="str"/>
-      <x:c r="K60" s="141" t="str"/>
-    </x:row>
-    <x:row r="61">
-      <x:c r="A61" s="82" t="str"/>
-      <x:c r="B61" s="84" t="str"/>
-      <x:c r="C61" s="96" t="str"/>
-      <x:c r="D61" s="82" t="str"/>
-      <x:c r="E61" s="82" t="str"/>
-      <x:c r="F61" s="82" t="str"/>
-      <x:c r="G61" s="82" t="str"/>
-      <x:c r="H61" s="82" t="str"/>
-      <x:c r="I61" s="82" t="str"/>
-      <x:c r="J61" s="82" t="str"/>
-      <x:c r="K61" s="141" t="str"/>
-    </x:row>
-    <x:row r="62">
-      <x:c r="A62" s="82" t="str"/>
-      <x:c r="B62" s="84" t="str"/>
-      <x:c r="C62" s="96" t="str"/>
-      <x:c r="D62" s="82" t="str"/>
-      <x:c r="E62" s="82" t="str"/>
-      <x:c r="F62" s="82" t="str"/>
-      <x:c r="G62" s="82" t="str"/>
-      <x:c r="H62" s="82" t="str"/>
-      <x:c r="I62" s="82" t="str"/>
-      <x:c r="J62" s="82" t="str"/>
-      <x:c r="K62" s="141" t="str"/>
-    </x:row>
-    <x:row r="63">
-      <x:c r="A63" s="82" t="str"/>
-      <x:c r="B63" s="84" t="str"/>
-      <x:c r="C63" s="96" t="str"/>
-      <x:c r="D63" s="82" t="str"/>
-      <x:c r="E63" s="82" t="str"/>
-      <x:c r="F63" s="82" t="str"/>
-      <x:c r="G63" s="82" t="str"/>
-      <x:c r="H63" s="82" t="str"/>
-      <x:c r="I63" s="82" t="str"/>
-      <x:c r="J63" s="82" t="str"/>
-      <x:c r="K63" s="141" t="str"/>
-    </x:row>
-    <x:row r="64">
-      <x:c r="A64" s="82" t="str"/>
-      <x:c r="B64" s="84" t="str"/>
-      <x:c r="C64" s="96" t="str"/>
-      <x:c r="D64" s="82" t="str"/>
-      <x:c r="E64" s="82" t="str"/>
-      <x:c r="F64" s="82" t="str"/>
-      <x:c r="G64" s="82" t="str"/>
-      <x:c r="H64" s="82" t="str"/>
-      <x:c r="I64" s="82" t="str"/>
-      <x:c r="J64" s="82" t="str"/>
-      <x:c r="K64" s="141" t="str"/>
-    </x:row>
-    <x:row r="65">
-      <x:c r="A65" s="82" t="str"/>
-      <x:c r="B65" s="84" t="str"/>
-      <x:c r="C65" s="96" t="str"/>
-      <x:c r="D65" s="82" t="str"/>
-      <x:c r="E65" s="82" t="str"/>
-      <x:c r="F65" s="82" t="str"/>
-      <x:c r="G65" s="82" t="str"/>
-      <x:c r="H65" s="82" t="str"/>
-      <x:c r="I65" s="82" t="str"/>
-      <x:c r="J65" s="82" t="str"/>
-      <x:c r="K65" s="141" t="str"/>
-    </x:row>
-    <x:row r="66">
-      <x:c r="A66" s="82" t="str"/>
-      <x:c r="B66" s="84" t="str"/>
-      <x:c r="C66" s="96" t="str"/>
-      <x:c r="D66" s="82" t="str"/>
-      <x:c r="E66" s="82" t="str"/>
-      <x:c r="F66" s="82" t="str"/>
-      <x:c r="G66" s="82" t="str"/>
-      <x:c r="H66" s="82" t="str"/>
-      <x:c r="I66" s="82" t="str"/>
-      <x:c r="J66" s="82" t="str"/>
-      <x:c r="K66" s="141" t="str"/>
-    </x:row>
-    <x:row r="67">
-      <x:c r="A67" s="82" t="str"/>
-      <x:c r="B67" s="84" t="str"/>
-      <x:c r="C67" s="96" t="str"/>
-      <x:c r="D67" s="82" t="str"/>
-      <x:c r="E67" s="82" t="str"/>
-      <x:c r="F67" s="82" t="str"/>
-      <x:c r="G67" s="82" t="str"/>
-      <x:c r="H67" s="82" t="str"/>
-      <x:c r="I67" s="82" t="str"/>
-      <x:c r="J67" s="82" t="str"/>
-      <x:c r="K67" s="141" t="str"/>
-    </x:row>
-    <x:row r="68">
-      <x:c r="A68" s="82" t="str"/>
-      <x:c r="B68" s="84" t="str"/>
-      <x:c r="C68" s="96" t="str"/>
-      <x:c r="D68" s="82" t="str"/>
-      <x:c r="E68" s="82" t="str"/>
-      <x:c r="F68" s="82" t="str"/>
-      <x:c r="G68" s="82" t="str"/>
-      <x:c r="H68" s="82" t="str"/>
-      <x:c r="I68" s="82" t="str"/>
-      <x:c r="J68" s="82" t="str"/>
-      <x:c r="K68" s="141" t="str"/>
-    </x:row>
-    <x:row r="69">
-      <x:c r="A69" s="82" t="str"/>
-      <x:c r="B69" s="84" t="str"/>
-      <x:c r="C69" s="96" t="str"/>
-      <x:c r="D69" s="82" t="str"/>
-      <x:c r="E69" s="82" t="str"/>
-      <x:c r="F69" s="82" t="str"/>
-      <x:c r="G69" s="82" t="str"/>
-      <x:c r="H69" s="82" t="str"/>
-      <x:c r="I69" s="82" t="str"/>
-      <x:c r="J69" s="82" t="str"/>
-      <x:c r="K69" s="141" t="str"/>
-    </x:row>
-    <x:row r="70">
-      <x:c r="A70" s="82" t="str"/>
-      <x:c r="B70" s="84" t="str"/>
-      <x:c r="C70" s="96" t="str"/>
-      <x:c r="D70" s="82" t="str"/>
-      <x:c r="E70" s="82" t="str"/>
-      <x:c r="F70" s="82" t="str"/>
-      <x:c r="G70" s="82" t="str"/>
-      <x:c r="H70" s="82" t="str"/>
-      <x:c r="I70" s="82" t="str"/>
-      <x:c r="J70" s="82" t="str"/>
-      <x:c r="K70" s="141" t="str"/>
-    </x:row>
-    <x:row r="71">
-      <x:c r="A71" s="82" t="str"/>
-      <x:c r="B71" s="84" t="str"/>
-      <x:c r="C71" s="96" t="str"/>
-      <x:c r="D71" s="82" t="str"/>
-      <x:c r="E71" s="82" t="str"/>
-      <x:c r="F71" s="82" t="str"/>
-      <x:c r="G71" s="82" t="str"/>
-      <x:c r="H71" s="82" t="str"/>
-      <x:c r="I71" s="82" t="str"/>
-      <x:c r="J71" s="82" t="str"/>
-      <x:c r="K71" s="141" t="str"/>
-    </x:row>
-    <x:row r="72">
-      <x:c r="A72" s="82" t="str"/>
-      <x:c r="B72" s="84" t="str"/>
-      <x:c r="C72" s="96" t="str"/>
-      <x:c r="D72" s="82" t="str"/>
-      <x:c r="E72" s="82" t="str"/>
-      <x:c r="F72" s="82" t="str"/>
-      <x:c r="G72" s="82" t="str"/>
-      <x:c r="H72" s="82" t="str"/>
-      <x:c r="I72" s="82" t="str"/>
-      <x:c r="J72" s="82" t="str"/>
-      <x:c r="K72" s="141" t="str"/>
-    </x:row>
-    <x:row r="73">
-      <x:c r="A73" s="82" t="str"/>
-      <x:c r="B73" s="84" t="str"/>
-      <x:c r="C73" s="96" t="str"/>
-      <x:c r="D73" s="82" t="str"/>
-      <x:c r="E73" s="82" t="str"/>
-      <x:c r="F73" s="82" t="str"/>
-      <x:c r="G73" s="82" t="str"/>
-      <x:c r="H73" s="82" t="str"/>
-      <x:c r="I73" s="82" t="str"/>
-      <x:c r="J73" s="82" t="str"/>
-      <x:c r="K73" s="141" t="str"/>
-    </x:row>
-    <x:row r="74">
-      <x:c r="A74" s="82" t="str"/>
-      <x:c r="B74" s="84" t="str"/>
-      <x:c r="C74" s="96" t="str"/>
-      <x:c r="D74" s="82" t="str"/>
-      <x:c r="E74" s="82" t="str"/>
-      <x:c r="F74" s="82" t="str"/>
-      <x:c r="G74" s="82" t="str"/>
-      <x:c r="H74" s="82" t="str"/>
-      <x:c r="I74" s="82" t="str"/>
-      <x:c r="J74" s="82" t="str"/>
-      <x:c r="K74" s="141" t="str"/>
-    </x:row>
-    <x:row r="75">
-      <x:c r="A75" s="82" t="str"/>
-      <x:c r="B75" s="84" t="str"/>
-      <x:c r="C75" s="96" t="str"/>
-      <x:c r="D75" s="82" t="str"/>
-      <x:c r="E75" s="82" t="str"/>
-      <x:c r="F75" s="82" t="str"/>
-      <x:c r="G75" s="82" t="str"/>
-      <x:c r="H75" s="82" t="str"/>
-      <x:c r="I75" s="82" t="str"/>
-      <x:c r="J75" s="82" t="str"/>
-      <x:c r="K75" s="141" t="str"/>
-    </x:row>
-    <x:row r="76">
-      <x:c r="A76" s="82" t="str"/>
-      <x:c r="B76" s="84" t="str"/>
-      <x:c r="C76" s="96" t="str"/>
-      <x:c r="D76" s="82" t="str"/>
-      <x:c r="E76" s="82" t="str"/>
-      <x:c r="F76" s="82" t="str"/>
-      <x:c r="G76" s="82" t="str"/>
-      <x:c r="H76" s="82" t="str"/>
-      <x:c r="I76" s="82" t="str"/>
-      <x:c r="J76" s="82" t="str"/>
-      <x:c r="K76" s="141" t="str"/>
-    </x:row>
-    <x:row r="77">
-      <x:c r="A77" s="82" t="str"/>
-      <x:c r="B77" s="84" t="str"/>
-      <x:c r="C77" s="96" t="str"/>
-      <x:c r="D77" s="82" t="str"/>
-      <x:c r="E77" s="82" t="str"/>
-      <x:c r="F77" s="82" t="str"/>
-      <x:c r="G77" s="82" t="str"/>
-      <x:c r="H77" s="82" t="str"/>
-      <x:c r="I77" s="82" t="str"/>
-      <x:c r="J77" s="82" t="str"/>
-      <x:c r="K77" s="141" t="str"/>
-    </x:row>
-    <x:row r="78">
-      <x:c r="A78" s="82" t="str"/>
-      <x:c r="B78" s="84" t="str"/>
-      <x:c r="C78" s="96" t="str"/>
-      <x:c r="D78" s="82" t="str"/>
-      <x:c r="E78" s="82" t="str"/>
-      <x:c r="F78" s="82" t="str"/>
-      <x:c r="G78" s="82" t="str"/>
-      <x:c r="H78" s="82" t="str"/>
-      <x:c r="I78" s="82" t="str"/>
-      <x:c r="J78" s="82" t="str"/>
-      <x:c r="K78" s="141" t="str"/>
-    </x:row>
-    <x:row r="79">
-      <x:c r="A79" s="82" t="str"/>
-      <x:c r="B79" s="84" t="str"/>
-      <x:c r="C79" s="96" t="str"/>
-      <x:c r="D79" s="82" t="str"/>
-      <x:c r="E79" s="82" t="str"/>
-      <x:c r="F79" s="82" t="str"/>
-      <x:c r="G79" s="82" t="str"/>
-      <x:c r="H79" s="82" t="str"/>
-      <x:c r="I79" s="82" t="str"/>
-      <x:c r="J79" s="82" t="str"/>
-      <x:c r="K79" s="141" t="str"/>
-    </x:row>
-    <x:row r="80">
-      <x:c r="A80" s="82" t="str"/>
-      <x:c r="B80" s="84" t="str"/>
-      <x:c r="C80" s="96" t="str"/>
-      <x:c r="D80" s="82" t="str"/>
-      <x:c r="E80" s="82" t="str"/>
-      <x:c r="F80" s="82" t="str"/>
-      <x:c r="G80" s="82" t="str"/>
-      <x:c r="H80" s="82" t="str"/>
-      <x:c r="I80" s="82" t="str"/>
-      <x:c r="J80" s="82" t="str"/>
-      <x:c r="K80" s="141" t="str"/>
-    </x:row>
-    <x:row r="81">
-      <x:c r="A81" s="82" t="str"/>
-      <x:c r="B81" s="84" t="str"/>
-      <x:c r="C81" s="96" t="str"/>
-      <x:c r="D81" s="82" t="str"/>
-      <x:c r="E81" s="82" t="str"/>
-      <x:c r="F81" s="82" t="str"/>
-      <x:c r="G81" s="82" t="str"/>
-      <x:c r="H81" s="82" t="str"/>
-      <x:c r="I81" s="82" t="str"/>
-      <x:c r="J81" s="82" t="str"/>
-      <x:c r="K81" s="141" t="str"/>
-    </x:row>
-    <x:row r="82">
-      <x:c r="A82" s="82" t="str"/>
-      <x:c r="B82" s="84" t="str"/>
-      <x:c r="C82" s="96" t="str"/>
-      <x:c r="D82" s="82" t="str"/>
-      <x:c r="E82" s="82" t="str"/>
-      <x:c r="F82" s="82" t="str"/>
-      <x:c r="G82" s="82" t="str"/>
-      <x:c r="H82" s="82" t="str"/>
-      <x:c r="I82" s="82" t="str"/>
-      <x:c r="J82" s="82" t="str"/>
-      <x:c r="K82" s="141" t="str"/>
-    </x:row>
-    <x:row r="83">
-      <x:c r="A83" s="82" t="str"/>
-      <x:c r="B83" s="84" t="str"/>
-      <x:c r="C83" s="96" t="str"/>
-      <x:c r="D83" s="82" t="str"/>
-      <x:c r="E83" s="82" t="str"/>
-      <x:c r="F83" s="82" t="str"/>
-      <x:c r="G83" s="82" t="str"/>
-      <x:c r="H83" s="82" t="str"/>
-      <x:c r="I83" s="82" t="str"/>
-      <x:c r="J83" s="82" t="str"/>
-      <x:c r="K83" s="141" t="str"/>
-    </x:row>
-    <x:row r="84">
-      <x:c r="A84" s="82" t="str"/>
-      <x:c r="B84" s="84" t="str"/>
-      <x:c r="C84" s="96" t="str"/>
-      <x:c r="D84" s="82" t="str"/>
-      <x:c r="E84" s="82" t="str"/>
-      <x:c r="F84" s="82" t="str"/>
-      <x:c r="G84" s="82" t="str"/>
-      <x:c r="H84" s="82" t="str"/>
-      <x:c r="I84" s="82" t="str"/>
-      <x:c r="J84" s="82" t="str"/>
-      <x:c r="K84" s="141" t="str"/>
-    </x:row>
-    <x:row r="85">
-      <x:c r="A85" s="82" t="str"/>
-      <x:c r="B85" s="84" t="str"/>
-      <x:c r="C85" s="96" t="str"/>
-      <x:c r="D85" s="82" t="str"/>
-      <x:c r="E85" s="82" t="str"/>
-      <x:c r="F85" s="82" t="str"/>
-      <x:c r="G85" s="82" t="str"/>
-      <x:c r="H85" s="82" t="str"/>
-      <x:c r="I85" s="82" t="str"/>
-      <x:c r="J85" s="82" t="str"/>
-      <x:c r="K85" s="141" t="str"/>
-    </x:row>
-    <x:row r="86">
-      <x:c r="A86" s="82" t="str"/>
-      <x:c r="B86" s="84" t="str"/>
-      <x:c r="C86" s="96" t="str"/>
-      <x:c r="D86" s="82" t="str"/>
-      <x:c r="E86" s="82" t="str"/>
-      <x:c r="F86" s="82" t="str"/>
-      <x:c r="G86" s="82" t="str"/>
-      <x:c r="H86" s="82" t="str"/>
-      <x:c r="I86" s="82" t="str"/>
-      <x:c r="J86" s="82" t="str"/>
-      <x:c r="K86" s="141" t="str"/>
-    </x:row>
-    <x:row r="87">
-      <x:c r="A87" s="82" t="str"/>
-      <x:c r="B87" s="84" t="str"/>
-      <x:c r="C87" s="96" t="str"/>
-      <x:c r="D87" s="82" t="str"/>
-      <x:c r="E87" s="82" t="str"/>
-      <x:c r="F87" s="82" t="str"/>
-      <x:c r="G87" s="82" t="str"/>
-      <x:c r="H87" s="82" t="str"/>
-      <x:c r="I87" s="82" t="str"/>
-      <x:c r="J87" s="82" t="str"/>
-      <x:c r="K87" s="141" t="str"/>
-    </x:row>
-    <x:row r="88">
-      <x:c r="A88" s="82" t="str"/>
-      <x:c r="B88" s="84" t="str"/>
-      <x:c r="C88" s="96" t="str"/>
-      <x:c r="D88" s="82" t="str"/>
-      <x:c r="E88" s="82" t="str"/>
-      <x:c r="F88" s="82" t="str"/>
-      <x:c r="G88" s="82" t="str"/>
-      <x:c r="H88" s="82" t="str"/>
-      <x:c r="I88" s="82" t="str"/>
-      <x:c r="J88" s="82" t="str"/>
-      <x:c r="K88" s="141" t="str"/>
-    </x:row>
-    <x:row r="89">
-      <x:c r="A89" s="82" t="str"/>
-      <x:c r="B89" s="84" t="str"/>
-      <x:c r="C89" s="96" t="str"/>
-      <x:c r="D89" s="82" t="str"/>
-      <x:c r="E89" s="82" t="str"/>
-      <x:c r="F89" s="82" t="str"/>
-      <x:c r="G89" s="82" t="str"/>
-      <x:c r="H89" s="82" t="str"/>
-      <x:c r="I89" s="82" t="str"/>
-      <x:c r="J89" s="82" t="str"/>
-      <x:c r="K89" s="141" t="str"/>
-    </x:row>
-    <x:row r="90">
-      <x:c r="A90" s="82" t="str"/>
-      <x:c r="B90" s="84" t="str"/>
-      <x:c r="C90" s="96" t="str"/>
-      <x:c r="D90" s="82" t="str"/>
-      <x:c r="E90" s="82" t="str"/>
-      <x:c r="F90" s="82" t="str"/>
-      <x:c r="G90" s="82" t="str"/>
-      <x:c r="H90" s="82" t="str"/>
-      <x:c r="I90" s="82" t="str"/>
-      <x:c r="J90" s="82" t="str"/>
-      <x:c r="K90" s="141" t="str"/>
-    </x:row>
-    <x:row r="91">
-      <x:c r="A91" s="82" t="str"/>
-      <x:c r="B91" s="84" t="str"/>
-      <x:c r="C91" s="96" t="str"/>
-      <x:c r="D91" s="82" t="str"/>
-      <x:c r="E91" s="82" t="str"/>
-      <x:c r="F91" s="82" t="str"/>
-      <x:c r="G91" s="82" t="str"/>
-      <x:c r="H91" s="82" t="str"/>
-      <x:c r="I91" s="82" t="str"/>
-      <x:c r="J91" s="82" t="str"/>
-      <x:c r="K91" s="141" t="str"/>
-    </x:row>
-    <x:row r="92">
-      <x:c r="A92" s="82" t="str"/>
-      <x:c r="B92" s="84" t="str"/>
-      <x:c r="C92" s="96" t="str"/>
-      <x:c r="D92" s="82" t="str"/>
-      <x:c r="E92" s="82" t="str"/>
-      <x:c r="F92" s="82" t="str"/>
-      <x:c r="G92" s="82" t="str"/>
-      <x:c r="H92" s="82" t="str"/>
-      <x:c r="I92" s="82" t="str"/>
-      <x:c r="J92" s="82" t="str"/>
-      <x:c r="K92" s="141" t="str"/>
-    </x:row>
-    <x:row r="93">
-      <x:c r="A93" s="82" t="str"/>
-      <x:c r="B93" s="84" t="str"/>
-      <x:c r="C93" s="96" t="str"/>
-      <x:c r="D93" s="82" t="str"/>
-      <x:c r="E93" s="82" t="str"/>
-      <x:c r="F93" s="82" t="str"/>
-      <x:c r="G93" s="82" t="str"/>
-      <x:c r="H93" s="82" t="str"/>
-      <x:c r="I93" s="82" t="str"/>
-      <x:c r="J93" s="82" t="str"/>
-      <x:c r="K93" s="141" t="str"/>
-    </x:row>
-    <x:row r="94">
-      <x:c r="A94" s="82" t="str"/>
-      <x:c r="B94" s="84" t="str"/>
-      <x:c r="C94" s="96" t="str"/>
-      <x:c r="D94" s="82" t="str"/>
-      <x:c r="E94" s="82" t="str"/>
-      <x:c r="F94" s="82" t="str"/>
-      <x:c r="G94" s="82" t="str"/>
-      <x:c r="H94" s="82" t="str"/>
-      <x:c r="I94" s="82" t="str"/>
-      <x:c r="J94" s="82" t="str"/>
-      <x:c r="K94" s="141" t="str"/>
-    </x:row>
-    <x:row r="95">
-      <x:c r="A95" s="82" t="str"/>
-      <x:c r="B95" s="84" t="str"/>
-      <x:c r="C95" s="96" t="str"/>
-      <x:c r="D95" s="82" t="str"/>
-      <x:c r="E95" s="82" t="str"/>
-      <x:c r="F95" s="82" t="str"/>
-      <x:c r="G95" s="82" t="str"/>
-      <x:c r="H95" s="82" t="str"/>
-      <x:c r="I95" s="82" t="str"/>
-      <x:c r="J95" s="82" t="str"/>
-      <x:c r="K95" s="141" t="str"/>
-    </x:row>
-    <x:row r="96">
-      <x:c r="A96" s="82" t="str"/>
-      <x:c r="B96" s="84" t="str"/>
-      <x:c r="C96" s="96" t="str"/>
-      <x:c r="D96" s="82" t="str"/>
-      <x:c r="E96" s="82" t="str"/>
-      <x:c r="F96" s="82" t="str"/>
-      <x:c r="G96" s="82" t="str"/>
-      <x:c r="H96" s="82" t="str"/>
-      <x:c r="I96" s="82" t="str"/>
-      <x:c r="J96" s="82" t="str"/>
-      <x:c r="K96" s="141" t="str"/>
-    </x:row>
-    <x:row r="97">
-      <x:c r="A97" s="82" t="str"/>
-      <x:c r="B97" s="84" t="str"/>
-      <x:c r="C97" s="96" t="str"/>
-      <x:c r="D97" s="82" t="str"/>
-      <x:c r="E97" s="82" t="str"/>
-      <x:c r="F97" s="82" t="str"/>
-      <x:c r="G97" s="82" t="str"/>
-      <x:c r="H97" s="82" t="str"/>
-      <x:c r="I97" s="82" t="str"/>
-      <x:c r="J97" s="82" t="str"/>
-      <x:c r="K97" s="141" t="str"/>
-    </x:row>
-    <x:row r="98">
-      <x:c r="A98" s="82" t="str"/>
-      <x:c r="B98" s="84" t="str"/>
-      <x:c r="C98" s="96" t="str"/>
-      <x:c r="D98" s="82" t="str"/>
-      <x:c r="E98" s="82" t="str"/>
-      <x:c r="F98" s="82" t="str"/>
-      <x:c r="G98" s="82" t="str"/>
-      <x:c r="H98" s="82" t="str"/>
-      <x:c r="I98" s="82" t="str"/>
-      <x:c r="J98" s="82" t="str"/>
-      <x:c r="K98" s="141" t="str"/>
-    </x:row>
-    <x:row r="99">
-      <x:c r="A99" s="82" t="str"/>
-      <x:c r="B99" s="84" t="str"/>
-      <x:c r="C99" s="96" t="str"/>
-      <x:c r="D99" s="82" t="str"/>
-      <x:c r="E99" s="82" t="str"/>
-      <x:c r="F99" s="82" t="str"/>
-      <x:c r="G99" s="82" t="str"/>
-      <x:c r="H99" s="82" t="str"/>
-      <x:c r="I99" s="82" t="str"/>
-      <x:c r="J99" s="82" t="str"/>
-      <x:c r="K99" s="141" t="str"/>
-    </x:row>
-    <x:row r="100">
-      <x:c r="A100" s="82" t="str"/>
-      <x:c r="B100" s="84" t="str"/>
-      <x:c r="C100" s="96" t="str"/>
-      <x:c r="D100" s="82" t="str"/>
-      <x:c r="E100" s="82" t="str"/>
-      <x:c r="F100" s="82" t="str"/>
-      <x:c r="G100" s="82" t="str"/>
-      <x:c r="H100" s="82" t="str"/>
-      <x:c r="I100" s="82" t="str"/>
-      <x:c r="J100" s="82" t="str"/>
-      <x:c r="K100" s="141" t="str"/>
-    </x:row>
-    <x:row r="101">
-      <x:c r="A101" s="82" t="str"/>
-      <x:c r="B101" s="84" t="str"/>
-      <x:c r="C101" s="96" t="str"/>
-      <x:c r="D101" s="82" t="str"/>
-      <x:c r="E101" s="82" t="str"/>
-      <x:c r="F101" s="82" t="str"/>
-      <x:c r="G101" s="82" t="str"/>
-      <x:c r="H101" s="82" t="str"/>
-      <x:c r="I101" s="82" t="str"/>
-      <x:c r="J101" s="82" t="str"/>
-      <x:c r="K101" s="141" t="str"/>
-    </x:row>
-    <x:row r="102">
-      <x:c r="A102" s="82" t="str"/>
-      <x:c r="B102" s="84" t="str"/>
-      <x:c r="C102" s="96" t="str"/>
-      <x:c r="D102" s="82" t="str"/>
-      <x:c r="E102" s="82" t="str"/>
-      <x:c r="F102" s="82" t="str"/>
-      <x:c r="G102" s="82" t="str"/>
-      <x:c r="H102" s="82" t="str"/>
-      <x:c r="I102" s="82" t="str"/>
-      <x:c r="J102" s="82" t="str"/>
-      <x:c r="K102" s="141" t="str"/>
-    </x:row>
-    <x:row r="103">
-      <x:c r="A103" s="82" t="str"/>
-      <x:c r="B103" s="84" t="str"/>
-      <x:c r="C103" s="96" t="str"/>
-      <x:c r="D103" s="82" t="str"/>
-      <x:c r="E103" s="82" t="str"/>
-      <x:c r="F103" s="82" t="str"/>
-      <x:c r="G103" s="82" t="str"/>
-      <x:c r="H103" s="82" t="str"/>
-      <x:c r="I103" s="82" t="str"/>
-      <x:c r="J103" s="82" t="str"/>
-      <x:c r="K103" s="141" t="str"/>
-    </x:row>
-    <x:row r="104">
-      <x:c r="A104" s="82" t="str"/>
-      <x:c r="B104" s="84" t="str"/>
-      <x:c r="C104" s="96" t="str"/>
-      <x:c r="D104" s="82" t="str"/>
-      <x:c r="E104" s="82" t="str"/>
-      <x:c r="F104" s="82" t="str"/>
-      <x:c r="G104" s="82" t="str"/>
-      <x:c r="H104" s="82" t="str"/>
-      <x:c r="I104" s="82" t="str"/>
-      <x:c r="J104" s="82" t="str"/>
-      <x:c r="K104" s="141" t="str"/>
-    </x:row>
-    <x:row r="105">
-      <x:c r="A105" s="82" t="str"/>
-      <x:c r="B105" s="84" t="str"/>
-      <x:c r="C105" s="96" t="str"/>
-      <x:c r="D105" s="82" t="str"/>
-      <x:c r="E105" s="82" t="str"/>
-      <x:c r="F105" s="82" t="str"/>
-      <x:c r="G105" s="82" t="str"/>
-      <x:c r="H105" s="82" t="str"/>
-      <x:c r="I105" s="82" t="str"/>
-      <x:c r="J105" s="82" t="str"/>
-      <x:c r="K105" s="141" t="str"/>
-    </x:row>
-    <x:row r="106">
-      <x:c r="A106" s="82" t="str"/>
-      <x:c r="B106" s="84" t="str"/>
-      <x:c r="C106" s="96" t="str"/>
-      <x:c r="D106" s="82" t="str"/>
-      <x:c r="E106" s="82" t="str"/>
-      <x:c r="F106" s="82" t="str"/>
-      <x:c r="G106" s="82" t="str"/>
-      <x:c r="H106" s="82" t="str"/>
-      <x:c r="I106" s="82" t="str"/>
-      <x:c r="J106" s="82" t="str"/>
-      <x:c r="K106" s="141" t="str"/>
-    </x:row>
-    <x:row r="107">
-      <x:c r="A107" s="82" t="str"/>
-      <x:c r="B107" s="84" t="str"/>
-      <x:c r="C107" s="96" t="str"/>
-      <x:c r="D107" s="82" t="str"/>
-      <x:c r="E107" s="82" t="str"/>
-      <x:c r="F107" s="82" t="str"/>
-      <x:c r="G107" s="82" t="str"/>
-      <x:c r="H107" s="82" t="str"/>
-      <x:c r="I107" s="82" t="str"/>
-      <x:c r="J107" s="82" t="str"/>
-      <x:c r="K107" s="141" t="str"/>
-    </x:row>
-    <x:row r="108">
-      <x:c r="A108" s="82" t="str"/>
-      <x:c r="B108" s="84" t="str"/>
-      <x:c r="C108" s="96" t="str"/>
-      <x:c r="D108" s="82" t="str"/>
-      <x:c r="E108" s="82" t="str"/>
-      <x:c r="F108" s="82" t="str"/>
-      <x:c r="G108" s="82" t="str"/>
-      <x:c r="H108" s="82" t="str"/>
-      <x:c r="I108" s="82" t="str"/>
-      <x:c r="J108" s="82" t="str"/>
-      <x:c r="K108" s="141" t="str"/>
-    </x:row>
-    <x:row r="109">
-      <x:c r="A109" s="82" t="str"/>
-      <x:c r="B109" s="84" t="str"/>
-      <x:c r="C109" s="96" t="str"/>
-      <x:c r="D109" s="82" t="str"/>
-      <x:c r="E109" s="82" t="str"/>
-      <x:c r="F109" s="82" t="str"/>
-      <x:c r="G109" s="82" t="str"/>
-      <x:c r="H109" s="82" t="str"/>
-      <x:c r="I109" s="82" t="str"/>
-      <x:c r="J109" s="82" t="str"/>
-      <x:c r="K109" s="141" t="str"/>
-    </x:row>
-    <x:row r="110">
-      <x:c r="A110" s="82" t="str"/>
-      <x:c r="B110" s="84" t="str"/>
-      <x:c r="C110" s="96" t="str"/>
-      <x:c r="D110" s="82" t="str"/>
-      <x:c r="E110" s="82" t="str"/>
-      <x:c r="F110" s="82" t="str"/>
-      <x:c r="G110" s="82" t="str"/>
-      <x:c r="H110" s="82" t="str"/>
-      <x:c r="I110" s="82" t="str"/>
-      <x:c r="J110" s="82" t="str"/>
-      <x:c r="K110" s="141" t="str"/>
-    </x:row>
-    <x:row r="111">
-      <x:c r="A111" s="82" t="str"/>
-      <x:c r="B111" s="84" t="str"/>
-      <x:c r="C111" s="96" t="str"/>
-      <x:c r="D111" s="82" t="str"/>
-      <x:c r="E111" s="82" t="str"/>
-      <x:c r="F111" s="82" t="str"/>
-      <x:c r="G111" s="82" t="str"/>
-      <x:c r="H111" s="82" t="str"/>
-      <x:c r="I111" s="82" t="str"/>
-      <x:c r="J111" s="82" t="str"/>
-      <x:c r="K111" s="141" t="str"/>
-    </x:row>
-    <x:row r="112">
-      <x:c r="A112" s="82" t="str"/>
-      <x:c r="B112" s="84" t="str"/>
-      <x:c r="C112" s="96" t="str"/>
-      <x:c r="D112" s="82" t="str"/>
-      <x:c r="E112" s="82" t="str"/>
-      <x:c r="F112" s="82" t="str"/>
-      <x:c r="G112" s="82" t="str"/>
-      <x:c r="H112" s="82" t="str"/>
-      <x:c r="I112" s="82" t="str"/>
-      <x:c r="J112" s="82" t="str"/>
-      <x:c r="K112" s="141" t="str"/>
-    </x:row>
-    <x:row r="113">
-      <x:c r="A113" s="82" t="str"/>
-      <x:c r="B113" s="84" t="str"/>
-      <x:c r="C113" s="96" t="str"/>
-      <x:c r="D113" s="82" t="str"/>
-      <x:c r="E113" s="82" t="str"/>
-      <x:c r="F113" s="82" t="str"/>
-      <x:c r="G113" s="82" t="str"/>
-      <x:c r="H113" s="82" t="str"/>
-      <x:c r="I113" s="82" t="str"/>
-      <x:c r="J113" s="82" t="str"/>
-      <x:c r="K113" s="141" t="str"/>
-    </x:row>
-    <x:row r="114">
-      <x:c r="A114" s="82" t="str"/>
-      <x:c r="B114" s="84" t="str"/>
-      <x:c r="C114" s="96" t="str"/>
-      <x:c r="D114" s="82" t="str"/>
-      <x:c r="E114" s="82" t="str"/>
-      <x:c r="F114" s="82" t="str"/>
-      <x:c r="G114" s="82" t="str"/>
-      <x:c r="H114" s="82" t="str"/>
-      <x:c r="I114" s="82" t="str"/>
-      <x:c r="J114" s="82" t="str"/>
-      <x:c r="K114" s="141" t="str"/>
-    </x:row>
-    <x:row r="115">
-      <x:c r="A115" s="82" t="str"/>
-      <x:c r="B115" s="84" t="str"/>
-      <x:c r="C115" s="96" t="str"/>
-      <x:c r="D115" s="82" t="str"/>
-      <x:c r="E115" s="82" t="str"/>
-      <x:c r="F115" s="82" t="str"/>
-      <x:c r="G115" s="82" t="str"/>
-      <x:c r="H115" s="82" t="str"/>
-      <x:c r="I115" s="82" t="str"/>
-      <x:c r="J115" s="82" t="str"/>
-      <x:c r="K115" s="141" t="str"/>
-    </x:row>
-    <x:row r="116">
-      <x:c r="A116" s="82" t="str"/>
-      <x:c r="B116" s="84" t="str"/>
-      <x:c r="C116" s="96" t="str"/>
-      <x:c r="D116" s="82" t="str"/>
-      <x:c r="E116" s="82" t="str"/>
-      <x:c r="F116" s="82" t="str"/>
-      <x:c r="G116" s="82" t="str"/>
-      <x:c r="H116" s="82" t="str"/>
-      <x:c r="I116" s="82" t="str"/>
-      <x:c r="J116" s="82" t="str"/>
-      <x:c r="K116" s="141" t="str"/>
-    </x:row>
-    <x:row r="117">
-      <x:c r="A117" s="82" t="str"/>
-      <x:c r="B117" s="84" t="str"/>
-      <x:c r="C117" s="96" t="str"/>
-      <x:c r="D117" s="82" t="str"/>
-      <x:c r="E117" s="82" t="str"/>
-      <x:c r="F117" s="82" t="str"/>
-      <x:c r="G117" s="82" t="str"/>
-      <x:c r="H117" s="82" t="str"/>
-      <x:c r="I117" s="82" t="str"/>
-      <x:c r="J117" s="82" t="str"/>
-      <x:c r="K117" s="141" t="str"/>
-    </x:row>
-    <x:row r="118">
-      <x:c r="A118" s="82" t="str"/>
-      <x:c r="B118" s="84" t="str"/>
-      <x:c r="C118" s="96" t="str"/>
-      <x:c r="D118" s="82" t="str"/>
-      <x:c r="E118" s="82" t="str"/>
-      <x:c r="F118" s="82" t="str"/>
-      <x:c r="G118" s="82" t="str"/>
-      <x:c r="H118" s="82" t="str"/>
-      <x:c r="I118" s="82" t="str"/>
-      <x:c r="J118" s="82" t="str"/>
-      <x:c r="K118" s="141" t="str"/>
-    </x:row>
-    <x:row r="119">
-      <x:c r="A119" s="82" t="str"/>
-      <x:c r="B119" s="84" t="str"/>
-      <x:c r="C119" s="96" t="str"/>
-      <x:c r="D119" s="82" t="str"/>
-      <x:c r="E119" s="82" t="str"/>
-      <x:c r="F119" s="82" t="str"/>
-      <x:c r="G119" s="82" t="str"/>
-      <x:c r="H119" s="82" t="str"/>
-      <x:c r="I119" s="82" t="str"/>
-      <x:c r="J119" s="82" t="str"/>
-      <x:c r="K119" s="141" t="str"/>
-    </x:row>
-    <x:row r="120">
-      <x:c r="A120" s="82" t="str"/>
-      <x:c r="B120" s="84" t="str"/>
-      <x:c r="C120" s="96" t="str"/>
-      <x:c r="D120" s="82" t="str"/>
-      <x:c r="E120" s="82" t="str"/>
-      <x:c r="F120" s="82" t="str"/>
-      <x:c r="G120" s="82" t="str"/>
-      <x:c r="H120" s="82" t="str"/>
-      <x:c r="I120" s="82" t="str"/>
-      <x:c r="J120" s="82" t="str"/>
-      <x:c r="K120" s="141" t="str"/>
-    </x:row>
-    <x:row r="121">
-      <x:c r="A121" s="82" t="str"/>
-      <x:c r="B121" s="84" t="str"/>
-      <x:c r="C121" s="96" t="str"/>
-      <x:c r="D121" s="82" t="str"/>
-      <x:c r="E121" s="82" t="str"/>
-      <x:c r="F121" s="82" t="str"/>
-      <x:c r="G121" s="82" t="str"/>
-      <x:c r="H121" s="82" t="str"/>
-      <x:c r="I121" s="82" t="str"/>
-      <x:c r="J121" s="82" t="str"/>
-      <x:c r="K121" s="141" t="str"/>
-    </x:row>
-    <x:row r="122">
-      <x:c r="A122" s="82" t="str"/>
-      <x:c r="B122" s="84" t="str"/>
-      <x:c r="C122" s="96" t="str"/>
-      <x:c r="D122" s="82" t="str"/>
-      <x:c r="E122" s="82" t="str"/>
-      <x:c r="F122" s="82" t="str"/>
-      <x:c r="G122" s="82" t="str"/>
-      <x:c r="H122" s="82" t="str"/>
-      <x:c r="I122" s="82" t="str"/>
-      <x:c r="J122" s="82" t="str"/>
-      <x:c r="K122" s="141" t="str"/>
-    </x:row>
-    <x:row r="123">
-      <x:c r="A123" s="82" t="str"/>
-      <x:c r="B123" s="84" t="str"/>
-      <x:c r="C123" s="96" t="str"/>
-      <x:c r="D123" s="82" t="str"/>
-      <x:c r="E123" s="82" t="str"/>
-      <x:c r="F123" s="82" t="str"/>
-      <x:c r="G123" s="82" t="str"/>
-      <x:c r="H123" s="82" t="str"/>
-      <x:c r="I123" s="82" t="str"/>
-      <x:c r="J123" s="82" t="str"/>
-      <x:c r="K123" s="141" t="str"/>
-    </x:row>
-    <x:row r="124">
-      <x:c r="A124" s="82" t="str"/>
-      <x:c r="B124" s="84" t="str"/>
-      <x:c r="C124" s="96" t="str"/>
-      <x:c r="D124" s="82" t="str"/>
-      <x:c r="E124" s="82" t="str"/>
-      <x:c r="F124" s="82" t="str"/>
-      <x:c r="G124" s="82" t="str"/>
-      <x:c r="H124" s="82" t="str"/>
-      <x:c r="I124" s="82" t="str"/>
-      <x:c r="J124" s="82" t="str"/>
-      <x:c r="K124" s="141" t="str"/>
-    </x:row>
-    <x:row r="125">
-      <x:c r="A125" s="82" t="str"/>
-      <x:c r="B125" s="84" t="str"/>
-      <x:c r="C125" s="96" t="str"/>
-      <x:c r="D125" s="82" t="str"/>
-      <x:c r="E125" s="82" t="str"/>
-      <x:c r="F125" s="82" t="str"/>
-      <x:c r="G125" s="82" t="str"/>
-      <x:c r="H125" s="82" t="str"/>
-      <x:c r="I125" s="82" t="str"/>
-      <x:c r="J125" s="82" t="str"/>
-      <x:c r="K125" s="141" t="str"/>
-    </x:row>
-    <x:row r="126">
-      <x:c r="A126" s="82" t="str"/>
-      <x:c r="B126" s="84" t="str"/>
-      <x:c r="C126" s="96" t="str"/>
-      <x:c r="D126" s="82" t="str"/>
-      <x:c r="E126" s="82" t="str"/>
-      <x:c r="F126" s="82" t="str"/>
-      <x:c r="G126" s="82" t="str"/>
-      <x:c r="H126" s="82" t="str"/>
-      <x:c r="I126" s="82" t="str"/>
-      <x:c r="J126" s="82" t="str"/>
-      <x:c r="K126" s="141" t="str"/>
-    </x:row>
-    <x:row r="127">
-      <x:c r="A127" s="82" t="str"/>
-      <x:c r="B127" s="84" t="str"/>
-      <x:c r="C127" s="96" t="str"/>
-      <x:c r="D127" s="82" t="str"/>
-      <x:c r="E127" s="82" t="str"/>
-      <x:c r="F127" s="82" t="str"/>
-      <x:c r="G127" s="82" t="str"/>
-      <x:c r="H127" s="82" t="str"/>
-      <x:c r="I127" s="82" t="str"/>
-      <x:c r="J127" s="82" t="str"/>
-      <x:c r="K127" s="141" t="str"/>
-    </x:row>
-    <x:row r="128">
-      <x:c r="A128" s="82" t="str"/>
-      <x:c r="B128" s="84" t="str"/>
-      <x:c r="C128" s="96" t="str"/>
-      <x:c r="D128" s="82" t="str"/>
-      <x:c r="E128" s="82" t="str"/>
-      <x:c r="F128" s="82" t="str"/>
-      <x:c r="G128" s="82" t="str"/>
-      <x:c r="H128" s="82" t="str"/>
-      <x:c r="I128" s="82" t="str"/>
-      <x:c r="J128" s="82" t="str"/>
-      <x:c r="K128" s="141" t="str"/>
-    </x:row>
-    <x:row r="129">
-      <x:c r="A129" s="82" t="str"/>
-      <x:c r="B129" s="84" t="str"/>
-      <x:c r="C129" s="96" t="str"/>
-      <x:c r="D129" s="82" t="str"/>
-      <x:c r="E129" s="82" t="str"/>
-      <x:c r="F129" s="82" t="str"/>
-      <x:c r="G129" s="82" t="str"/>
-      <x:c r="H129" s="82" t="str"/>
-      <x:c r="I129" s="82" t="str"/>
-      <x:c r="J129" s="82" t="str"/>
-      <x:c r="K129" s="141" t="str"/>
-    </x:row>
-    <x:row r="130">
-      <x:c r="A130" s="82" t="str"/>
-      <x:c r="B130" s="84" t="str"/>
-      <x:c r="C130" s="96" t="str"/>
-      <x:c r="D130" s="82" t="str"/>
-      <x:c r="E130" s="82" t="str"/>
-      <x:c r="F130" s="82" t="str"/>
-      <x:c r="G130" s="82" t="str"/>
-      <x:c r="H130" s="82" t="str"/>
-      <x:c r="I130" s="82" t="str"/>
-      <x:c r="J130" s="82" t="str"/>
-      <x:c r="K130" s="141" t="str"/>
-    </x:row>
-    <x:row r="131">
-      <x:c r="A131" s="82" t="str"/>
-      <x:c r="B131" s="84" t="str"/>
-      <x:c r="C131" s="96" t="str"/>
-      <x:c r="D131" s="82" t="str"/>
-      <x:c r="E131" s="82" t="str"/>
-      <x:c r="F131" s="82" t="str"/>
-      <x:c r="G131" s="82" t="str"/>
-      <x:c r="H131" s="82" t="str"/>
-      <x:c r="I131" s="82" t="str"/>
-      <x:c r="J131" s="82" t="str"/>
-      <x:c r="K131" s="141" t="str"/>
-    </x:row>
-    <x:row r="132">
-      <x:c r="A132" s="82" t="str"/>
-      <x:c r="B132" s="84" t="str"/>
-      <x:c r="C132" s="96" t="str"/>
-      <x:c r="D132" s="82" t="str"/>
-      <x:c r="E132" s="82" t="str"/>
-      <x:c r="F132" s="82" t="str"/>
-      <x:c r="G132" s="82" t="str"/>
-      <x:c r="H132" s="82" t="str"/>
-      <x:c r="I132" s="82" t="str"/>
-      <x:c r="J132" s="82" t="str"/>
-      <x:c r="K132" s="141" t="str"/>
-    </x:row>
-    <x:row r="133">
-      <x:c r="A133" s="82" t="str"/>
-      <x:c r="B133" s="84" t="str"/>
-      <x:c r="C133" s="96" t="str"/>
-      <x:c r="D133" s="82" t="str"/>
-      <x:c r="E133" s="82" t="str"/>
-      <x:c r="F133" s="82" t="str"/>
-      <x:c r="G133" s="82" t="str"/>
-      <x:c r="H133" s="82" t="str"/>
-      <x:c r="I133" s="82" t="str"/>
-      <x:c r="J133" s="82" t="str"/>
-      <x:c r="K133" s="141" t="str"/>
-    </x:row>
-    <x:row r="134">
-      <x:c r="A134" s="82" t="str"/>
-      <x:c r="B134" s="84" t="str"/>
-      <x:c r="C134" s="96" t="str"/>
-      <x:c r="D134" s="82" t="str"/>
-      <x:c r="E134" s="82" t="str"/>
-      <x:c r="F134" s="82" t="str"/>
-      <x:c r="G134" s="82" t="str"/>
-      <x:c r="H134" s="82" t="str"/>
-      <x:c r="I134" s="82" t="str"/>
-      <x:c r="J134" s="82" t="str"/>
-      <x:c r="K134" s="141" t="str"/>
-    </x:row>
-    <x:row r="135">
-      <x:c r="A135" s="82" t="str"/>
-      <x:c r="B135" s="84" t="str"/>
-      <x:c r="C135" s="96" t="str"/>
-      <x:c r="D135" s="82" t="str"/>
-      <x:c r="E135" s="82" t="str"/>
-      <x:c r="F135" s="82" t="str"/>
-      <x:c r="G135" s="82" t="str"/>
-      <x:c r="H135" s="82" t="str"/>
-      <x:c r="I135" s="82" t="str"/>
-      <x:c r="J135" s="82" t="str"/>
-      <x:c r="K135" s="141" t="str"/>
-    </x:row>
-    <x:row r="136">
-      <x:c r="A136" s="82" t="str"/>
-      <x:c r="B136" s="84" t="str"/>
-      <x:c r="C136" s="96" t="str"/>
-      <x:c r="D136" s="82" t="str"/>
-      <x:c r="E136" s="82" t="str"/>
-      <x:c r="F136" s="82" t="str"/>
-      <x:c r="G136" s="82" t="str"/>
-      <x:c r="H136" s="82" t="str"/>
-      <x:c r="I136" s="82" t="str"/>
-      <x:c r="J136" s="82" t="str"/>
-      <x:c r="K136" s="141" t="str"/>
-    </x:row>
-    <x:row r="137">
-      <x:c r="A137" s="82" t="str"/>
-      <x:c r="B137" s="84" t="str"/>
-      <x:c r="C137" s="96" t="str"/>
-      <x:c r="D137" s="82" t="str"/>
-      <x:c r="E137" s="82" t="str"/>
-      <x:c r="F137" s="82" t="str"/>
-      <x:c r="G137" s="82" t="str"/>
-      <x:c r="H137" s="82" t="str"/>
-      <x:c r="I137" s="82" t="str"/>
-      <x:c r="J137" s="82" t="str"/>
-      <x:c r="K137" s="141" t="str"/>
-    </x:row>
-    <x:row r="138">
-      <x:c r="A138" s="82" t="str"/>
-      <x:c r="B138" s="84" t="str"/>
-      <x:c r="C138" s="96" t="str"/>
-      <x:c r="D138" s="82" t="str"/>
-      <x:c r="E138" s="82" t="str"/>
-      <x:c r="F138" s="82" t="str"/>
-      <x:c r="G138" s="82" t="str"/>
-      <x:c r="H138" s="82" t="str"/>
-      <x:c r="I138" s="82" t="str"/>
-      <x:c r="J138" s="82" t="str"/>
-      <x:c r="K138" s="141" t="str"/>
-    </x:row>
-    <x:row r="139">
-      <x:c r="A139" s="82" t="str"/>
-      <x:c r="B139" s="84" t="str"/>
-      <x:c r="C139" s="96" t="str"/>
-      <x:c r="D139" s="82" t="str"/>
-      <x:c r="E139" s="82" t="str"/>
-      <x:c r="F139" s="82" t="str"/>
-      <x:c r="G139" s="82" t="str"/>
-      <x:c r="H139" s="82" t="str"/>
-      <x:c r="I139" s="82" t="str"/>
-      <x:c r="J139" s="82" t="str"/>
-      <x:c r="K139" s="141" t="str"/>
-    </x:row>
-    <x:row r="140">
-      <x:c r="A140" s="82" t="str"/>
-      <x:c r="B140" s="84" t="str"/>
-      <x:c r="C140" s="96" t="str"/>
-      <x:c r="D140" s="82" t="str"/>
-      <x:c r="E140" s="82" t="str"/>
-      <x:c r="F140" s="82" t="str"/>
-      <x:c r="G140" s="82" t="str"/>
-      <x:c r="H140" s="82" t="str"/>
-      <x:c r="I140" s="82" t="str"/>
-      <x:c r="J140" s="82" t="str"/>
-      <x:c r="K140" s="141" t="str"/>
-    </x:row>
-    <x:row r="141">
-      <x:c r="A141" s="82" t="str"/>
-      <x:c r="B141" s="84" t="str"/>
-      <x:c r="C141" s="96" t="str"/>
-      <x:c r="D141" s="82" t="str"/>
-      <x:c r="E141" s="82" t="str"/>
-      <x:c r="F141" s="82" t="str"/>
-      <x:c r="G141" s="82" t="str"/>
-      <x:c r="H141" s="82" t="str"/>
-      <x:c r="I141" s="82" t="str"/>
-      <x:c r="J141" s="82" t="str"/>
-      <x:c r="K141" s="141" t="str"/>
-    </x:row>
-    <x:row r="142">
-      <x:c r="A142" s="82" t="str"/>
-      <x:c r="B142" s="84" t="str"/>
-      <x:c r="C142" s="96" t="str"/>
-      <x:c r="D142" s="82" t="str"/>
-      <x:c r="E142" s="82" t="str"/>
-      <x:c r="F142" s="82" t="str"/>
-      <x:c r="G142" s="82" t="str"/>
-      <x:c r="H142" s="82" t="str"/>
-      <x:c r="I142" s="82" t="str"/>
-      <x:c r="J142" s="82" t="str"/>
-      <x:c r="K142" s="141" t="str"/>
-    </x:row>
-    <x:row r="143">
-      <x:c r="A143" s="82" t="str"/>
-      <x:c r="B143" s="84" t="str"/>
-      <x:c r="C143" s="96" t="str"/>
-      <x:c r="D143" s="82" t="str"/>
-      <x:c r="E143" s="82" t="str"/>
-      <x:c r="F143" s="82" t="str"/>
-      <x:c r="G143" s="82" t="str"/>
-      <x:c r="H143" s="82" t="str"/>
-      <x:c r="I143" s="82" t="str"/>
-      <x:c r="J143" s="82" t="str"/>
-      <x:c r="K143" s="141" t="str"/>
-    </x:row>
-    <x:row r="144">
-      <x:c r="A144" s="82" t="str"/>
-      <x:c r="B144" s="84" t="str"/>
-      <x:c r="C144" s="96" t="str"/>
-      <x:c r="D144" s="82" t="str"/>
-      <x:c r="E144" s="82" t="str"/>
-      <x:c r="F144" s="82" t="str"/>
-      <x:c r="G144" s="82" t="str"/>
-      <x:c r="H144" s="82" t="str"/>
-      <x:c r="I144" s="82" t="str"/>
-      <x:c r="J144" s="82" t="str"/>
-      <x:c r="K144" s="141" t="str"/>
-    </x:row>
-    <x:row r="145">
-      <x:c r="A145" s="82" t="str"/>
-      <x:c r="B145" s="84" t="str"/>
-      <x:c r="C145" s="96" t="str"/>
-      <x:c r="D145" s="82" t="str"/>
-      <x:c r="E145" s="82" t="str"/>
-      <x:c r="F145" s="82" t="str"/>
-      <x:c r="G145" s="82" t="str"/>
-      <x:c r="H145" s="82" t="str"/>
-      <x:c r="I145" s="82" t="str"/>
-      <x:c r="J145" s="82" t="str"/>
-      <x:c r="K145" s="141" t="str"/>
-    </x:row>
-    <x:row r="146">
-      <x:c r="A146" s="82" t="str"/>
-      <x:c r="B146" s="84" t="str"/>
-      <x:c r="C146" s="96" t="str"/>
-      <x:c r="D146" s="82" t="str"/>
-      <x:c r="E146" s="82" t="str"/>
-      <x:c r="F146" s="82" t="str"/>
-      <x:c r="G146" s="82" t="str"/>
-      <x:c r="H146" s="82" t="str"/>
-      <x:c r="I146" s="82" t="str"/>
-      <x:c r="J146" s="82" t="str"/>
-      <x:c r="K146" s="141" t="str"/>
-    </x:row>
-    <x:row r="147">
-      <x:c r="A147" s="82" t="str"/>
-      <x:c r="B147" s="84" t="str"/>
-      <x:c r="C147" s="96" t="str"/>
-      <x:c r="D147" s="82" t="str"/>
-      <x:c r="E147" s="82" t="str"/>
-      <x:c r="F147" s="82" t="str"/>
-      <x:c r="G147" s="82" t="str"/>
-      <x:c r="H147" s="82" t="str"/>
-      <x:c r="I147" s="82" t="str"/>
-      <x:c r="J147" s="82" t="str"/>
-      <x:c r="K147" s="141" t="str"/>
-    </x:row>
-    <x:row r="148">
-      <x:c r="A148" s="82" t="str"/>
-      <x:c r="B148" s="84" t="str"/>
-      <x:c r="C148" s="96" t="str"/>
-      <x:c r="D148" s="82" t="str"/>
-      <x:c r="E148" s="82" t="str"/>
-      <x:c r="F148" s="82" t="str"/>
-      <x:c r="G148" s="82" t="str"/>
-      <x:c r="H148" s="82" t="str"/>
-      <x:c r="I148" s="82" t="str"/>
-      <x:c r="J148" s="82" t="str"/>
-      <x:c r="K148" s="141" t="str"/>
-    </x:row>
-    <x:row r="149">
-      <x:c r="A149" s="82" t="str"/>
-      <x:c r="B149" s="84" t="str"/>
-      <x:c r="C149" s="96" t="str"/>
-      <x:c r="D149" s="82" t="str"/>
-      <x:c r="E149" s="82" t="str"/>
-      <x:c r="F149" s="82" t="str"/>
-      <x:c r="G149" s="82" t="str"/>
-      <x:c r="H149" s="82" t="str"/>
-      <x:c r="I149" s="82" t="str"/>
-      <x:c r="J149" s="82" t="str"/>
-      <x:c r="K149" s="141" t="str"/>
-    </x:row>
-    <x:row r="150">
-      <x:c r="A150" s="82" t="str"/>
-      <x:c r="B150" s="84" t="str"/>
-      <x:c r="C150" s="96" t="str"/>
-      <x:c r="D150" s="82" t="str"/>
-      <x:c r="E150" s="82" t="str"/>
-      <x:c r="F150" s="82" t="str"/>
-      <x:c r="G150" s="82" t="str"/>
-      <x:c r="H150" s="82" t="str"/>
-      <x:c r="I150" s="82" t="str"/>
-      <x:c r="J150" s="82" t="str"/>
-      <x:c r="K150" s="141" t="str"/>
-    </x:row>
-    <x:row r="151">
-      <x:c r="A151" s="82" t="str"/>
-      <x:c r="B151" s="84" t="str"/>
-      <x:c r="C151" s="96" t="str"/>
-      <x:c r="D151" s="82" t="str"/>
-      <x:c r="E151" s="82" t="str"/>
-      <x:c r="F151" s="82" t="str"/>
-      <x:c r="G151" s="82" t="str"/>
-      <x:c r="H151" s="82" t="str"/>
-      <x:c r="I151" s="82" t="str"/>
-      <x:c r="J151" s="82" t="str"/>
-      <x:c r="K151" s="141" t="str"/>
-    </x:row>
-    <x:row r="152">
-      <x:c r="A152" s="82" t="str"/>
-      <x:c r="B152" s="84" t="str"/>
-      <x:c r="C152" s="96" t="str"/>
-      <x:c r="D152" s="82" t="str"/>
-      <x:c r="E152" s="82" t="str"/>
-      <x:c r="F152" s="82" t="str"/>
-      <x:c r="G152" s="82" t="str"/>
-      <x:c r="H152" s="82" t="str"/>
-      <x:c r="I152" s="82" t="str"/>
-      <x:c r="J152" s="82" t="str"/>
-      <x:c r="K152" s="141" t="str"/>
-    </x:row>
-    <x:row r="153">
-      <x:c r="A153" s="82" t="str"/>
-      <x:c r="B153" s="84" t="str"/>
-      <x:c r="C153" s="96" t="str"/>
-      <x:c r="D153" s="82" t="str"/>
-      <x:c r="E153" s="82" t="str"/>
-      <x:c r="F153" s="82" t="str"/>
-      <x:c r="G153" s="82" t="str"/>
-      <x:c r="H153" s="82" t="str"/>
-      <x:c r="I153" s="82" t="str"/>
-      <x:c r="J153" s="82" t="str"/>
-      <x:c r="K153" s="141" t="str"/>
-    </x:row>
-    <x:row r="154">
-      <x:c r="A154" s="82" t="str"/>
-      <x:c r="B154" s="84" t="str"/>
-      <x:c r="C154" s="96" t="str"/>
-      <x:c r="D154" s="82" t="str"/>
-      <x:c r="E154" s="82" t="str"/>
-      <x:c r="F154" s="82" t="str"/>
-      <x:c r="G154" s="82" t="str"/>
-      <x:c r="H154" s="82" t="str"/>
-      <x:c r="I154" s="82" t="str"/>
-      <x:c r="J154" s="82" t="str"/>
-      <x:c r="K154" s="141" t="str"/>
-    </x:row>
-    <x:row r="155">
-      <x:c r="A155" s="82" t="str"/>
-      <x:c r="B155" s="84" t="str"/>
-      <x:c r="C155" s="96" t="str"/>
-      <x:c r="D155" s="82" t="str"/>
-      <x:c r="E155" s="82" t="str"/>
-      <x:c r="F155" s="82" t="str"/>
-      <x:c r="G155" s="82" t="str"/>
-      <x:c r="H155" s="82" t="str"/>
-      <x:c r="I155" s="82" t="str"/>
-      <x:c r="J155" s="82" t="str"/>
-      <x:c r="K155" s="141" t="str"/>
-    </x:row>
-    <x:row r="156">
-      <x:c r="A156" s="82" t="str"/>
-      <x:c r="B156" s="84" t="str"/>
-      <x:c r="C156" s="96" t="str"/>
-      <x:c r="D156" s="82" t="str"/>
-      <x:c r="E156" s="82" t="str"/>
-      <x:c r="F156" s="82" t="str"/>
-      <x:c r="G156" s="82" t="str"/>
-      <x:c r="H156" s="82" t="str"/>
-      <x:c r="I156" s="82" t="str"/>
-      <x:c r="J156" s="82" t="str"/>
-      <x:c r="K156" s="141" t="str"/>
-    </x:row>
-    <x:row r="157">
-      <x:c r="A157" s="82" t="str"/>
-      <x:c r="B157" s="84" t="str"/>
-      <x:c r="C157" s="96" t="str"/>
-      <x:c r="D157" s="82" t="str"/>
-      <x:c r="E157" s="82" t="str"/>
-      <x:c r="F157" s="82" t="str"/>
-      <x:c r="G157" s="82" t="str"/>
-      <x:c r="H157" s="82" t="str"/>
-      <x:c r="I157" s="82" t="str"/>
-      <x:c r="J157" s="82" t="str"/>
-      <x:c r="K157" s="141" t="str"/>
-    </x:row>
-    <x:row r="158">
-      <x:c r="A158" s="82" t="str"/>
-      <x:c r="B158" s="84" t="str"/>
-      <x:c r="C158" s="96" t="str"/>
-      <x:c r="D158" s="82" t="str"/>
-      <x:c r="E158" s="82" t="str"/>
-      <x:c r="F158" s="82" t="str"/>
-      <x:c r="G158" s="82" t="str"/>
-      <x:c r="H158" s="82" t="str"/>
-      <x:c r="I158" s="82" t="str"/>
-      <x:c r="J158" s="82" t="str"/>
-      <x:c r="K158" s="141" t="str"/>
-    </x:row>
-    <x:row r="159">
-      <x:c r="A159" s="82" t="str"/>
-      <x:c r="B159" s="84" t="str"/>
-      <x:c r="C159" s="96" t="str"/>
-      <x:c r="D159" s="82" t="str"/>
-      <x:c r="E159" s="82" t="str"/>
-      <x:c r="F159" s="82" t="str"/>
-      <x:c r="G159" s="82" t="str"/>
-      <x:c r="H159" s="82" t="str"/>
-      <x:c r="I159" s="82" t="str"/>
-      <x:c r="J159" s="82" t="str"/>
-      <x:c r="K159" s="141" t="str"/>
-    </x:row>
-    <x:row r="160">
-      <x:c r="A160" s="82" t="str"/>
-      <x:c r="B160" s="84" t="str"/>
-      <x:c r="C160" s="96" t="str"/>
-      <x:c r="D160" s="82" t="str"/>
-      <x:c r="E160" s="82" t="str"/>
-      <x:c r="F160" s="82" t="str"/>
-      <x:c r="G160" s="82" t="str"/>
-      <x:c r="H160" s="82" t="str"/>
-      <x:c r="I160" s="82" t="str"/>
-      <x:c r="J160" s="82" t="str"/>
-      <x:c r="K160" s="141" t="str"/>
-    </x:row>
-    <x:row r="161">
-      <x:c r="A161" s="82" t="str"/>
-      <x:c r="B161" s="84" t="str"/>
-      <x:c r="C161" s="96" t="str"/>
-      <x:c r="D161" s="82" t="str"/>
-      <x:c r="E161" s="82" t="str"/>
-      <x:c r="F161" s="82" t="str"/>
-      <x:c r="G161" s="82" t="str"/>
-      <x:c r="H161" s="82" t="str"/>
-      <x:c r="I161" s="82" t="str"/>
-      <x:c r="J161" s="82" t="str"/>
-      <x:c r="K161" s="141" t="str"/>
-    </x:row>
-    <x:row r="162">
-      <x:c r="A162" s="82" t="str"/>
-      <x:c r="B162" s="84" t="str"/>
-      <x:c r="C162" s="96" t="str"/>
-      <x:c r="D162" s="82" t="str"/>
-      <x:c r="E162" s="82" t="str"/>
-      <x:c r="F162" s="82" t="str"/>
-      <x:c r="G162" s="82" t="str"/>
-      <x:c r="H162" s="82" t="str"/>
-      <x:c r="I162" s="82" t="str"/>
-      <x:c r="J162" s="82" t="str"/>
-      <x:c r="K162" s="141" t="str"/>
-    </x:row>
-    <x:row r="163">
-      <x:c r="A163" s="82" t="str"/>
-      <x:c r="B163" s="84" t="str"/>
-      <x:c r="C163" s="96" t="str"/>
-      <x:c r="D163" s="82" t="str"/>
-      <x:c r="E163" s="82" t="str"/>
-      <x:c r="F163" s="82" t="str"/>
-      <x:c r="G163" s="82" t="str"/>
-      <x:c r="H163" s="82" t="str"/>
-      <x:c r="I163" s="82" t="str"/>
-      <x:c r="J163" s="82" t="str"/>
-      <x:c r="K163" s="141" t="str"/>
-    </x:row>
-    <x:row r="164">
-      <x:c r="A164" s="82" t="str"/>
-      <x:c r="B164" s="84" t="str"/>
-      <x:c r="C164" s="96" t="str"/>
-      <x:c r="D164" s="82" t="str"/>
-      <x:c r="E164" s="82" t="str"/>
-      <x:c r="F164" s="82" t="str"/>
-      <x:c r="G164" s="82" t="str"/>
-      <x:c r="H164" s="82" t="str"/>
-      <x:c r="I164" s="82" t="str"/>
-      <x:c r="J164" s="82" t="str"/>
-      <x:c r="K164" s="141" t="str"/>
-    </x:row>
-    <x:row r="165">
-      <x:c r="A165" s="82" t="str"/>
-      <x:c r="B165" s="84" t="str"/>
-      <x:c r="C165" s="96" t="str"/>
-      <x:c r="D165" s="82" t="str"/>
-      <x:c r="E165" s="82" t="str"/>
-      <x:c r="F165" s="82" t="str"/>
-      <x:c r="G165" s="82" t="str"/>
-      <x:c r="H165" s="82" t="str"/>
-      <x:c r="I165" s="82" t="str"/>
-      <x:c r="J165" s="82" t="str"/>
-      <x:c r="K165" s="141" t="str"/>
-    </x:row>
-    <x:row r="166">
-      <x:c r="A166" s="82" t="str"/>
-      <x:c r="B166" s="84" t="str"/>
-      <x:c r="C166" s="96" t="str"/>
-      <x:c r="D166" s="82" t="str"/>
-      <x:c r="E166" s="82" t="str"/>
-      <x:c r="F166" s="82" t="str"/>
-      <x:c r="G166" s="82" t="str"/>
-      <x:c r="H166" s="82" t="str"/>
-      <x:c r="I166" s="82" t="str"/>
-      <x:c r="J166" s="82" t="str"/>
-      <x:c r="K166" s="141" t="str"/>
-    </x:row>
-    <x:row r="167">
-      <x:c r="A167" s="82" t="str"/>
-      <x:c r="B167" s="84" t="str"/>
-      <x:c r="C167" s="96" t="str"/>
-      <x:c r="D167" s="82" t="str"/>
-      <x:c r="E167" s="82" t="str"/>
-      <x:c r="F167" s="82" t="str"/>
-      <x:c r="G167" s="82" t="str"/>
-      <x:c r="H167" s="82" t="str"/>
-      <x:c r="I167" s="82" t="str"/>
-      <x:c r="J167" s="82" t="str"/>
-      <x:c r="K167" s="141" t="str"/>
-    </x:row>
-    <x:row r="168">
-      <x:c r="A168" s="82" t="str"/>
-      <x:c r="B168" s="84" t="str"/>
-      <x:c r="C168" s="96" t="str"/>
-      <x:c r="D168" s="82" t="str"/>
-      <x:c r="E168" s="82" t="str"/>
-      <x:c r="F168" s="82" t="str"/>
-      <x:c r="G168" s="82" t="str"/>
-      <x:c r="H168" s="82" t="str"/>
-      <x:c r="I168" s="82" t="str"/>
-      <x:c r="J168" s="82" t="str"/>
-      <x:c r="K168" s="141" t="str"/>
-    </x:row>
-    <x:row r="169">
-      <x:c r="A169" s="82" t="str"/>
-      <x:c r="B169" s="84" t="str"/>
-      <x:c r="C169" s="96" t="str"/>
-      <x:c r="D169" s="82" t="str"/>
-      <x:c r="E169" s="82" t="str"/>
-      <x:c r="F169" s="82" t="str"/>
-      <x:c r="G169" s="82" t="str"/>
-      <x:c r="H169" s="82" t="str"/>
-      <x:c r="I169" s="82" t="str"/>
-      <x:c r="J169" s="82" t="str"/>
-      <x:c r="K169" s="141" t="str"/>
-    </x:row>
-    <x:row r="170">
-      <x:c r="A170" s="82" t="str"/>
-      <x:c r="B170" s="84" t="str"/>
-      <x:c r="C170" s="96" t="str"/>
-      <x:c r="D170" s="82" t="str"/>
-      <x:c r="E170" s="82" t="str"/>
-      <x:c r="F170" s="82" t="str"/>
-      <x:c r="G170" s="82" t="str"/>
-      <x:c r="H170" s="82" t="str"/>
-      <x:c r="I170" s="82" t="str"/>
-      <x:c r="J170" s="82" t="str"/>
-      <x:c r="K170" s="141" t="str"/>
-    </x:row>
-    <x:row r="171">
-      <x:c r="A171" s="82" t="str"/>
-      <x:c r="B171" s="84" t="str"/>
-      <x:c r="C171" s="96" t="str"/>
-      <x:c r="D171" s="82" t="str"/>
-      <x:c r="E171" s="82" t="str"/>
-      <x:c r="F171" s="82" t="str"/>
-      <x:c r="G171" s="82" t="str"/>
-      <x:c r="H171" s="82" t="str"/>
-      <x:c r="I171" s="82" t="str"/>
-      <x:c r="J171" s="82" t="str"/>
-      <x:c r="K171" s="141" t="str"/>
-    </x:row>
-    <x:row r="172">
-      <x:c r="A172" s="82" t="str"/>
-      <x:c r="B172" s="84" t="str"/>
-      <x:c r="C172" s="96" t="str"/>
-      <x:c r="D172" s="82" t="str"/>
-      <x:c r="E172" s="82" t="str"/>
-      <x:c r="F172" s="82" t="str"/>
-      <x:c r="G172" s="82" t="str"/>
-      <x:c r="H172" s="82" t="str"/>
-      <x:c r="I172" s="82" t="str"/>
-      <x:c r="J172" s="82" t="str"/>
-      <x:c r="K172" s="141" t="str"/>
-    </x:row>
-    <x:row r="173">
-      <x:c r="A173" s="82" t="str"/>
-      <x:c r="B173" s="84" t="str"/>
-      <x:c r="C173" s="96" t="str"/>
-      <x:c r="D173" s="82" t="str"/>
-      <x:c r="E173" s="82" t="str"/>
-      <x:c r="F173" s="82" t="str"/>
-      <x:c r="G173" s="82" t="str"/>
-      <x:c r="H173" s="82" t="str"/>
-      <x:c r="I173" s="82" t="str"/>
-      <x:c r="J173" s="82" t="str"/>
-      <x:c r="K173" s="141" t="str"/>
-    </x:row>
-    <x:row r="174">
-      <x:c r="A174" s="82" t="str"/>
-      <x:c r="B174" s="84" t="str"/>
-      <x:c r="C174" s="96" t="str"/>
-      <x:c r="D174" s="82" t="str"/>
-      <x:c r="E174" s="82" t="str"/>
-      <x:c r="F174" s="82" t="str"/>
-      <x:c r="G174" s="82" t="str"/>
-      <x:c r="H174" s="82" t="str"/>
-      <x:c r="I174" s="82" t="str"/>
-      <x:c r="J174" s="82" t="str"/>
-      <x:c r="K174" s="141" t="str"/>
-    </x:row>
-    <x:row r="175">
-      <x:c r="A175" s="82" t="str"/>
-      <x:c r="B175" s="84" t="str"/>
-      <x:c r="C175" s="96" t="str"/>
-      <x:c r="D175" s="82" t="str"/>
-      <x:c r="E175" s="82" t="str"/>
-      <x:c r="F175" s="82" t="str"/>
-      <x:c r="G175" s="82" t="str"/>
-      <x:c r="H175" s="82" t="str"/>
-      <x:c r="I175" s="82" t="str"/>
-      <x:c r="J175" s="82" t="str"/>
-      <x:c r="K175" s="141" t="str"/>
-    </x:row>
-    <x:row r="176">
-      <x:c r="A176" s="82" t="str"/>
-      <x:c r="B176" s="84" t="str"/>
-      <x:c r="C176" s="96" t="str"/>
-      <x:c r="D176" s="82" t="str"/>
-      <x:c r="E176" s="82" t="str"/>
-      <x:c r="F176" s="82" t="str"/>
-      <x:c r="G176" s="82" t="str"/>
-      <x:c r="H176" s="82" t="str"/>
-      <x:c r="I176" s="82" t="str"/>
-      <x:c r="J176" s="82" t="str"/>
-      <x:c r="K176" s="141" t="str"/>
-    </x:row>
-    <x:row r="177">
-      <x:c r="A177" s="82" t="str"/>
-      <x:c r="B177" s="84" t="str"/>
-      <x:c r="C177" s="96" t="str"/>
-      <x:c r="D177" s="82" t="str"/>
-      <x:c r="E177" s="82" t="str"/>
-      <x:c r="F177" s="82" t="str"/>
-      <x:c r="G177" s="82" t="str"/>
-      <x:c r="H177" s="82" t="str"/>
-      <x:c r="I177" s="82" t="str"/>
-      <x:c r="J177" s="82" t="str"/>
-      <x:c r="K177" s="141" t="str"/>
-    </x:row>
-    <x:row r="178">
-      <x:c r="A178" s="82" t="str"/>
-      <x:c r="B178" s="84" t="str"/>
-      <x:c r="C178" s="96" t="str"/>
-      <x:c r="D178" s="82" t="str"/>
-      <x:c r="E178" s="82" t="str"/>
-      <x:c r="F178" s="82" t="str"/>
-      <x:c r="G178" s="82" t="str"/>
-      <x:c r="H178" s="82" t="str"/>
-      <x:c r="I178" s="82" t="str"/>
-      <x:c r="J178" s="82" t="str"/>
-      <x:c r="K178" s="141" t="str"/>
-    </x:row>
-    <x:row r="179">
-      <x:c r="A179" s="82" t="str"/>
-      <x:c r="B179" s="84" t="str"/>
-      <x:c r="C179" s="96" t="str"/>
-      <x:c r="D179" s="82" t="str"/>
-      <x:c r="E179" s="82" t="str"/>
-      <x:c r="F179" s="82" t="str"/>
-      <x:c r="G179" s="82" t="str"/>
-      <x:c r="H179" s="82" t="str"/>
-      <x:c r="I179" s="82" t="str"/>
-      <x:c r="J179" s="82" t="str"/>
-      <x:c r="K179" s="141" t="str"/>
-    </x:row>
-    <x:row r="180">
-      <x:c r="A180" s="82" t="str"/>
-      <x:c r="B180" s="84" t="str"/>
-      <x:c r="C180" s="96" t="str"/>
-      <x:c r="D180" s="82" t="str"/>
-      <x:c r="E180" s="82" t="str"/>
-      <x:c r="F180" s="82" t="str"/>
-      <x:c r="G180" s="82" t="str"/>
-      <x:c r="H180" s="82" t="str"/>
-      <x:c r="I180" s="82" t="str"/>
-      <x:c r="J180" s="82" t="str"/>
-      <x:c r="K180" s="141" t="str"/>
-    </x:row>
-    <x:row r="181">
-      <x:c r="A181" s="82" t="str"/>
-      <x:c r="B181" s="84" t="str"/>
-      <x:c r="C181" s="96" t="str"/>
-      <x:c r="D181" s="82" t="str"/>
-      <x:c r="E181" s="82" t="str"/>
-      <x:c r="F181" s="82" t="str"/>
-      <x:c r="G181" s="82" t="str"/>
-      <x:c r="H181" s="82" t="str"/>
-      <x:c r="I181" s="82" t="str"/>
-      <x:c r="J181" s="82" t="str"/>
-      <x:c r="K181" s="141" t="str"/>
-    </x:row>
-    <x:row r="182">
-      <x:c r="A182" s="82" t="str"/>
-      <x:c r="B182" s="84" t="str"/>
-      <x:c r="C182" s="96" t="str"/>
-      <x:c r="D182" s="82" t="str"/>
-      <x:c r="E182" s="82" t="str"/>
-      <x:c r="F182" s="82" t="str"/>
-      <x:c r="G182" s="82" t="str"/>
-      <x:c r="H182" s="82" t="str"/>
-      <x:c r="I182" s="82" t="str"/>
-      <x:c r="J182" s="82" t="str"/>
-      <x:c r="K182" s="141" t="str"/>
-    </x:row>
-    <x:row r="183">
-      <x:c r="A183" s="82" t="str"/>
-      <x:c r="B183" s="84" t="str"/>
-      <x:c r="C183" s="96" t="str"/>
-      <x:c r="D183" s="82" t="str"/>
-      <x:c r="E183" s="82" t="str"/>
-      <x:c r="F183" s="82" t="str"/>
-      <x:c r="G183" s="82" t="str"/>
-      <x:c r="H183" s="82" t="str"/>
-      <x:c r="I183" s="82" t="str"/>
-      <x:c r="J183" s="82" t="str"/>
-      <x:c r="K183" s="141" t="str"/>
-    </x:row>
-    <x:row r="184">
-      <x:c r="A184" s="82" t="str"/>
-      <x:c r="B184" s="84" t="str"/>
-      <x:c r="C184" s="96" t="str"/>
-      <x:c r="D184" s="82" t="str"/>
-      <x:c r="E184" s="82" t="str"/>
-      <x:c r="F184" s="82" t="str"/>
-      <x:c r="G184" s="82" t="str"/>
-      <x:c r="H184" s="82" t="str"/>
-      <x:c r="I184" s="82" t="str"/>
-      <x:c r="J184" s="82" t="str"/>
-      <x:c r="K184" s="141" t="str"/>
-    </x:row>
-    <x:row r="185">
-      <x:c r="A185" s="82" t="str"/>
-      <x:c r="B185" s="84" t="str"/>
-      <x:c r="C185" s="96" t="str"/>
-      <x:c r="D185" s="82" t="str"/>
-      <x:c r="E185" s="82" t="str"/>
-      <x:c r="F185" s="82" t="str"/>
-      <x:c r="G185" s="82" t="str"/>
-      <x:c r="H185" s="82" t="str"/>
-      <x:c r="I185" s="82" t="str"/>
-      <x:c r="J185" s="82" t="str"/>
-      <x:c r="K185" s="141" t="str"/>
-    </x:row>
-    <x:row r="186">
-      <x:c r="A186" s="82" t="str"/>
-      <x:c r="B186" s="84" t="str"/>
-      <x:c r="C186" s="96" t="str"/>
-      <x:c r="D186" s="82" t="str"/>
-      <x:c r="E186" s="82" t="str"/>
-      <x:c r="F186" s="82" t="str"/>
-      <x:c r="G186" s="82" t="str"/>
-      <x:c r="H186" s="82" t="str"/>
-      <x:c r="I186" s="82" t="str"/>
-      <x:c r="J186" s="82" t="str"/>
-      <x:c r="K186" s="141" t="str"/>
-    </x:row>
-    <x:row r="187">
-      <x:c r="A187" s="82" t="str"/>
-      <x:c r="B187" s="84" t="str"/>
-      <x:c r="C187" s="96" t="str"/>
-      <x:c r="D187" s="82" t="str"/>
-      <x:c r="E187" s="82" t="str"/>
-      <x:c r="F187" s="82" t="str"/>
-      <x:c r="G187" s="82" t="str"/>
-      <x:c r="H187" s="82" t="str"/>
-      <x:c r="I187" s="82" t="str"/>
-      <x:c r="J187" s="82" t="str"/>
-      <x:c r="K187" s="141" t="str"/>
-    </x:row>
-    <x:row r="188">
-      <x:c r="A188" s="82" t="str"/>
-      <x:c r="B188" s="84" t="str"/>
-      <x:c r="C188" s="96" t="str"/>
-      <x:c r="D188" s="82" t="str"/>
-      <x:c r="E188" s="82" t="str"/>
-      <x:c r="F188" s="82" t="str"/>
-      <x:c r="G188" s="82" t="str"/>
-      <x:c r="H188" s="82" t="str"/>
-      <x:c r="I188" s="82" t="str"/>
-      <x:c r="J188" s="82" t="str"/>
-      <x:c r="K188" s="141" t="str"/>
-    </x:row>
-    <x:row r="189">
-      <x:c r="A189" s="82" t="str"/>
-      <x:c r="B189" s="84" t="str"/>
-      <x:c r="C189" s="96" t="str"/>
-      <x:c r="D189" s="82" t="str"/>
-      <x:c r="E189" s="82" t="str"/>
-      <x:c r="F189" s="82" t="str"/>
-      <x:c r="G189" s="82" t="str"/>
-      <x:c r="H189" s="82" t="str"/>
-      <x:c r="I189" s="82" t="str"/>
-      <x:c r="J189" s="82" t="str"/>
-      <x:c r="K189" s="141" t="str"/>
-    </x:row>
-    <x:row r="190">
-      <x:c r="A190" s="82" t="str"/>
-      <x:c r="B190" s="84" t="str"/>
-      <x:c r="C190" s="96" t="str"/>
-      <x:c r="D190" s="82" t="str"/>
-      <x:c r="E190" s="82" t="str"/>
-      <x:c r="F190" s="82" t="str"/>
-      <x:c r="G190" s="82" t="str"/>
-      <x:c r="H190" s="82" t="str"/>
-      <x:c r="I190" s="82" t="str"/>
-      <x:c r="J190" s="82" t="str"/>
-      <x:c r="K190" s="141" t="str"/>
-    </x:row>
-    <x:row r="191">
-      <x:c r="A191" s="82" t="str"/>
-      <x:c r="B191" s="84" t="str"/>
-      <x:c r="C191" s="96" t="str"/>
-      <x:c r="D191" s="82" t="str"/>
-      <x:c r="E191" s="82" t="str"/>
-      <x:c r="F191" s="82" t="str"/>
-      <x:c r="G191" s="82" t="str"/>
-      <x:c r="H191" s="82" t="str"/>
-      <x:c r="I191" s="82" t="str"/>
-      <x:c r="J191" s="82" t="str"/>
-      <x:c r="K191" s="141" t="str"/>
-    </x:row>
-    <x:row r="192">
-      <x:c r="A192" s="82" t="str"/>
-      <x:c r="B192" s="84" t="str"/>
-      <x:c r="C192" s="96" t="str"/>
-      <x:c r="D192" s="82" t="str"/>
-      <x:c r="E192" s="82" t="str"/>
-      <x:c r="F192" s="82" t="str"/>
-      <x:c r="G192" s="82" t="str"/>
-      <x:c r="H192" s="82" t="str"/>
-      <x:c r="I192" s="82" t="str"/>
-      <x:c r="J192" s="82" t="str"/>
-      <x:c r="K192" s="141" t="str"/>
-    </x:row>
-    <x:row r="193">
-      <x:c r="A193" s="82" t="str"/>
-      <x:c r="B193" s="84" t="str"/>
-      <x:c r="C193" s="96" t="str"/>
-      <x:c r="D193" s="82" t="str"/>
-      <x:c r="E193" s="82" t="str"/>
-      <x:c r="F193" s="82" t="str"/>
-      <x:c r="G193" s="82" t="str"/>
-      <x:c r="H193" s="82" t="str"/>
-      <x:c r="I193" s="82" t="str"/>
-      <x:c r="J193" s="82" t="str"/>
-      <x:c r="K193" s="141" t="str"/>
-    </x:row>
-    <x:row r="194">
-      <x:c r="A194" s="82" t="str"/>
-      <x:c r="B194" s="84" t="str"/>
-      <x:c r="C194" s="96" t="str"/>
-      <x:c r="D194" s="82" t="str"/>
-      <x:c r="E194" s="82" t="str"/>
-      <x:c r="F194" s="82" t="str"/>
-      <x:c r="G194" s="82" t="str"/>
-      <x:c r="H194" s="82" t="str"/>
-      <x:c r="I194" s="82" t="str"/>
-      <x:c r="J194" s="82" t="str"/>
-      <x:c r="K194" s="141" t="str"/>
-    </x:row>
-    <x:row r="195">
-      <x:c r="A195" s="82" t="str"/>
-      <x:c r="B195" s="84" t="str"/>
-      <x:c r="C195" s="96" t="str"/>
-      <x:c r="D195" s="82" t="str"/>
-      <x:c r="E195" s="82" t="str"/>
-      <x:c r="F195" s="82" t="str"/>
-      <x:c r="G195" s="82" t="str"/>
-      <x:c r="H195" s="82" t="str"/>
-      <x:c r="I195" s="82" t="str"/>
-      <x:c r="J195" s="82" t="str"/>
-      <x:c r="K195" s="141" t="str"/>
-    </x:row>
-    <x:row r="196">
-      <x:c r="A196" s="82" t="str"/>
-      <x:c r="B196" s="84" t="str"/>
-      <x:c r="C196" s="96" t="str"/>
-      <x:c r="D196" s="82" t="str"/>
-      <x:c r="E196" s="82" t="str"/>
-      <x:c r="F196" s="82" t="str"/>
-      <x:c r="G196" s="82" t="str"/>
-      <x:c r="H196" s="82" t="str"/>
-      <x:c r="I196" s="82" t="str"/>
-      <x:c r="J196" s="82" t="str"/>
-      <x:c r="K196" s="141" t="str"/>
-    </x:row>
-    <x:row r="197">
-      <x:c r="A197" s="82" t="str"/>
-      <x:c r="B197" s="84" t="str"/>
-      <x:c r="C197" s="96" t="str"/>
-      <x:c r="D197" s="82" t="str"/>
-      <x:c r="E197" s="82" t="str"/>
-      <x:c r="F197" s="82" t="str"/>
-      <x:c r="G197" s="82" t="str"/>
-      <x:c r="H197" s="82" t="str"/>
-      <x:c r="I197" s="82" t="str"/>
-      <x:c r="J197" s="82" t="str"/>
-      <x:c r="K197" s="141" t="str"/>
-    </x:row>
-    <x:row r="198">
-      <x:c r="A198" s="82" t="str"/>
-      <x:c r="B198" s="84" t="str"/>
-      <x:c r="C198" s="96" t="str"/>
-      <x:c r="D198" s="82" t="str"/>
-      <x:c r="E198" s="82" t="str"/>
-      <x:c r="F198" s="82" t="str"/>
-      <x:c r="G198" s="82" t="str"/>
-      <x:c r="H198" s="82" t="str"/>
-      <x:c r="I198" s="82" t="str"/>
-      <x:c r="J198" s="82" t="str"/>
-      <x:c r="K198" s="141" t="str"/>
-    </x:row>
-    <x:row r="199">
-      <x:c r="A199" s="82" t="str"/>
-      <x:c r="B199" s="84" t="str"/>
-      <x:c r="C199" s="96" t="str"/>
-      <x:c r="D199" s="82" t="str"/>
-      <x:c r="E199" s="82" t="str"/>
-      <x:c r="F199" s="82" t="str"/>
-      <x:c r="G199" s="82" t="str"/>
-      <x:c r="H199" s="82" t="str"/>
-      <x:c r="I199" s="82" t="str"/>
-      <x:c r="J199" s="82" t="str"/>
-      <x:c r="K199" s="141" t="str"/>
-    </x:row>
-    <x:row r="200">
-      <x:c r="A200" s="82" t="str"/>
-      <x:c r="B200" s="84" t="str"/>
-      <x:c r="C200" s="96" t="str"/>
-      <x:c r="D200" s="82" t="str"/>
-      <x:c r="E200" s="82" t="str"/>
-      <x:c r="F200" s="82" t="str"/>
-      <x:c r="G200" s="82" t="str"/>
-      <x:c r="H200" s="82" t="str"/>
-      <x:c r="I200" s="82" t="str"/>
-      <x:c r="J200" s="82" t="str"/>
-      <x:c r="K200" s="141" t="str"/>
-    </x:row>
-    <x:row r="201">
-      <x:c r="A201" s="82" t="str"/>
-      <x:c r="B201" s="84" t="str"/>
-      <x:c r="C201" s="96" t="str"/>
-      <x:c r="D201" s="82" t="str"/>
-      <x:c r="E201" s="82" t="str"/>
-      <x:c r="F201" s="82" t="str"/>
-      <x:c r="G201" s="82" t="str"/>
-      <x:c r="H201" s="82" t="str"/>
-      <x:c r="I201" s="82" t="str"/>
-      <x:c r="J201" s="82" t="str"/>
-      <x:c r="K201" s="141" t="str"/>
-    </x:row>
-    <x:row r="202">
-      <x:c r="A202" s="84"/>
-      <x:c r="B202" s="83"/>
-      <x:c r="C202" s="82"/>
-      <x:c r="D202" s="82"/>
-      <x:c r="E202" s="82"/>
-      <x:c r="F202" s="82"/>
-      <x:c r="G202" s="82"/>
-      <x:c r="H202" s="82"/>
-      <x:c r="I202" s="82"/>
-      <x:c r="J202" s="82"/>
-    </x:row>
-    <x:row r="203">
-      <x:c r="A203" s="84"/>
-      <x:c r="B203" s="83"/>
-      <x:c r="C203" s="82"/>
-      <x:c r="D203" s="82"/>
-      <x:c r="E203" s="82"/>
-      <x:c r="F203" s="82"/>
-      <x:c r="G203" s="82"/>
-      <x:c r="H203" s="82"/>
-      <x:c r="I203" s="82"/>
-      <x:c r="J203" s="82"/>
-    </x:row>
-    <x:row r="204">
-      <x:c r="A204" s="84"/>
-      <x:c r="B204" s="83"/>
-      <x:c r="C204" s="82"/>
-      <x:c r="D204" s="82"/>
-      <x:c r="E204" s="82"/>
-      <x:c r="F204" s="82"/>
-      <x:c r="G204" s="82"/>
-      <x:c r="H204" s="82"/>
-      <x:c r="I204" s="82"/>
-      <x:c r="J204" s="82"/>
-    </x:row>
-    <x:row r="205">
-      <x:c r="A205" s="84"/>
-      <x:c r="B205" s="83"/>
-      <x:c r="C205" s="82"/>
-      <x:c r="D205" s="82"/>
-      <x:c r="E205" s="82"/>
-      <x:c r="F205" s="82"/>
-      <x:c r="G205" s="82"/>
-      <x:c r="H205" s="82"/>
-      <x:c r="I205" s="82"/>
-      <x:c r="J205" s="82"/>
-    </x:row>
-    <x:row r="206">
-      <x:c r="A206" s="84"/>
-      <x:c r="B206" s="83"/>
-      <x:c r="C206" s="82"/>
-      <x:c r="D206" s="82"/>
-      <x:c r="E206" s="82"/>
-      <x:c r="F206" s="82"/>
-      <x:c r="G206" s="82"/>
-      <x:c r="H206" s="82"/>
-      <x:c r="I206" s="82"/>
-      <x:c r="J206" s="82"/>
-    </x:row>
-    <x:row r="207">
-      <x:c r="A207" s="84"/>
-      <x:c r="B207" s="83"/>
-      <x:c r="C207" s="82"/>
-      <x:c r="D207" s="82"/>
-      <x:c r="E207" s="82"/>
-      <x:c r="F207" s="82"/>
-      <x:c r="G207" s="82"/>
-      <x:c r="H207" s="82"/>
-      <x:c r="I207" s="82"/>
-      <x:c r="J207" s="82"/>
-    </x:row>
-    <x:row r="208">
-      <x:c r="A208" s="84"/>
-      <x:c r="B208" s="83"/>
-      <x:c r="C208" s="82"/>
-      <x:c r="D208" s="82"/>
-      <x:c r="E208" s="82"/>
-      <x:c r="F208" s="82"/>
-      <x:c r="G208" s="82"/>
-      <x:c r="H208" s="82"/>
-      <x:c r="I208" s="82"/>
-      <x:c r="J208" s="82"/>
-    </x:row>
-    <x:row r="209">
-      <x:c r="A209" s="84"/>
-      <x:c r="B209" s="83"/>
-      <x:c r="C209" s="82"/>
-      <x:c r="D209" s="82"/>
-      <x:c r="E209" s="82"/>
-      <x:c r="F209" s="82"/>
-      <x:c r="G209" s="82"/>
-      <x:c r="H209" s="82"/>
-      <x:c r="I209" s="82"/>
-      <x:c r="J209" s="82"/>
-    </x:row>
-    <x:row r="210">
-      <x:c r="A210" s="84"/>
-      <x:c r="B210" s="83"/>
-      <x:c r="C210" s="82"/>
-      <x:c r="D210" s="82"/>
-      <x:c r="E210" s="82"/>
-      <x:c r="F210" s="82"/>
-      <x:c r="G210" s="82"/>
-      <x:c r="H210" s="82"/>
-      <x:c r="I210" s="82"/>
-      <x:c r="J210" s="82"/>
-    </x:row>
-    <x:row r="211">
-      <x:c r="A211" s="84"/>
-      <x:c r="B211" s="83"/>
-      <x:c r="C211" s="82"/>
-      <x:c r="D211" s="82"/>
-      <x:c r="E211" s="82"/>
-      <x:c r="F211" s="82"/>
-      <x:c r="G211" s="82"/>
-      <x:c r="H211" s="82"/>
-      <x:c r="I211" s="82"/>
-      <x:c r="J211" s="82"/>
-    </x:row>
-    <x:row r="212">
-      <x:c r="A212" s="84"/>
-      <x:c r="B212" s="83"/>
-      <x:c r="C212" s="82"/>
-      <x:c r="D212" s="82"/>
-      <x:c r="E212" s="82"/>
-      <x:c r="F212" s="82"/>
-      <x:c r="G212" s="82"/>
-      <x:c r="H212" s="82"/>
-      <x:c r="I212" s="82"/>
-      <x:c r="J212" s="82"/>
-    </x:row>
-    <x:row r="213">
-      <x:c r="A213" s="84"/>
-      <x:c r="B213" s="83"/>
-      <x:c r="C213" s="82"/>
-      <x:c r="D213" s="82"/>
-      <x:c r="E213" s="82"/>
-      <x:c r="F213" s="82"/>
-      <x:c r="G213" s="82"/>
-      <x:c r="H213" s="82"/>
-      <x:c r="I213" s="82"/>
-      <x:c r="J213" s="82"/>
-    </x:row>
-    <x:row r="214">
-      <x:c r="A214" s="84"/>
-      <x:c r="B214" s="83"/>
-      <x:c r="C214" s="82"/>
-      <x:c r="D214" s="82"/>
-      <x:c r="E214" s="82"/>
-      <x:c r="F214" s="82"/>
-      <x:c r="G214" s="82"/>
-      <x:c r="H214" s="82"/>
-      <x:c r="I214" s="82"/>
-      <x:c r="J214" s="82"/>
-    </x:row>
-    <x:row r="215">
-      <x:c r="A215" s="84"/>
-      <x:c r="B215" s="83"/>
-      <x:c r="C215" s="82"/>
-      <x:c r="D215" s="82"/>
-      <x:c r="E215" s="82"/>
-      <x:c r="F215" s="82"/>
-      <x:c r="G215" s="82"/>
-      <x:c r="H215" s="82"/>
-      <x:c r="I215" s="82"/>
-      <x:c r="J215" s="82"/>
-    </x:row>
-    <x:row r="216">
-      <x:c r="A216" s="84"/>
-      <x:c r="B216" s="83"/>
-      <x:c r="C216" s="82"/>
-      <x:c r="D216" s="82"/>
-      <x:c r="E216" s="82"/>
-      <x:c r="F216" s="82"/>
-      <x:c r="G216" s="82"/>
-      <x:c r="H216" s="82"/>
-      <x:c r="I216" s="82"/>
-      <x:c r="J216" s="82"/>
-    </x:row>
-    <x:row r="217">
-      <x:c r="A217" s="84"/>
-      <x:c r="B217" s="83"/>
-      <x:c r="C217" s="82"/>
-      <x:c r="D217" s="82"/>
-      <x:c r="E217" s="82"/>
-      <x:c r="F217" s="82"/>
-      <x:c r="G217" s="82"/>
-      <x:c r="H217" s="82"/>
-      <x:c r="I217" s="82"/>
-      <x:c r="J217" s="82"/>
-    </x:row>
-    <x:row r="218">
-      <x:c r="A218" s="84"/>
-      <x:c r="B218" s="83"/>
-      <x:c r="C218" s="82"/>
-      <x:c r="D218" s="82"/>
-      <x:c r="E218" s="82"/>
-      <x:c r="F218" s="82"/>
-      <x:c r="G218" s="82"/>
-      <x:c r="H218" s="82"/>
-      <x:c r="I218" s="82"/>
-      <x:c r="J218" s="82"/>
-    </x:row>
-    <x:row r="219">
-      <x:c r="A219" s="84"/>
-      <x:c r="B219" s="83"/>
-      <x:c r="C219" s="82"/>
-      <x:c r="D219" s="82"/>
-      <x:c r="E219" s="82"/>
-      <x:c r="F219" s="82"/>
-      <x:c r="G219" s="82"/>
-      <x:c r="H219" s="82"/>
-      <x:c r="I219" s="82"/>
-      <x:c r="J219" s="82"/>
-    </x:row>
-    <x:row r="220">
-      <x:c r="A220" s="84"/>
-      <x:c r="B220" s="83"/>
-      <x:c r="C220" s="82"/>
-      <x:c r="D220" s="82"/>
-      <x:c r="E220" s="82"/>
-      <x:c r="F220" s="82"/>
-      <x:c r="G220" s="82"/>
-      <x:c r="H220" s="82"/>
-      <x:c r="I220" s="82"/>
-      <x:c r="J220" s="82"/>
-    </x:row>
-    <x:row r="221">
-      <x:c r="A221" s="84"/>
-      <x:c r="B221" s="83"/>
-      <x:c r="C221" s="82"/>
-      <x:c r="D221" s="82"/>
-      <x:c r="E221" s="82"/>
-      <x:c r="F221" s="82"/>
-      <x:c r="G221" s="82"/>
-      <x:c r="H221" s="82"/>
-      <x:c r="I221" s="82"/>
-      <x:c r="J221" s="82"/>
-    </x:row>
-    <x:row r="222">
-      <x:c r="A222" s="84"/>
-      <x:c r="B222" s="83"/>
-      <x:c r="C222" s="82"/>
-      <x:c r="D222" s="82"/>
-      <x:c r="E222" s="82"/>
-      <x:c r="F222" s="82"/>
-      <x:c r="G222" s="82"/>
-      <x:c r="H222" s="82"/>
-      <x:c r="I222" s="82"/>
-      <x:c r="J222" s="82"/>
-    </x:row>
-    <x:row r="223">
-      <x:c r="A223" s="84"/>
-      <x:c r="B223" s="83"/>
-      <x:c r="C223" s="82"/>
-      <x:c r="D223" s="82"/>
-      <x:c r="E223" s="82"/>
-      <x:c r="F223" s="82"/>
-      <x:c r="G223" s="82"/>
-      <x:c r="H223" s="82"/>
-      <x:c r="I223" s="82"/>
-      <x:c r="J223" s="82"/>
-    </x:row>
-    <x:row r="224">
-      <x:c r="A224" s="84"/>
-      <x:c r="B224" s="83"/>
-      <x:c r="C224" s="82"/>
-      <x:c r="D224" s="82"/>
-      <x:c r="E224" s="82"/>
-      <x:c r="F224" s="82"/>
-      <x:c r="G224" s="82"/>
-      <x:c r="H224" s="82"/>
-      <x:c r="I224" s="82"/>
-      <x:c r="J224" s="82"/>
-    </x:row>
-    <x:row r="225">
-      <x:c r="A225" s="84"/>
-      <x:c r="B225" s="83"/>
-      <x:c r="C225" s="82"/>
-      <x:c r="D225" s="82"/>
-      <x:c r="E225" s="82"/>
-      <x:c r="F225" s="82"/>
-      <x:c r="G225" s="82"/>
-      <x:c r="H225" s="82"/>
-      <x:c r="I225" s="82"/>
-      <x:c r="J225" s="82"/>
-    </x:row>
-    <x:row r="226">
-      <x:c r="A226" s="84"/>
-      <x:c r="B226" s="83"/>
-      <x:c r="C226" s="82"/>
-      <x:c r="D226" s="82"/>
-      <x:c r="E226" s="82"/>
-      <x:c r="F226" s="82"/>
-      <x:c r="G226" s="82"/>
-      <x:c r="H226" s="82"/>
-      <x:c r="I226" s="82"/>
-      <x:c r="J226" s="82"/>
-    </x:row>
-    <x:row r="227">
-      <x:c r="A227" s="84"/>
-      <x:c r="B227" s="83"/>
-      <x:c r="C227" s="82"/>
-      <x:c r="D227" s="82"/>
-      <x:c r="E227" s="82"/>
-      <x:c r="F227" s="82"/>
-      <x:c r="G227" s="82"/>
-      <x:c r="H227" s="82"/>
-      <x:c r="I227" s="82"/>
-      <x:c r="J227" s="82"/>
-    </x:row>
-    <x:row r="228">
-      <x:c r="A228" s="84"/>
-      <x:c r="B228" s="83"/>
-      <x:c r="C228" s="82"/>
-      <x:c r="D228" s="82"/>
-      <x:c r="E228" s="82"/>
-      <x:c r="F228" s="82"/>
-      <x:c r="G228" s="82"/>
-      <x:c r="H228" s="82"/>
-      <x:c r="I228" s="82"/>
-      <x:c r="J228" s="82"/>
-    </x:row>
-    <x:row r="229">
-      <x:c r="A229" s="84"/>
-      <x:c r="B229" s="83"/>
-      <x:c r="C229" s="82"/>
-      <x:c r="D229" s="82"/>
-      <x:c r="E229" s="82"/>
-      <x:c r="F229" s="82"/>
-      <x:c r="G229" s="82"/>
-      <x:c r="H229" s="82"/>
-      <x:c r="I229" s="82"/>
-      <x:c r="J229" s="82"/>
-    </x:row>
-    <x:row r="230">
-      <x:c r="A230" s="84"/>
-      <x:c r="B230" s="83"/>
-      <x:c r="C230" s="82"/>
-      <x:c r="D230" s="82"/>
-      <x:c r="E230" s="82"/>
-      <x:c r="F230" s="82"/>
-      <x:c r="G230" s="82"/>
-      <x:c r="H230" s="82"/>
-      <x:c r="I230" s="82"/>
-      <x:c r="J230" s="82"/>
-    </x:row>
-    <x:row r="231">
-      <x:c r="A231" s="84"/>
-      <x:c r="B231" s="83"/>
-      <x:c r="C231" s="82"/>
-      <x:c r="D231" s="82"/>
-      <x:c r="E231" s="82"/>
-      <x:c r="F231" s="82"/>
-      <x:c r="G231" s="82"/>
-      <x:c r="H231" s="82"/>
-      <x:c r="I231" s="82"/>
-      <x:c r="J231" s="82"/>
-    </x:row>
-    <x:row r="232">
-      <x:c r="A232" s="84"/>
-      <x:c r="B232" s="83"/>
-      <x:c r="C232" s="82"/>
-      <x:c r="D232" s="82"/>
-      <x:c r="E232" s="82"/>
-      <x:c r="F232" s="82"/>
-      <x:c r="G232" s="82"/>
-      <x:c r="H232" s="82"/>
-      <x:c r="I232" s="82"/>
-      <x:c r="J232" s="82"/>
-    </x:row>
-    <x:row r="233">
-      <x:c r="A233" s="84"/>
-      <x:c r="B233" s="83"/>
-      <x:c r="C233" s="82"/>
-      <x:c r="D233" s="82"/>
-      <x:c r="E233" s="82"/>
-      <x:c r="F233" s="82"/>
-      <x:c r="G233" s="82"/>
-      <x:c r="H233" s="82"/>
-      <x:c r="I233" s="82"/>
-      <x:c r="J233" s="82"/>
-    </x:row>
-    <x:row r="234">
-      <x:c r="A234" s="84"/>
-      <x:c r="B234" s="83"/>
-      <x:c r="C234" s="82"/>
-      <x:c r="D234" s="82"/>
-      <x:c r="E234" s="82"/>
-      <x:c r="F234" s="82"/>
-      <x:c r="G234" s="82"/>
-      <x:c r="H234" s="82"/>
-      <x:c r="I234" s="82"/>
-      <x:c r="J234" s="82"/>
-    </x:row>
-    <x:row r="235">
-      <x:c r="A235" s="84"/>
-      <x:c r="B235" s="83"/>
-      <x:c r="C235" s="82"/>
-      <x:c r="D235" s="82"/>
-      <x:c r="E235" s="82"/>
-      <x:c r="F235" s="82"/>
-      <x:c r="G235" s="82"/>
-      <x:c r="H235" s="82"/>
-      <x:c r="I235" s="82"/>
-      <x:c r="J235" s="82"/>
-    </x:row>
-    <x:row r="236">
-      <x:c r="A236" s="84"/>
-      <x:c r="B236" s="83"/>
-      <x:c r="C236" s="82"/>
-      <x:c r="D236" s="82"/>
-      <x:c r="E236" s="82"/>
-      <x:c r="F236" s="82"/>
-      <x:c r="G236" s="82"/>
-      <x:c r="H236" s="82"/>
-      <x:c r="I236" s="82"/>
-      <x:c r="J236" s="82"/>
-    </x:row>
-    <x:row r="237">
-      <x:c r="A237" s="84"/>
-      <x:c r="B237" s="83"/>
-      <x:c r="C237" s="82"/>
-      <x:c r="D237" s="82"/>
-      <x:c r="E237" s="82"/>
-      <x:c r="F237" s="82"/>
-      <x:c r="G237" s="82"/>
-      <x:c r="H237" s="82"/>
-      <x:c r="I237" s="82"/>
-      <x:c r="J237" s="82"/>
-    </x:row>
-    <x:row r="238">
-      <x:c r="A238" s="84"/>
-      <x:c r="B238" s="83"/>
-      <x:c r="C238" s="82"/>
-      <x:c r="D238" s="82"/>
-      <x:c r="E238" s="82"/>
-      <x:c r="F238" s="82"/>
-      <x:c r="G238" s="82"/>
-      <x:c r="H238" s="82"/>
-      <x:c r="I238" s="82"/>
-      <x:c r="J238" s="82"/>
-    </x:row>
-    <x:row r="239">
-      <x:c r="A239" s="84"/>
-      <x:c r="B239" s="83"/>
-      <x:c r="C239" s="82"/>
-      <x:c r="D239" s="82"/>
-      <x:c r="E239" s="82"/>
-      <x:c r="F239" s="82"/>
-      <x:c r="G239" s="82"/>
-      <x:c r="H239" s="82"/>
-      <x:c r="I239" s="82"/>
-      <x:c r="J239" s="82"/>
-    </x:row>
-    <x:row r="240">
-      <x:c r="A240" s="84"/>
-      <x:c r="B240" s="83"/>
-      <x:c r="C240" s="82"/>
-      <x:c r="D240" s="82"/>
-      <x:c r="E240" s="82"/>
-      <x:c r="F240" s="82"/>
-      <x:c r="G240" s="82"/>
-      <x:c r="H240" s="82"/>
-      <x:c r="I240" s="82"/>
-      <x:c r="J240" s="82"/>
-    </x:row>
-    <x:row r="241">
-      <x:c r="A241" s="84"/>
-      <x:c r="B241" s="83"/>
-      <x:c r="C241" s="82"/>
-      <x:c r="D241" s="82"/>
-      <x:c r="E241" s="82"/>
-      <x:c r="F241" s="82"/>
-      <x:c r="G241" s="82"/>
-      <x:c r="H241" s="82"/>
-      <x:c r="I241" s="82"/>
-      <x:c r="J241" s="82"/>
-    </x:row>
-    <x:row r="242">
-      <x:c r="A242" s="84"/>
-      <x:c r="B242" s="83"/>
-      <x:c r="C242" s="82"/>
-      <x:c r="D242" s="82"/>
-      <x:c r="E242" s="82"/>
-      <x:c r="F242" s="82"/>
-      <x:c r="G242" s="82"/>
-      <x:c r="H242" s="82"/>
-      <x:c r="I242" s="82"/>
-      <x:c r="J242" s="82"/>
-    </x:row>
-    <x:row r="243">
-      <x:c r="A243" s="84"/>
-      <x:c r="B243" s="83"/>
-      <x:c r="C243" s="82"/>
-      <x:c r="D243" s="82"/>
-      <x:c r="E243" s="82"/>
-      <x:c r="F243" s="82"/>
-      <x:c r="G243" s="82"/>
-      <x:c r="H243" s="82"/>
-      <x:c r="I243" s="82"/>
-      <x:c r="J243" s="82"/>
-    </x:row>
-    <x:row r="244">
-      <x:c r="A244" s="84"/>
-      <x:c r="B244" s="83"/>
-      <x:c r="C244" s="82"/>
-      <x:c r="D244" s="82"/>
-      <x:c r="E244" s="82"/>
-      <x:c r="F244" s="82"/>
-      <x:c r="G244" s="82"/>
-      <x:c r="H244" s="82"/>
-      <x:c r="I244" s="82"/>
-      <x:c r="J244" s="82"/>
-    </x:row>
-    <x:row r="245">
-      <x:c r="A245" s="84"/>
-      <x:c r="B245" s="83"/>
-      <x:c r="C245" s="82"/>
-      <x:c r="D245" s="82"/>
-      <x:c r="E245" s="82"/>
-      <x:c r="F245" s="82"/>
-      <x:c r="G245" s="82"/>
-      <x:c r="H245" s="82"/>
-      <x:c r="I245" s="82"/>
-      <x:c r="J245" s="82"/>
-    </x:row>
-    <x:row r="246">
-      <x:c r="A246" s="84"/>
-      <x:c r="B246" s="83"/>
-      <x:c r="C246" s="82"/>
-      <x:c r="D246" s="82"/>
-      <x:c r="E246" s="82"/>
-      <x:c r="F246" s="82"/>
-      <x:c r="G246" s="82"/>
-      <x:c r="H246" s="82"/>
-      <x:c r="I246" s="82"/>
-      <x:c r="J246" s="82"/>
-    </x:row>
-    <x:row r="247">
-      <x:c r="A247" s="84"/>
-      <x:c r="B247" s="83"/>
-      <x:c r="C247" s="82"/>
-      <x:c r="D247" s="82"/>
-      <x:c r="E247" s="82"/>
-      <x:c r="F247" s="82"/>
-      <x:c r="G247" s="82"/>
-      <x:c r="H247" s="82"/>
-      <x:c r="I247" s="82"/>
-      <x:c r="J247" s="82"/>
-    </x:row>
-    <x:row r="248">
-      <x:c r="A248" s="84"/>
-      <x:c r="B248" s="83"/>
-      <x:c r="C248" s="82"/>
-      <x:c r="D248" s="82"/>
-      <x:c r="E248" s="82"/>
-      <x:c r="F248" s="82"/>
-      <x:c r="G248" s="82"/>
-      <x:c r="H248" s="82"/>
-      <x:c r="I248" s="82"/>
-      <x:c r="J248" s="82"/>
-    </x:row>
-    <x:row r="249">
-      <x:c r="A249" s="84"/>
-      <x:c r="B249" s="83"/>
-      <x:c r="C249" s="82"/>
-      <x:c r="D249" s="82"/>
-      <x:c r="E249" s="82"/>
-      <x:c r="F249" s="82"/>
-      <x:c r="G249" s="82"/>
-      <x:c r="H249" s="82"/>
-      <x:c r="I249" s="82"/>
-      <x:c r="J249" s="82"/>
-    </x:row>
-    <x:row r="250">
-      <x:c r="A250" s="84"/>
-      <x:c r="B250" s="83"/>
-      <x:c r="C250" s="82"/>
-      <x:c r="D250" s="82"/>
-      <x:c r="E250" s="82"/>
-      <x:c r="F250" s="82"/>
-      <x:c r="G250" s="82"/>
-      <x:c r="H250" s="82"/>
-      <x:c r="I250" s="82"/>
-      <x:c r="J250" s="82"/>
-    </x:row>
-    <x:row r="251">
-      <x:c r="A251" s="84"/>
-      <x:c r="B251" s="83"/>
-      <x:c r="C251" s="82"/>
-      <x:c r="D251" s="82"/>
-      <x:c r="E251" s="82"/>
-      <x:c r="F251" s="82"/>
-      <x:c r="G251" s="82"/>
-      <x:c r="H251" s="82"/>
-      <x:c r="I251" s="82"/>
-      <x:c r="J251" s="82"/>
-    </x:row>
-    <x:row r="252">
-      <x:c r="A252" s="84"/>
-      <x:c r="B252" s="83"/>
-      <x:c r="C252" s="82"/>
-      <x:c r="D252" s="82"/>
-      <x:c r="E252" s="82"/>
-      <x:c r="F252" s="82"/>
-      <x:c r="G252" s="82"/>
-      <x:c r="H252" s="82"/>
-      <x:c r="I252" s="82"/>
-      <x:c r="J252" s="82"/>
-    </x:row>
-    <x:row r="253">
-      <x:c r="A253" s="84"/>
-      <x:c r="B253" s="83"/>
-      <x:c r="C253" s="82"/>
-      <x:c r="D253" s="82"/>
-      <x:c r="E253" s="82"/>
-      <x:c r="F253" s="82"/>
-      <x:c r="G253" s="82"/>
-      <x:c r="H253" s="82"/>
-      <x:c r="I253" s="82"/>
-      <x:c r="J253" s="82"/>
-    </x:row>
-    <x:row r="254">
-      <x:c r="A254" s="84"/>
-      <x:c r="B254" s="83"/>
-      <x:c r="C254" s="82"/>
-      <x:c r="D254" s="82"/>
-      <x:c r="E254" s="82"/>
-      <x:c r="F254" s="82"/>
-      <x:c r="G254" s="82"/>
-      <x:c r="H254" s="82"/>
-      <x:c r="I254" s="82"/>
-      <x:c r="J254" s="82"/>
-    </x:row>
-    <x:row r="255">
-      <x:c r="A255" s="84"/>
-      <x:c r="B255" s="83"/>
-      <x:c r="C255" s="82"/>
-      <x:c r="D255" s="82"/>
-      <x:c r="E255" s="82"/>
-      <x:c r="F255" s="82"/>
-      <x:c r="G255" s="82"/>
-      <x:c r="H255" s="82"/>
-      <x:c r="I255" s="82"/>
-      <x:c r="J255" s="82"/>
-    </x:row>
-    <x:row r="256">
-      <x:c r="A256" s="84"/>
-      <x:c r="B256" s="83"/>
-      <x:c r="C256" s="82"/>
-      <x:c r="D256" s="82"/>
-      <x:c r="E256" s="82"/>
-      <x:c r="F256" s="82"/>
-      <x:c r="G256" s="82"/>
-      <x:c r="H256" s="82"/>
-      <x:c r="I256" s="82"/>
-      <x:c r="J256" s="82"/>
-    </x:row>
-    <x:row r="257">
-      <x:c r="A257" s="84"/>
-      <x:c r="B257" s="83"/>
-      <x:c r="C257" s="82"/>
-      <x:c r="D257" s="82"/>
-      <x:c r="E257" s="82"/>
-      <x:c r="F257" s="82"/>
-      <x:c r="G257" s="82"/>
-      <x:c r="H257" s="82"/>
-      <x:c r="I257" s="82"/>
-      <x:c r="J257" s="82"/>
-    </x:row>
-    <x:row r="258">
-      <x:c r="A258" s="84"/>
-      <x:c r="B258" s="83"/>
-      <x:c r="C258" s="82"/>
-      <x:c r="D258" s="82"/>
-      <x:c r="E258" s="82"/>
-      <x:c r="F258" s="82"/>
-      <x:c r="G258" s="82"/>
-      <x:c r="H258" s="82"/>
-      <x:c r="I258" s="82"/>
-      <x:c r="J258" s="82"/>
-    </x:row>
-    <x:row r="259">
-      <x:c r="A259" s="84"/>
-      <x:c r="B259" s="83"/>
-      <x:c r="C259" s="82"/>
-      <x:c r="D259" s="82"/>
-      <x:c r="E259" s="82"/>
-      <x:c r="F259" s="82"/>
-      <x:c r="G259" s="82"/>
-      <x:c r="H259" s="82"/>
-      <x:c r="I259" s="82"/>
-      <x:c r="J259" s="82"/>
-    </x:row>
-    <x:row r="260">
-      <x:c r="A260" s="84"/>
-      <x:c r="B260" s="83"/>
-      <x:c r="C260" s="82"/>
-      <x:c r="D260" s="82"/>
-      <x:c r="E260" s="82"/>
-      <x:c r="F260" s="82"/>
-      <x:c r="G260" s="82"/>
-      <x:c r="H260" s="82"/>
-      <x:c r="I260" s="82"/>
-      <x:c r="J260" s="82"/>
-    </x:row>
-    <x:row r="261">
-      <x:c r="A261" s="84"/>
-      <x:c r="B261" s="83"/>
-      <x:c r="C261" s="82"/>
-      <x:c r="D261" s="82"/>
-      <x:c r="E261" s="82"/>
-      <x:c r="F261" s="82"/>
-      <x:c r="G261" s="82"/>
-      <x:c r="H261" s="82"/>
-      <x:c r="I261" s="82"/>
-      <x:c r="J261" s="82"/>
-    </x:row>
-    <x:row r="262">
-      <x:c r="A262" s="84"/>
-      <x:c r="B262" s="83"/>
-      <x:c r="C262" s="82"/>
-      <x:c r="D262" s="82"/>
-      <x:c r="E262" s="82"/>
-      <x:c r="F262" s="82"/>
-      <x:c r="G262" s="82"/>
-      <x:c r="H262" s="82"/>
-      <x:c r="I262" s="82"/>
-      <x:c r="J262" s="82"/>
-    </x:row>
-    <x:row r="263">
-      <x:c r="A263" s="84"/>
-      <x:c r="B263" s="83"/>
-      <x:c r="C263" s="82"/>
-      <x:c r="D263" s="82"/>
-      <x:c r="E263" s="82"/>
-      <x:c r="F263" s="82"/>
-      <x:c r="G263" s="82"/>
-      <x:c r="H263" s="82"/>
-      <x:c r="I263" s="82"/>
-      <x:c r="J263" s="82"/>
-    </x:row>
-    <x:row r="264">
-      <x:c r="A264" s="84"/>
-      <x:c r="B264" s="83"/>
-      <x:c r="C264" s="82"/>
-      <x:c r="D264" s="82"/>
-      <x:c r="E264" s="82"/>
-      <x:c r="F264" s="82"/>
-      <x:c r="G264" s="82"/>
-      <x:c r="H264" s="82"/>
-      <x:c r="I264" s="82"/>
-      <x:c r="J264" s="82"/>
-    </x:row>
-    <x:row r="265">
-      <x:c r="A265" s="84"/>
-      <x:c r="B265" s="83"/>
-      <x:c r="C265" s="82"/>
-      <x:c r="D265" s="82"/>
-      <x:c r="E265" s="82"/>
-      <x:c r="F265" s="82"/>
-      <x:c r="G265" s="82"/>
-      <x:c r="H265" s="82"/>
-      <x:c r="I265" s="82"/>
-      <x:c r="J265" s="82"/>
-    </x:row>
-    <x:row r="266">
-      <x:c r="A266" s="84"/>
-      <x:c r="B266" s="83"/>
-      <x:c r="C266" s="82"/>
-      <x:c r="D266" s="82"/>
-      <x:c r="E266" s="82"/>
-      <x:c r="F266" s="82"/>
-      <x:c r="G266" s="82"/>
-      <x:c r="H266" s="82"/>
-      <x:c r="I266" s="82"/>
-      <x:c r="J266" s="82"/>
-    </x:row>
-    <x:row r="267">
-      <x:c r="A267" s="84"/>
-      <x:c r="B267" s="83"/>
-      <x:c r="C267" s="82"/>
-      <x:c r="D267" s="82"/>
-      <x:c r="E267" s="82"/>
-      <x:c r="F267" s="82"/>
-      <x:c r="G267" s="82"/>
-      <x:c r="H267" s="82"/>
-      <x:c r="I267" s="82"/>
-      <x:c r="J267" s="82"/>
-    </x:row>
-    <x:row r="268">
-      <x:c r="A268" s="84"/>
-      <x:c r="B268" s="83"/>
-      <x:c r="C268" s="82"/>
-      <x:c r="D268" s="82"/>
-      <x:c r="E268" s="82"/>
-      <x:c r="F268" s="82"/>
-      <x:c r="G268" s="82"/>
-      <x:c r="H268" s="82"/>
-      <x:c r="I268" s="82"/>
-      <x:c r="J268" s="82"/>
-    </x:row>
-    <x:row r="269">
-      <x:c r="A269" s="84"/>
-      <x:c r="B269" s="83"/>
-      <x:c r="C269" s="82"/>
-      <x:c r="D269" s="82"/>
-      <x:c r="E269" s="82"/>
-      <x:c r="F269" s="82"/>
-      <x:c r="G269" s="82"/>
-      <x:c r="H269" s="82"/>
-      <x:c r="I269" s="82"/>
-      <x:c r="J269" s="82"/>
-    </x:row>
-    <x:row r="270">
-      <x:c r="A270" s="84"/>
-      <x:c r="B270" s="83"/>
-      <x:c r="C270" s="82"/>
-      <x:c r="D270" s="82"/>
-      <x:c r="E270" s="82"/>
-      <x:c r="F270" s="82"/>
-      <x:c r="G270" s="82"/>
-      <x:c r="H270" s="82"/>
-      <x:c r="I270" s="82"/>
-      <x:c r="J270" s="82"/>
-    </x:row>
-    <x:row r="271">
-      <x:c r="A271" s="84"/>
-      <x:c r="B271" s="83"/>
-      <x:c r="C271" s="82"/>
-      <x:c r="D271" s="82"/>
-      <x:c r="E271" s="82"/>
-      <x:c r="F271" s="82"/>
-      <x:c r="G271" s="82"/>
-      <x:c r="H271" s="82"/>
-      <x:c r="I271" s="82"/>
-      <x:c r="J271" s="82"/>
-    </x:row>
-    <x:row r="272">
-      <x:c r="A272" s="84"/>
-      <x:c r="B272" s="83"/>
-      <x:c r="C272" s="82"/>
-      <x:c r="D272" s="82"/>
-      <x:c r="E272" s="82"/>
-      <x:c r="F272" s="82"/>
-      <x:c r="G272" s="82"/>
-      <x:c r="H272" s="82"/>
-      <x:c r="I272" s="82"/>
-      <x:c r="J272" s="82"/>
-    </x:row>
-    <x:row r="273">
-      <x:c r="A273" s="84"/>
-      <x:c r="B273" s="83"/>
-      <x:c r="C273" s="82"/>
-      <x:c r="D273" s="82"/>
-      <x:c r="E273" s="82"/>
-      <x:c r="F273" s="82"/>
-      <x:c r="G273" s="82"/>
-      <x:c r="H273" s="82"/>
-      <x:c r="I273" s="82"/>
-      <x:c r="J273" s="82"/>
-    </x:row>
-    <x:row r="274">
-      <x:c r="A274" s="84"/>
-      <x:c r="B274" s="83"/>
-      <x:c r="C274" s="82"/>
-      <x:c r="D274" s="82"/>
-      <x:c r="E274" s="82"/>
-      <x:c r="F274" s="82"/>
-      <x:c r="G274" s="82"/>
-      <x:c r="H274" s="82"/>
-      <x:c r="I274" s="82"/>
-      <x:c r="J274" s="82"/>
-    </x:row>
-    <x:row r="275">
-      <x:c r="A275" s="84"/>
-      <x:c r="B275" s="83"/>
-      <x:c r="C275" s="82"/>
-      <x:c r="D275" s="82"/>
-      <x:c r="E275" s="82"/>
-      <x:c r="F275" s="82"/>
-      <x:c r="G275" s="82"/>
-      <x:c r="H275" s="82"/>
-      <x:c r="I275" s="82"/>
-      <x:c r="J275" s="82"/>
-    </x:row>
-    <x:row r="276">
-      <x:c r="A276" s="84"/>
-      <x:c r="B276" s="83"/>
-      <x:c r="C276" s="82"/>
-      <x:c r="D276" s="82"/>
-      <x:c r="E276" s="82"/>
-      <x:c r="F276" s="82"/>
-      <x:c r="G276" s="82"/>
-      <x:c r="H276" s="82"/>
-      <x:c r="I276" s="82"/>
-      <x:c r="J276" s="82"/>
-    </x:row>
-    <x:row r="277">
-      <x:c r="A277" s="84"/>
-      <x:c r="B277" s="83"/>
-      <x:c r="C277" s="82"/>
-      <x:c r="D277" s="82"/>
-      <x:c r="E277" s="82"/>
-      <x:c r="F277" s="82"/>
-      <x:c r="G277" s="82"/>
-      <x:c r="H277" s="82"/>
-      <x:c r="I277" s="82"/>
-      <x:c r="J277" s="82"/>
-    </x:row>
-    <x:row r="278">
-      <x:c r="A278" s="84"/>
-      <x:c r="B278" s="83"/>
-      <x:c r="C278" s="82"/>
-      <x:c r="D278" s="82"/>
-      <x:c r="E278" s="82"/>
-      <x:c r="F278" s="82"/>
-      <x:c r="G278" s="82"/>
-      <x:c r="H278" s="82"/>
-      <x:c r="I278" s="82"/>
-      <x:c r="J278" s="82"/>
-    </x:row>
-    <x:row r="279">
-      <x:c r="A279" s="84"/>
-      <x:c r="B279" s="83"/>
-      <x:c r="C279" s="82"/>
-      <x:c r="D279" s="82"/>
-      <x:c r="E279" s="82"/>
-      <x:c r="F279" s="82"/>
-      <x:c r="G279" s="82"/>
-      <x:c r="H279" s="82"/>
-      <x:c r="I279" s="82"/>
-      <x:c r="J279" s="82"/>
-    </x:row>
-    <x:row r="280">
-      <x:c r="A280" s="84"/>
-      <x:c r="B280" s="83"/>
-      <x:c r="C280" s="82"/>
-      <x:c r="D280" s="82"/>
-      <x:c r="E280" s="82"/>
-      <x:c r="F280" s="82"/>
-      <x:c r="G280" s="82"/>
-      <x:c r="H280" s="82"/>
-      <x:c r="I280" s="82"/>
-      <x:c r="J280" s="82"/>
-    </x:row>
-    <x:row r="281">
-      <x:c r="A281" s="84"/>
-      <x:c r="B281" s="83"/>
-      <x:c r="C281" s="82"/>
-      <x:c r="D281" s="82"/>
-      <x:c r="E281" s="82"/>
-      <x:c r="F281" s="82"/>
-      <x:c r="G281" s="82"/>
-      <x:c r="H281" s="82"/>
-      <x:c r="I281" s="82"/>
-      <x:c r="J281" s="82"/>
-    </x:row>
-    <x:row r="282">
-      <x:c r="A282" s="84"/>
-      <x:c r="B282" s="83"/>
-      <x:c r="C282" s="82"/>
-      <x:c r="D282" s="82"/>
-      <x:c r="E282" s="82"/>
-      <x:c r="F282" s="82"/>
-      <x:c r="G282" s="82"/>
-      <x:c r="H282" s="82"/>
-      <x:c r="I282" s="82"/>
-      <x:c r="J282" s="82"/>
-    </x:row>
-    <x:row r="283">
-      <x:c r="A283" s="84"/>
-      <x:c r="B283" s="83"/>
-      <x:c r="C283" s="82"/>
-      <x:c r="D283" s="82"/>
-      <x:c r="E283" s="82"/>
-      <x:c r="F283" s="82"/>
-      <x:c r="G283" s="82"/>
-      <x:c r="H283" s="82"/>
-      <x:c r="I283" s="82"/>
-      <x:c r="J283" s="82"/>
-    </x:row>
-    <x:row r="284">
-      <x:c r="A284" s="84"/>
-      <x:c r="B284" s="83"/>
-      <x:c r="C284" s="82"/>
-      <x:c r="D284" s="82"/>
-      <x:c r="E284" s="82"/>
-      <x:c r="F284" s="82"/>
-      <x:c r="G284" s="82"/>
-      <x:c r="H284" s="82"/>
-      <x:c r="I284" s="82"/>
-      <x:c r="J284" s="82"/>
-    </x:row>
-    <x:row r="285">
-      <x:c r="A285" s="84"/>
-      <x:c r="B285" s="83"/>
-      <x:c r="C285" s="82"/>
-      <x:c r="D285" s="82"/>
-      <x:c r="E285" s="82"/>
-      <x:c r="F285" s="82"/>
-      <x:c r="G285" s="82"/>
-      <x:c r="H285" s="82"/>
-      <x:c r="I285" s="82"/>
-      <x:c r="J285" s="82"/>
-    </x:row>
-    <x:row r="286">
-      <x:c r="A286" s="84"/>
-      <x:c r="B286" s="83"/>
-      <x:c r="C286" s="82"/>
-      <x:c r="D286" s="82"/>
-      <x:c r="E286" s="82"/>
-      <x:c r="F286" s="82"/>
-      <x:c r="G286" s="82"/>
-      <x:c r="H286" s="82"/>
-      <x:c r="I286" s="82"/>
-      <x:c r="J286" s="82"/>
-    </x:row>
-    <x:row r="287">
-      <x:c r="A287" s="84"/>
-      <x:c r="B287" s="83"/>
-      <x:c r="C287" s="82"/>
-      <x:c r="D287" s="82"/>
-      <x:c r="E287" s="82"/>
-      <x:c r="F287" s="82"/>
-      <x:c r="G287" s="82"/>
-      <x:c r="H287" s="82"/>
-      <x:c r="I287" s="82"/>
-      <x:c r="J287" s="82"/>
-    </x:row>
-    <x:row r="288">
-      <x:c r="A288" s="84"/>
-      <x:c r="B288" s="83"/>
-      <x:c r="C288" s="82"/>
-      <x:c r="D288" s="82"/>
-      <x:c r="E288" s="82"/>
-      <x:c r="F288" s="82"/>
-      <x:c r="G288" s="82"/>
-      <x:c r="H288" s="82"/>
-      <x:c r="I288" s="82"/>
-      <x:c r="J288" s="82"/>
-    </x:row>
-    <x:row r="289">
-      <x:c r="A289" s="84"/>
-      <x:c r="B289" s="83"/>
-      <x:c r="C289" s="82"/>
-      <x:c r="D289" s="82"/>
-      <x:c r="E289" s="82"/>
-      <x:c r="F289" s="82"/>
-      <x:c r="G289" s="82"/>
-      <x:c r="H289" s="82"/>
-      <x:c r="I289" s="82"/>
-      <x:c r="J289" s="82"/>
-    </x:row>
-    <x:row r="290">
-      <x:c r="A290" s="84"/>
-      <x:c r="B290" s="83"/>
-      <x:c r="C290" s="82"/>
-      <x:c r="D290" s="82"/>
-      <x:c r="E290" s="82"/>
-      <x:c r="F290" s="82"/>
-      <x:c r="G290" s="82"/>
-      <x:c r="H290" s="82"/>
-      <x:c r="I290" s="82"/>
-      <x:c r="J290" s="82"/>
-    </x:row>
-    <x:row r="291">
-      <x:c r="A291" s="84"/>
-      <x:c r="B291" s="83"/>
-      <x:c r="C291" s="82"/>
-      <x:c r="D291" s="82"/>
-      <x:c r="E291" s="82"/>
-      <x:c r="F291" s="82"/>
-      <x:c r="G291" s="82"/>
-      <x:c r="H291" s="82"/>
-      <x:c r="I291" s="82"/>
-      <x:c r="J291" s="82"/>
-    </x:row>
-    <x:row r="292">
-      <x:c r="A292" s="84"/>
-      <x:c r="B292" s="83"/>
-      <x:c r="C292" s="82"/>
-      <x:c r="D292" s="82"/>
-      <x:c r="E292" s="82"/>
-      <x:c r="F292" s="82"/>
-      <x:c r="G292" s="82"/>
-      <x:c r="H292" s="82"/>
-      <x:c r="I292" s="82"/>
-      <x:c r="J292" s="82"/>
-    </x:row>
-    <x:row r="293">
-      <x:c r="A293" s="84"/>
-      <x:c r="B293" s="83"/>
-      <x:c r="C293" s="82"/>
-      <x:c r="D293" s="82"/>
-      <x:c r="E293" s="82"/>
-      <x:c r="F293" s="82"/>
-      <x:c r="G293" s="82"/>
-      <x:c r="H293" s="82"/>
-      <x:c r="I293" s="82"/>
-      <x:c r="J293" s="82"/>
-    </x:row>
-    <x:row r="294">
-      <x:c r="A294" s="84"/>
-      <x:c r="B294" s="83"/>
-      <x:c r="C294" s="82"/>
-      <x:c r="D294" s="82"/>
-      <x:c r="E294" s="82"/>
-      <x:c r="F294" s="82"/>
-      <x:c r="G294" s="82"/>
-      <x:c r="H294" s="82"/>
-      <x:c r="I294" s="82"/>
-      <x:c r="J294" s="82"/>
-    </x:row>
-    <x:row r="295">
-      <x:c r="A295" s="84"/>
-      <x:c r="B295" s="83"/>
-      <x:c r="C295" s="82"/>
-      <x:c r="D295" s="82"/>
-      <x:c r="E295" s="82"/>
-      <x:c r="F295" s="82"/>
-      <x:c r="G295" s="82"/>
-      <x:c r="H295" s="82"/>
-      <x:c r="I295" s="82"/>
-      <x:c r="J295" s="82"/>
-    </x:row>
-    <x:row r="296">
-      <x:c r="A296" s="84"/>
-      <x:c r="B296" s="83"/>
-      <x:c r="C296" s="82"/>
-      <x:c r="D296" s="82"/>
-      <x:c r="E296" s="82"/>
-      <x:c r="F296" s="82"/>
-      <x:c r="G296" s="82"/>
-      <x:c r="H296" s="82"/>
-      <x:c r="I296" s="82"/>
-      <x:c r="J296" s="82"/>
-    </x:row>
-    <x:row r="297">
-      <x:c r="A297" s="84"/>
-      <x:c r="B297" s="83"/>
-      <x:c r="C297" s="82"/>
-      <x:c r="D297" s="82"/>
-      <x:c r="E297" s="82"/>
-      <x:c r="F297" s="82"/>
-      <x:c r="G297" s="82"/>
-      <x:c r="H297" s="82"/>
-      <x:c r="I297" s="82"/>
-      <x:c r="J297" s="82"/>
-    </x:row>
-    <x:row r="298">
-      <x:c r="A298" s="84"/>
-      <x:c r="B298" s="83"/>
-      <x:c r="C298" s="82"/>
-      <x:c r="D298" s="82"/>
-      <x:c r="E298" s="82"/>
-      <x:c r="F298" s="82"/>
-      <x:c r="G298" s="82"/>
-      <x:c r="H298" s="82"/>
-      <x:c r="I298" s="82"/>
-      <x:c r="J298" s="82"/>
-    </x:row>
-    <x:row r="299">
-      <x:c r="A299" s="84"/>
-      <x:c r="B299" s="83"/>
-      <x:c r="C299" s="82"/>
-      <x:c r="D299" s="82"/>
-      <x:c r="E299" s="82"/>
-      <x:c r="F299" s="82"/>
-      <x:c r="G299" s="82"/>
-      <x:c r="H299" s="82"/>
-      <x:c r="I299" s="82"/>
-      <x:c r="J299" s="82"/>
-    </x:row>
-    <x:row r="300">
-      <x:c r="A300" s="84"/>
-      <x:c r="B300" s="83"/>
-      <x:c r="C300" s="82"/>
-      <x:c r="D300" s="82"/>
-      <x:c r="E300" s="82"/>
-      <x:c r="F300" s="82"/>
-      <x:c r="G300" s="82"/>
-      <x:c r="H300" s="82"/>
-      <x:c r="I300" s="82"/>
-      <x:c r="J300" s="82"/>
-    </x:row>
-    <x:row r="301">
-      <x:c r="A301" s="84"/>
-      <x:c r="B301" s="83"/>
-      <x:c r="C301" s="82"/>
-      <x:c r="D301" s="82"/>
-      <x:c r="E301" s="82"/>
-      <x:c r="F301" s="82"/>
-      <x:c r="G301" s="82"/>
-      <x:c r="H301" s="82"/>
-      <x:c r="I301" s="82"/>
-      <x:c r="J301" s="82"/>
-    </x:row>
-    <x:row r="302">
-      <x:c r="A302" s="84"/>
-      <x:c r="B302" s="83"/>
-      <x:c r="C302" s="82"/>
-      <x:c r="D302" s="82"/>
-      <x:c r="E302" s="82"/>
-      <x:c r="F302" s="82"/>
-      <x:c r="G302" s="82"/>
-      <x:c r="H302" s="82"/>
-      <x:c r="I302" s="82"/>
-      <x:c r="J302" s="82"/>
-    </x:row>
-    <x:row r="303">
-      <x:c r="A303" s="84"/>
-      <x:c r="B303" s="83"/>
-      <x:c r="C303" s="82"/>
-      <x:c r="D303" s="82"/>
-      <x:c r="E303" s="82"/>
-      <x:c r="F303" s="82"/>
-      <x:c r="G303" s="82"/>
-      <x:c r="H303" s="82"/>
-      <x:c r="I303" s="82"/>
-      <x:c r="J303" s="82"/>
-    </x:row>
-    <x:row r="304">
-      <x:c r="A304" s="84"/>
-      <x:c r="B304" s="83"/>
-      <x:c r="C304" s="82"/>
-      <x:c r="D304" s="82"/>
-      <x:c r="E304" s="82"/>
-      <x:c r="F304" s="82"/>
-      <x:c r="G304" s="82"/>
-      <x:c r="H304" s="82"/>
-      <x:c r="I304" s="82"/>
-      <x:c r="J304" s="82"/>
-    </x:row>
-    <x:row r="305">
-      <x:c r="A305" s="84"/>
-      <x:c r="B305" s="83"/>
-      <x:c r="C305" s="82"/>
-      <x:c r="D305" s="82"/>
-      <x:c r="E305" s="82"/>
-      <x:c r="F305" s="82"/>
-      <x:c r="G305" s="82"/>
-      <x:c r="H305" s="82"/>
-      <x:c r="I305" s="82"/>
-      <x:c r="J305" s="82"/>
-    </x:row>
-    <x:row r="306">
-      <x:c r="A306" s="84"/>
-      <x:c r="B306" s="83"/>
-      <x:c r="C306" s="82"/>
-      <x:c r="D306" s="82"/>
-      <x:c r="E306" s="82"/>
-      <x:c r="F306" s="82"/>
-      <x:c r="G306" s="82"/>
-      <x:c r="H306" s="82"/>
-      <x:c r="I306" s="82"/>
-      <x:c r="J306" s="82"/>
-    </x:row>
-    <x:row r="307">
-      <x:c r="A307" s="84"/>
-      <x:c r="B307" s="83"/>
-      <x:c r="C307" s="82"/>
-      <x:c r="D307" s="82"/>
-      <x:c r="E307" s="82"/>
-      <x:c r="F307" s="82"/>
-      <x:c r="G307" s="82"/>
-      <x:c r="H307" s="82"/>
-      <x:c r="I307" s="82"/>
-      <x:c r="J307" s="82"/>
-    </x:row>
-    <x:row r="308">
-      <x:c r="A308" s="84"/>
-      <x:c r="B308" s="83"/>
-      <x:c r="C308" s="82"/>
-      <x:c r="D308" s="82"/>
-      <x:c r="E308" s="82"/>
-      <x:c r="F308" s="82"/>
-      <x:c r="G308" s="82"/>
-      <x:c r="H308" s="82"/>
-      <x:c r="I308" s="82"/>
-      <x:c r="J308" s="82"/>
-    </x:row>
-    <x:row r="309">
-      <x:c r="A309" s="84"/>
-      <x:c r="B309" s="83"/>
-      <x:c r="C309" s="82"/>
-      <x:c r="D309" s="82"/>
-      <x:c r="E309" s="82"/>
-      <x:c r="F309" s="82"/>
-      <x:c r="G309" s="82"/>
-      <x:c r="H309" s="82"/>
-      <x:c r="I309" s="82"/>
-      <x:c r="J309" s="82"/>
-    </x:row>
-    <x:row r="310">
-      <x:c r="A310" s="84"/>
-      <x:c r="B310" s="83"/>
-      <x:c r="C310" s="82"/>
-      <x:c r="D310" s="82"/>
-      <x:c r="E310" s="82"/>
-      <x:c r="F310" s="82"/>
-      <x:c r="G310" s="82"/>
-      <x:c r="H310" s="82"/>
-      <x:c r="I310" s="82"/>
-      <x:c r="J310" s="82"/>
-    </x:row>
-    <x:row r="311">
-      <x:c r="A311" s="84"/>
-      <x:c r="B311" s="83"/>
-      <x:c r="C311" s="82"/>
-      <x:c r="D311" s="82"/>
-      <x:c r="E311" s="82"/>
-      <x:c r="F311" s="82"/>
-      <x:c r="G311" s="82"/>
-      <x:c r="H311" s="82"/>
-      <x:c r="I311" s="82"/>
-      <x:c r="J311" s="82"/>
-    </x:row>
-    <x:row r="312">
-      <x:c r="A312" s="84"/>
-      <x:c r="B312" s="83"/>
-      <x:c r="C312" s="82"/>
-      <x:c r="D312" s="82"/>
-      <x:c r="E312" s="82"/>
-      <x:c r="F312" s="82"/>
-      <x:c r="G312" s="82"/>
-      <x:c r="H312" s="82"/>
-      <x:c r="I312" s="82"/>
-      <x:c r="J312" s="82"/>
-    </x:row>
-    <x:row r="313">
-      <x:c r="A313" s="84"/>
-      <x:c r="B313" s="83"/>
-      <x:c r="C313" s="82"/>
-      <x:c r="D313" s="82"/>
-      <x:c r="E313" s="82"/>
-      <x:c r="F313" s="82"/>
-      <x:c r="G313" s="82"/>
-      <x:c r="H313" s="82"/>
-      <x:c r="I313" s="82"/>
-      <x:c r="J313" s="82"/>
-    </x:row>
-    <x:row r="314">
-      <x:c r="A314" s="84"/>
-      <x:c r="B314" s="83"/>
-      <x:c r="C314" s="82"/>
-      <x:c r="D314" s="82"/>
-      <x:c r="E314" s="82"/>
-      <x:c r="F314" s="82"/>
-      <x:c r="G314" s="82"/>
-      <x:c r="H314" s="82"/>
-      <x:c r="I314" s="82"/>
-      <x:c r="J314" s="82"/>
-    </x:row>
-    <x:row r="315">
-      <x:c r="A315" s="84"/>
-      <x:c r="B315" s="83"/>
-      <x:c r="C315" s="82"/>
-      <x:c r="D315" s="82"/>
-      <x:c r="E315" s="82"/>
-      <x:c r="F315" s="82"/>
-      <x:c r="G315" s="82"/>
-      <x:c r="H315" s="82"/>
-      <x:c r="I315" s="82"/>
-      <x:c r="J315" s="82"/>
-    </x:row>
-    <x:row r="316">
-      <x:c r="A316" s="84"/>
-      <x:c r="B316" s="83"/>
-      <x:c r="C316" s="82"/>
-      <x:c r="D316" s="82"/>
-      <x:c r="E316" s="82"/>
-      <x:c r="F316" s="82"/>
-      <x:c r="G316" s="82"/>
-      <x:c r="H316" s="82"/>
-      <x:c r="I316" s="82"/>
-      <x:c r="J316" s="82"/>
-    </x:row>
-    <x:row r="317">
-      <x:c r="A317" s="84"/>
-      <x:c r="B317" s="83"/>
-      <x:c r="C317" s="82"/>
-      <x:c r="D317" s="82"/>
-      <x:c r="E317" s="82"/>
-      <x:c r="F317" s="82"/>
-      <x:c r="G317" s="82"/>
-      <x:c r="H317" s="82"/>
-      <x:c r="I317" s="82"/>
-      <x:c r="J317" s="82"/>
-    </x:row>
-    <x:row r="318">
-      <x:c r="A318" s="84"/>
-      <x:c r="B318" s="83"/>
-      <x:c r="C318" s="82"/>
-      <x:c r="D318" s="82"/>
-      <x:c r="E318" s="82"/>
-      <x:c r="F318" s="82"/>
-      <x:c r="G318" s="82"/>
-      <x:c r="H318" s="82"/>
-      <x:c r="I318" s="82"/>
-      <x:c r="J318" s="82"/>
-    </x:row>
-    <x:row r="319">
-      <x:c r="A319" s="84"/>
-      <x:c r="B319" s="83"/>
-      <x:c r="C319" s="82"/>
-      <x:c r="D319" s="82"/>
-      <x:c r="E319" s="82"/>
-      <x:c r="F319" s="82"/>
-      <x:c r="G319" s="82"/>
-      <x:c r="H319" s="82"/>
-      <x:c r="I319" s="82"/>
-      <x:c r="J319" s="82"/>
-    </x:row>
-    <x:row r="320">
-      <x:c r="A320" s="84"/>
-      <x:c r="B320" s="83"/>
-      <x:c r="C320" s="82"/>
-      <x:c r="D320" s="82"/>
-      <x:c r="E320" s="82"/>
-      <x:c r="F320" s="82"/>
-      <x:c r="G320" s="82"/>
-      <x:c r="H320" s="82"/>
-      <x:c r="I320" s="82"/>
-      <x:c r="J320" s="82"/>
-    </x:row>
-    <x:row r="321">
-      <x:c r="A321" s="84"/>
-      <x:c r="B321" s="83"/>
-      <x:c r="C321" s="82"/>
-      <x:c r="D321" s="82"/>
-      <x:c r="E321" s="82"/>
-      <x:c r="F321" s="82"/>
-      <x:c r="G321" s="82"/>
-      <x:c r="H321" s="82"/>
-      <x:c r="I321" s="82"/>
-      <x:c r="J321" s="82"/>
-    </x:row>
-    <x:row r="322">
-      <x:c r="A322" s="84"/>
-      <x:c r="B322" s="83"/>
-      <x:c r="C322" s="82"/>
-      <x:c r="D322" s="82"/>
-      <x:c r="E322" s="82"/>
-      <x:c r="F322" s="82"/>
-      <x:c r="G322" s="82"/>
-      <x:c r="H322" s="82"/>
-      <x:c r="I322" s="82"/>
-      <x:c r="J322" s="82"/>
-    </x:row>
-    <x:row r="323">
-      <x:c r="A323" s="84"/>
-      <x:c r="B323" s="83"/>
-      <x:c r="C323" s="82"/>
-      <x:c r="D323" s="82"/>
-      <x:c r="E323" s="82"/>
-      <x:c r="F323" s="82"/>
-      <x:c r="G323" s="82"/>
-      <x:c r="H323" s="82"/>
-      <x:c r="I323" s="82"/>
-      <x:c r="J323" s="82"/>
-    </x:row>
-    <x:row r="324">
-      <x:c r="A324" s="84"/>
-      <x:c r="B324" s="83"/>
-      <x:c r="C324" s="82"/>
-      <x:c r="D324" s="82"/>
-      <x:c r="E324" s="82"/>
-      <x:c r="F324" s="82"/>
-      <x:c r="G324" s="82"/>
-      <x:c r="H324" s="82"/>
-      <x:c r="I324" s="82"/>
-      <x:c r="J324" s="82"/>
-    </x:row>
-    <x:row r="325">
-      <x:c r="A325" s="84"/>
-      <x:c r="B325" s="83"/>
-      <x:c r="C325" s="82"/>
-      <x:c r="D325" s="82"/>
-      <x:c r="E325" s="82"/>
-      <x:c r="F325" s="82"/>
-      <x:c r="G325" s="82"/>
-      <x:c r="H325" s="82"/>
-      <x:c r="I325" s="82"/>
-      <x:c r="J325" s="82"/>
-    </x:row>
-    <x:row r="326">
-      <x:c r="A326" s="84"/>
-      <x:c r="B326" s="83"/>
-      <x:c r="C326" s="82"/>
-      <x:c r="D326" s="82"/>
-      <x:c r="E326" s="82"/>
-      <x:c r="F326" s="82"/>
-      <x:c r="G326" s="82"/>
-      <x:c r="H326" s="82"/>
-      <x:c r="I326" s="82"/>
-      <x:c r="J326" s="82"/>
-    </x:row>
-    <x:row r="327">
-      <x:c r="A327" s="84"/>
-      <x:c r="B327" s="83"/>
-      <x:c r="C327" s="82"/>
-      <x:c r="D327" s="82"/>
-      <x:c r="E327" s="82"/>
-      <x:c r="F327" s="82"/>
-      <x:c r="G327" s="82"/>
-      <x:c r="H327" s="82"/>
-      <x:c r="I327" s="82"/>
-      <x:c r="J327" s="82"/>
-    </x:row>
-    <x:row r="328">
-      <x:c r="A328" s="84"/>
-      <x:c r="B328" s="83"/>
-      <x:c r="C328" s="82"/>
-      <x:c r="D328" s="82"/>
-      <x:c r="E328" s="82"/>
-      <x:c r="F328" s="82"/>
-      <x:c r="G328" s="82"/>
-      <x:c r="H328" s="82"/>
-      <x:c r="I328" s="82"/>
-      <x:c r="J328" s="82"/>
-    </x:row>
-    <x:row r="329">
-      <x:c r="A329" s="84"/>
-      <x:c r="B329" s="83"/>
-      <x:c r="C329" s="82"/>
-      <x:c r="D329" s="82"/>
-      <x:c r="E329" s="82"/>
-      <x:c r="F329" s="82"/>
-      <x:c r="G329" s="82"/>
-      <x:c r="H329" s="82"/>
-      <x:c r="I329" s="82"/>
-      <x:c r="J329" s="82"/>
-    </x:row>
-    <x:row r="330">
-      <x:c r="A330" s="84"/>
-      <x:c r="B330" s="83"/>
-      <x:c r="C330" s="82"/>
-      <x:c r="D330" s="82"/>
-      <x:c r="E330" s="82"/>
-      <x:c r="F330" s="82"/>
-      <x:c r="G330" s="82"/>
-      <x:c r="H330" s="82"/>
-      <x:c r="I330" s="82"/>
-      <x:c r="J330" s="82"/>
-    </x:row>
-    <x:row r="331">
-      <x:c r="A331" s="84"/>
-      <x:c r="B331" s="83"/>
-      <x:c r="C331" s="82"/>
-      <x:c r="D331" s="82"/>
-      <x:c r="E331" s="82"/>
-      <x:c r="F331" s="82"/>
-      <x:c r="G331" s="82"/>
-      <x:c r="H331" s="82"/>
-      <x:c r="I331" s="82"/>
-      <x:c r="J331" s="82"/>
-    </x:row>
-    <x:row r="332">
-      <x:c r="A332" s="84"/>
-      <x:c r="B332" s="83"/>
-      <x:c r="C332" s="82"/>
-      <x:c r="D332" s="82"/>
-      <x:c r="E332" s="82"/>
-      <x:c r="F332" s="82"/>
-      <x:c r="G332" s="82"/>
-      <x:c r="H332" s="82"/>
-      <x:c r="I332" s="82"/>
-      <x:c r="J332" s="82"/>
-    </x:row>
-    <x:row r="333">
-      <x:c r="A333" s="84"/>
-      <x:c r="B333" s="83"/>
-      <x:c r="C333" s="82"/>
-      <x:c r="D333" s="82"/>
-      <x:c r="E333" s="82"/>
-      <x:c r="F333" s="82"/>
-      <x:c r="G333" s="82"/>
-      <x:c r="H333" s="82"/>
-      <x:c r="I333" s="82"/>
-      <x:c r="J333" s="82"/>
-    </x:row>
-    <x:row r="334">
-      <x:c r="A334" s="84"/>
-      <x:c r="B334" s="83"/>
-      <x:c r="C334" s="82"/>
-      <x:c r="D334" s="82"/>
-      <x:c r="E334" s="82"/>
-      <x:c r="F334" s="82"/>
-      <x:c r="G334" s="82"/>
-      <x:c r="H334" s="82"/>
-      <x:c r="I334" s="82"/>
-      <x:c r="J334" s="82"/>
-    </x:row>
-    <x:row r="335">
-      <x:c r="A335" s="84"/>
-      <x:c r="B335" s="83"/>
-      <x:c r="C335" s="82"/>
-      <x:c r="D335" s="82"/>
-      <x:c r="E335" s="82"/>
-      <x:c r="F335" s="82"/>
-      <x:c r="G335" s="82"/>
-      <x:c r="H335" s="82"/>
-      <x:c r="I335" s="82"/>
-      <x:c r="J335" s="82"/>
-    </x:row>
-    <x:row r="336">
-      <x:c r="A336" s="84"/>
-      <x:c r="B336" s="83"/>
-      <x:c r="C336" s="82"/>
-      <x:c r="D336" s="82"/>
-      <x:c r="E336" s="82"/>
-      <x:c r="F336" s="82"/>
-      <x:c r="G336" s="82"/>
-      <x:c r="H336" s="82"/>
-      <x:c r="I336" s="82"/>
-      <x:c r="J336" s="82"/>
-    </x:row>
-    <x:row r="337">
-      <x:c r="A337" s="84"/>
-      <x:c r="B337" s="83"/>
-      <x:c r="C337" s="82"/>
-      <x:c r="D337" s="82"/>
-      <x:c r="E337" s="82"/>
-      <x:c r="F337" s="82"/>
-      <x:c r="G337" s="82"/>
-      <x:c r="H337" s="82"/>
-      <x:c r="I337" s="82"/>
-      <x:c r="J337" s="82"/>
-    </x:row>
-    <x:row r="338">
-      <x:c r="A338" s="84"/>
-      <x:c r="B338" s="83"/>
-      <x:c r="C338" s="82"/>
-      <x:c r="D338" s="82"/>
-      <x:c r="E338" s="82"/>
-      <x:c r="F338" s="82"/>
-      <x:c r="G338" s="82"/>
-      <x:c r="H338" s="82"/>
-      <x:c r="I338" s="82"/>
-      <x:c r="J338" s="82"/>
-    </x:row>
-    <x:row r="339">
-      <x:c r="A339" s="84"/>
-      <x:c r="B339" s="83"/>
-      <x:c r="C339" s="82"/>
-      <x:c r="D339" s="82"/>
-      <x:c r="E339" s="82"/>
-      <x:c r="F339" s="82"/>
-      <x:c r="G339" s="82"/>
-      <x:c r="H339" s="82"/>
-      <x:c r="I339" s="82"/>
-      <x:c r="J339" s="82"/>
-    </x:row>
-    <x:row r="340">
-      <x:c r="A340" s="84"/>
-      <x:c r="B340" s="83"/>
-      <x:c r="C340" s="82"/>
-      <x:c r="D340" s="82"/>
-      <x:c r="E340" s="82"/>
-      <x:c r="F340" s="82"/>
-      <x:c r="G340" s="82"/>
-      <x:c r="H340" s="82"/>
-      <x:c r="I340" s="82"/>
-      <x:c r="J340" s="82"/>
-    </x:row>
-    <x:row r="341">
-      <x:c r="A341" s="84"/>
-      <x:c r="B341" s="83"/>
-      <x:c r="C341" s="82"/>
-      <x:c r="D341" s="82"/>
-      <x:c r="E341" s="82"/>
-      <x:c r="F341" s="82"/>
-      <x:c r="G341" s="82"/>
-      <x:c r="H341" s="82"/>
-      <x:c r="I341" s="82"/>
-      <x:c r="J341" s="82"/>
-    </x:row>
-    <x:row r="342">
-      <x:c r="A342" s="84"/>
-      <x:c r="B342" s="83"/>
-      <x:c r="C342" s="82"/>
-      <x:c r="D342" s="82"/>
-      <x:c r="E342" s="82"/>
-      <x:c r="F342" s="82"/>
-      <x:c r="G342" s="82"/>
-      <x:c r="H342" s="82"/>
-      <x:c r="I342" s="82"/>
-      <x:c r="J342" s="82"/>
-    </x:row>
-    <x:row r="343">
-      <x:c r="A343" s="84"/>
-      <x:c r="B343" s="83"/>
-      <x:c r="C343" s="82"/>
-      <x:c r="D343" s="82"/>
-      <x:c r="E343" s="82"/>
-      <x:c r="F343" s="82"/>
-      <x:c r="G343" s="82"/>
-      <x:c r="H343" s="82"/>
-      <x:c r="I343" s="82"/>
-      <x:c r="J343" s="82"/>
-    </x:row>
-    <x:row r="344">
-      <x:c r="A344" s="84"/>
-      <x:c r="B344" s="83"/>
-      <x:c r="C344" s="82"/>
-      <x:c r="D344" s="82"/>
-      <x:c r="E344" s="82"/>
-      <x:c r="F344" s="82"/>
-      <x:c r="G344" s="82"/>
-      <x:c r="H344" s="82"/>
-      <x:c r="I344" s="82"/>
-      <x:c r="J344" s="82"/>
-    </x:row>
-    <x:row r="345">
-      <x:c r="A345" s="84"/>
-      <x:c r="B345" s="83"/>
-      <x:c r="C345" s="82"/>
-      <x:c r="D345" s="82"/>
-      <x:c r="E345" s="82"/>
-      <x:c r="F345" s="82"/>
-      <x:c r="G345" s="82"/>
-      <x:c r="H345" s="82"/>
-      <x:c r="I345" s="82"/>
-      <x:c r="J345" s="82"/>
-    </x:row>
-    <x:row r="346">
-      <x:c r="A346" s="84"/>
-      <x:c r="B346" s="83"/>
-      <x:c r="C346" s="82"/>
-      <x:c r="D346" s="82"/>
-      <x:c r="E346" s="82"/>
-      <x:c r="F346" s="82"/>
-      <x:c r="G346" s="82"/>
-      <x:c r="H346" s="82"/>
-      <x:c r="I346" s="82"/>
-      <x:c r="J346" s="82"/>
-    </x:row>
-    <x:row r="347">
-      <x:c r="A347" s="84"/>
-      <x:c r="B347" s="83"/>
-      <x:c r="C347" s="82"/>
-      <x:c r="D347" s="82"/>
-      <x:c r="E347" s="82"/>
-      <x:c r="F347" s="82"/>
-      <x:c r="G347" s="82"/>
-      <x:c r="H347" s="82"/>
-      <x:c r="I347" s="82"/>
-      <x:c r="J347" s="82"/>
-    </x:row>
-    <x:row r="348">
-      <x:c r="A348" s="84"/>
-      <x:c r="B348" s="83"/>
-      <x:c r="C348" s="82"/>
-      <x:c r="D348" s="82"/>
-      <x:c r="E348" s="82"/>
-      <x:c r="F348" s="82"/>
-      <x:c r="G348" s="82"/>
-      <x:c r="H348" s="82"/>
-      <x:c r="I348" s="82"/>
-      <x:c r="J348" s="82"/>
-    </x:row>
-    <x:row r="349">
-      <x:c r="A349" s="84"/>
-      <x:c r="B349" s="83"/>
-      <x:c r="C349" s="82"/>
-      <x:c r="D349" s="82"/>
-      <x:c r="E349" s="82"/>
-      <x:c r="F349" s="82"/>
-      <x:c r="G349" s="82"/>
-      <x:c r="H349" s="82"/>
-      <x:c r="I349" s="82"/>
-      <x:c r="J349" s="82"/>
-    </x:row>
-    <x:row r="350">
-      <x:c r="A350" s="84"/>
-      <x:c r="B350" s="83"/>
-      <x:c r="C350" s="82"/>
-      <x:c r="D350" s="82"/>
-      <x:c r="E350" s="82"/>
-      <x:c r="F350" s="82"/>
-      <x:c r="G350" s="82"/>
-      <x:c r="H350" s="82"/>
-      <x:c r="I350" s="82"/>
-      <x:c r="J350" s="82"/>
-    </x:row>
-    <x:row r="351">
-      <x:c r="A351" s="84"/>
-      <x:c r="B351" s="83"/>
-      <x:c r="C351" s="82"/>
-      <x:c r="D351" s="82"/>
-      <x:c r="E351" s="82"/>
-      <x:c r="F351" s="82"/>
-      <x:c r="G351" s="82"/>
-      <x:c r="H351" s="82"/>
-      <x:c r="I351" s="82"/>
-      <x:c r="J351" s="82"/>
-    </x:row>
-    <x:row r="352">
-      <x:c r="A352" s="84"/>
-      <x:c r="B352" s="83"/>
-      <x:c r="C352" s="82"/>
-      <x:c r="D352" s="82"/>
-      <x:c r="E352" s="82"/>
-      <x:c r="F352" s="82"/>
-      <x:c r="G352" s="82"/>
-      <x:c r="H352" s="82"/>
-      <x:c r="I352" s="82"/>
-      <x:c r="J352" s="82"/>
-    </x:row>
-    <x:row r="353">
-      <x:c r="A353" s="84"/>
-      <x:c r="B353" s="83"/>
-      <x:c r="C353" s="82"/>
-      <x:c r="D353" s="82"/>
-      <x:c r="E353" s="82"/>
-      <x:c r="F353" s="82"/>
-      <x:c r="G353" s="82"/>
-      <x:c r="H353" s="82"/>
-      <x:c r="I353" s="82"/>
-      <x:c r="J353" s="82"/>
-    </x:row>
-    <x:row r="354">
-      <x:c r="A354" s="84"/>
-      <x:c r="B354" s="83"/>
-      <x:c r="C354" s="82"/>
-      <x:c r="D354" s="82"/>
-      <x:c r="E354" s="82"/>
-      <x:c r="F354" s="82"/>
-      <x:c r="G354" s="82"/>
-      <x:c r="H354" s="82"/>
-      <x:c r="I354" s="82"/>
-      <x:c r="J354" s="82"/>
-    </x:row>
-    <x:row r="355">
-      <x:c r="A355" s="84"/>
-      <x:c r="B355" s="83"/>
-      <x:c r="C355" s="82"/>
-      <x:c r="D355" s="82"/>
-      <x:c r="E355" s="82"/>
-      <x:c r="F355" s="82"/>
-      <x:c r="G355" s="82"/>
-      <x:c r="H355" s="82"/>
-      <x:c r="I355" s="82"/>
-      <x:c r="J355" s="82"/>
-    </x:row>
-    <x:row r="356">
-      <x:c r="A356" s="84"/>
-      <x:c r="B356" s="83"/>
-      <x:c r="C356" s="82"/>
-      <x:c r="D356" s="82"/>
-      <x:c r="E356" s="82"/>
-      <x:c r="F356" s="82"/>
-      <x:c r="G356" s="82"/>
-      <x:c r="H356" s="82"/>
-      <x:c r="I356" s="82"/>
-      <x:c r="J356" s="82"/>
-    </x:row>
-    <x:row r="357">
-      <x:c r="A357" s="84"/>
-      <x:c r="B357" s="83"/>
-      <x:c r="C357" s="82"/>
-      <x:c r="D357" s="82"/>
-      <x:c r="E357" s="82"/>
-      <x:c r="F357" s="82"/>
-      <x:c r="G357" s="82"/>
-      <x:c r="H357" s="82"/>
-      <x:c r="I357" s="82"/>
-      <x:c r="J357" s="82"/>
-    </x:row>
-    <x:row r="358">
-      <x:c r="A358" s="84"/>
-      <x:c r="B358" s="83"/>
-      <x:c r="C358" s="82"/>
-      <x:c r="D358" s="82"/>
-      <x:c r="E358" s="82"/>
-      <x:c r="F358" s="82"/>
-      <x:c r="G358" s="82"/>
-      <x:c r="H358" s="82"/>
-      <x:c r="I358" s="82"/>
-      <x:c r="J358" s="82"/>
-    </x:row>
-    <x:row r="359">
-      <x:c r="A359" s="84"/>
-      <x:c r="B359" s="83"/>
-      <x:c r="C359" s="82"/>
-      <x:c r="D359" s="82"/>
-      <x:c r="E359" s="82"/>
-      <x:c r="F359" s="82"/>
-      <x:c r="G359" s="82"/>
-      <x:c r="H359" s="82"/>
-      <x:c r="I359" s="82"/>
-      <x:c r="J359" s="82"/>
-    </x:row>
-    <x:row r="360">
-      <x:c r="A360" s="84"/>
-      <x:c r="B360" s="83"/>
-      <x:c r="C360" s="82"/>
-      <x:c r="D360" s="82"/>
-      <x:c r="E360" s="82"/>
-      <x:c r="F360" s="82"/>
-      <x:c r="G360" s="82"/>
-      <x:c r="H360" s="82"/>
-      <x:c r="I360" s="82"/>
-      <x:c r="J360" s="82"/>
-    </x:row>
-    <x:row r="361">
-      <x:c r="A361" s="84"/>
-      <x:c r="B361" s="83"/>
-      <x:c r="C361" s="82"/>
-      <x:c r="D361" s="82"/>
-      <x:c r="E361" s="82"/>
-      <x:c r="F361" s="82"/>
-      <x:c r="G361" s="82"/>
-      <x:c r="H361" s="82"/>
-      <x:c r="I361" s="82"/>
-      <x:c r="J361" s="82"/>
-    </x:row>
-    <x:row r="362">
-      <x:c r="A362" s="84"/>
-      <x:c r="B362" s="83"/>
-      <x:c r="C362" s="82"/>
-      <x:c r="D362" s="82"/>
-      <x:c r="E362" s="82"/>
-      <x:c r="F362" s="82"/>
-      <x:c r="G362" s="82"/>
-      <x:c r="H362" s="82"/>
-      <x:c r="I362" s="82"/>
-      <x:c r="J362" s="82"/>
-    </x:row>
-    <x:row r="363">
-      <x:c r="A363" s="84"/>
-      <x:c r="B363" s="83"/>
-      <x:c r="C363" s="82"/>
-      <x:c r="D363" s="82"/>
-      <x:c r="E363" s="82"/>
-      <x:c r="F363" s="82"/>
-      <x:c r="G363" s="82"/>
-      <x:c r="H363" s="82"/>
-      <x:c r="I363" s="82"/>
-      <x:c r="J363" s="82"/>
-    </x:row>
-    <x:row r="364">
-      <x:c r="A364" s="84"/>
-      <x:c r="B364" s="83"/>
-      <x:c r="C364" s="82"/>
-      <x:c r="D364" s="82"/>
-      <x:c r="E364" s="82"/>
-      <x:c r="F364" s="82"/>
-      <x:c r="G364" s="82"/>
-      <x:c r="H364" s="82"/>
-      <x:c r="I364" s="82"/>
-      <x:c r="J364" s="82"/>
-    </x:row>
-    <x:row r="365">
-      <x:c r="A365" s="84"/>
-      <x:c r="B365" s="83"/>
-      <x:c r="C365" s="82"/>
-      <x:c r="D365" s="82"/>
-      <x:c r="E365" s="82"/>
-      <x:c r="F365" s="82"/>
-      <x:c r="G365" s="82"/>
-      <x:c r="H365" s="82"/>
-      <x:c r="I365" s="82"/>
-      <x:c r="J365" s="82"/>
-    </x:row>
-    <x:row r="366">
-      <x:c r="A366" s="84"/>
-      <x:c r="B366" s="83"/>
-      <x:c r="C366" s="82"/>
-      <x:c r="D366" s="82"/>
-      <x:c r="E366" s="82"/>
-      <x:c r="F366" s="82"/>
-      <x:c r="G366" s="82"/>
-      <x:c r="H366" s="82"/>
-      <x:c r="I366" s="82"/>
-      <x:c r="J366" s="82"/>
-    </x:row>
-    <x:row r="367">
-      <x:c r="A367" s="84"/>
-      <x:c r="B367" s="83"/>
-      <x:c r="C367" s="82"/>
-      <x:c r="D367" s="82"/>
-      <x:c r="E367" s="82"/>
-      <x:c r="F367" s="82"/>
-      <x:c r="G367" s="82"/>
-      <x:c r="H367" s="82"/>
-      <x:c r="I367" s="82"/>
-      <x:c r="J367" s="82"/>
-    </x:row>
-    <x:row r="368">
-      <x:c r="A368" s="84"/>
-      <x:c r="B368" s="83"/>
-      <x:c r="C368" s="82"/>
-      <x:c r="D368" s="82"/>
-      <x:c r="E368" s="82"/>
-      <x:c r="F368" s="82"/>
-      <x:c r="G368" s="82"/>
-      <x:c r="H368" s="82"/>
-      <x:c r="I368" s="82"/>
-      <x:c r="J368" s="82"/>
-    </x:row>
-    <x:row r="369">
-      <x:c r="A369" s="84"/>
-      <x:c r="B369" s="83"/>
-      <x:c r="C369" s="82"/>
-      <x:c r="D369" s="82"/>
-      <x:c r="E369" s="82"/>
-      <x:c r="F369" s="82"/>
-      <x:c r="G369" s="82"/>
-      <x:c r="H369" s="82"/>
-      <x:c r="I369" s="82"/>
-      <x:c r="J369" s="82"/>
-    </x:row>
-    <x:row r="370">
-      <x:c r="A370" s="84"/>
-      <x:c r="B370" s="83"/>
-      <x:c r="C370" s="82"/>
-      <x:c r="D370" s="82"/>
-      <x:c r="E370" s="82"/>
-      <x:c r="F370" s="82"/>
-      <x:c r="G370" s="82"/>
-      <x:c r="H370" s="82"/>
-      <x:c r="I370" s="82"/>
-      <x:c r="J370" s="82"/>
-    </x:row>
-    <x:row r="371">
-      <x:c r="A371" s="84"/>
-      <x:c r="B371" s="83"/>
-      <x:c r="C371" s="82"/>
-      <x:c r="D371" s="82"/>
-      <x:c r="E371" s="82"/>
-      <x:c r="F371" s="82"/>
-      <x:c r="G371" s="82"/>
-      <x:c r="H371" s="82"/>
-      <x:c r="I371" s="82"/>
-      <x:c r="J371" s="82"/>
-    </x:row>
-    <x:row r="372">
-      <x:c r="A372" s="84"/>
-      <x:c r="B372" s="83"/>
-      <x:c r="C372" s="82"/>
-      <x:c r="D372" s="82"/>
-      <x:c r="E372" s="82"/>
-      <x:c r="F372" s="82"/>
-      <x:c r="G372" s="82"/>
-      <x:c r="H372" s="82"/>
-      <x:c r="I372" s="82"/>
-      <x:c r="J372" s="82"/>
-    </x:row>
-    <x:row r="373">
-      <x:c r="A373" s="84"/>
-      <x:c r="B373" s="83"/>
-      <x:c r="C373" s="82"/>
-      <x:c r="D373" s="82"/>
-      <x:c r="E373" s="82"/>
-      <x:c r="F373" s="82"/>
-      <x:c r="G373" s="82"/>
-      <x:c r="H373" s="82"/>
-      <x:c r="I373" s="82"/>
-      <x:c r="J373" s="82"/>
-    </x:row>
-    <x:row r="374">
-      <x:c r="A374" s="84"/>
-      <x:c r="B374" s="83"/>
-      <x:c r="C374" s="82"/>
-      <x:c r="D374" s="82"/>
-      <x:c r="E374" s="82"/>
-      <x:c r="F374" s="82"/>
-      <x:c r="G374" s="82"/>
-      <x:c r="H374" s="82"/>
-      <x:c r="I374" s="82"/>
-      <x:c r="J374" s="82"/>
-    </x:row>
-    <x:row r="375">
-      <x:c r="A375" s="84"/>
-      <x:c r="B375" s="83"/>
-      <x:c r="C375" s="82"/>
-      <x:c r="D375" s="82"/>
-      <x:c r="E375" s="82"/>
-      <x:c r="F375" s="82"/>
-      <x:c r="G375" s="82"/>
-      <x:c r="H375" s="82"/>
-      <x:c r="I375" s="82"/>
-      <x:c r="J375" s="82"/>
-    </x:row>
-    <x:row r="376">
-      <x:c r="A376" s="84"/>
-      <x:c r="B376" s="83"/>
-      <x:c r="C376" s="82"/>
-      <x:c r="D376" s="82"/>
-      <x:c r="E376" s="82"/>
-      <x:c r="F376" s="82"/>
-      <x:c r="G376" s="82"/>
-      <x:c r="H376" s="82"/>
-      <x:c r="I376" s="82"/>
-      <x:c r="J376" s="82"/>
-    </x:row>
-    <x:row r="377">
-      <x:c r="A377" s="84"/>
-      <x:c r="B377" s="83"/>
-      <x:c r="C377" s="82"/>
-      <x:c r="D377" s="82"/>
-      <x:c r="E377" s="82"/>
-      <x:c r="F377" s="82"/>
-      <x:c r="G377" s="82"/>
-      <x:c r="H377" s="82"/>
-      <x:c r="I377" s="82"/>
-      <x:c r="J377" s="82"/>
-    </x:row>
-    <x:row r="378">
-      <x:c r="A378" s="84"/>
-      <x:c r="B378" s="83"/>
-      <x:c r="C378" s="82"/>
-      <x:c r="D378" s="82"/>
-      <x:c r="E378" s="82"/>
-      <x:c r="F378" s="82"/>
-      <x:c r="G378" s="82"/>
-      <x:c r="H378" s="82"/>
-      <x:c r="I378" s="82"/>
-      <x:c r="J378" s="82"/>
-    </x:row>
-    <x:row r="379">
-      <x:c r="A379" s="84"/>
-      <x:c r="B379" s="83"/>
-      <x:c r="C379" s="82"/>
-      <x:c r="D379" s="82"/>
-      <x:c r="E379" s="82"/>
-      <x:c r="F379" s="82"/>
-      <x:c r="G379" s="82"/>
-      <x:c r="H379" s="82"/>
-      <x:c r="I379" s="82"/>
-      <x:c r="J379" s="82"/>
-    </x:row>
-    <x:row r="380">
-      <x:c r="A380" s="84"/>
-      <x:c r="B380" s="83"/>
-      <x:c r="C380" s="82"/>
-      <x:c r="D380" s="82"/>
-      <x:c r="E380" s="82"/>
-      <x:c r="F380" s="82"/>
-      <x:c r="G380" s="82"/>
-      <x:c r="H380" s="82"/>
-      <x:c r="I380" s="82"/>
-      <x:c r="J380" s="82"/>
-    </x:row>
-    <x:row r="381">
-      <x:c r="A381" s="84"/>
-      <x:c r="B381" s="83"/>
-      <x:c r="C381" s="82"/>
-      <x:c r="D381" s="82"/>
-      <x:c r="E381" s="82"/>
-      <x:c r="F381" s="82"/>
-      <x:c r="G381" s="82"/>
-      <x:c r="H381" s="82"/>
-      <x:c r="I381" s="82"/>
-      <x:c r="J381" s="82"/>
-    </x:row>
-    <x:row r="382">
-      <x:c r="A382" s="84"/>
-      <x:c r="B382" s="83"/>
-      <x:c r="C382" s="82"/>
-      <x:c r="D382" s="82"/>
-      <x:c r="E382" s="82"/>
-      <x:c r="F382" s="82"/>
-      <x:c r="G382" s="82"/>
-      <x:c r="H382" s="82"/>
-      <x:c r="I382" s="82"/>
-      <x:c r="J382" s="82"/>
-    </x:row>
-    <x:row r="383">
-      <x:c r="A383" s="84"/>
-      <x:c r="B383" s="83"/>
-      <x:c r="C383" s="82"/>
-      <x:c r="D383" s="82"/>
-      <x:c r="E383" s="82"/>
-      <x:c r="F383" s="82"/>
-      <x:c r="G383" s="82"/>
-      <x:c r="H383" s="82"/>
-      <x:c r="I383" s="82"/>
-      <x:c r="J383" s="82"/>
-    </x:row>
-    <x:row r="384">
-      <x:c r="A384" s="84"/>
-      <x:c r="B384" s="83"/>
-      <x:c r="C384" s="82"/>
-      <x:c r="D384" s="82"/>
-      <x:c r="E384" s="82"/>
-      <x:c r="F384" s="82"/>
-      <x:c r="G384" s="82"/>
-      <x:c r="H384" s="82"/>
-      <x:c r="I384" s="82"/>
-      <x:c r="J384" s="82"/>
-    </x:row>
-    <x:row r="385">
-      <x:c r="A385" s="84"/>
-      <x:c r="B385" s="83"/>
-      <x:c r="C385" s="82"/>
-      <x:c r="D385" s="82"/>
-      <x:c r="E385" s="82"/>
-      <x:c r="F385" s="82"/>
-      <x:c r="G385" s="82"/>
-      <x:c r="H385" s="82"/>
-      <x:c r="I385" s="82"/>
-      <x:c r="J385" s="82"/>
-    </x:row>
-    <x:row r="386">
-      <x:c r="A386" s="84"/>
-      <x:c r="B386" s="83"/>
-      <x:c r="C386" s="82"/>
-      <x:c r="D386" s="82"/>
-      <x:c r="E386" s="82"/>
-      <x:c r="F386" s="82"/>
-      <x:c r="G386" s="82"/>
-      <x:c r="H386" s="82"/>
-      <x:c r="I386" s="82"/>
-      <x:c r="J386" s="82"/>
-    </x:row>
-    <x:row r="387">
-      <x:c r="A387" s="84"/>
-      <x:c r="B387" s="83"/>
-      <x:c r="C387" s="82"/>
-      <x:c r="D387" s="82"/>
-      <x:c r="E387" s="82"/>
-      <x:c r="F387" s="82"/>
-      <x:c r="G387" s="82"/>
-      <x:c r="H387" s="82"/>
-      <x:c r="I387" s="82"/>
-      <x:c r="J387" s="82"/>
-    </x:row>
-    <x:row r="388">
-      <x:c r="A388" s="84"/>
-      <x:c r="B388" s="83"/>
-      <x:c r="C388" s="82"/>
-      <x:c r="D388" s="82"/>
-      <x:c r="E388" s="82"/>
-      <x:c r="F388" s="82"/>
-      <x:c r="G388" s="82"/>
-      <x:c r="H388" s="82"/>
-      <x:c r="I388" s="82"/>
-      <x:c r="J388" s="82"/>
-    </x:row>
-    <x:row r="389">
-      <x:c r="A389" s="84"/>
-      <x:c r="B389" s="83"/>
-      <x:c r="C389" s="82"/>
-      <x:c r="D389" s="82"/>
-      <x:c r="E389" s="82"/>
-      <x:c r="F389" s="82"/>
-      <x:c r="G389" s="82"/>
-      <x:c r="H389" s="82"/>
-      <x:c r="I389" s="82"/>
-      <x:c r="J389" s="82"/>
-    </x:row>
-    <x:row r="390">
-      <x:c r="A390" s="84"/>
-      <x:c r="B390" s="83"/>
-      <x:c r="C390" s="82"/>
-      <x:c r="D390" s="82"/>
-      <x:c r="E390" s="82"/>
-      <x:c r="F390" s="82"/>
-      <x:c r="G390" s="82"/>
-      <x:c r="H390" s="82"/>
-      <x:c r="I390" s="82"/>
-      <x:c r="J390" s="82"/>
-    </x:row>
-    <x:row r="391">
-      <x:c r="A391" s="84"/>
-      <x:c r="B391" s="83"/>
-      <x:c r="C391" s="82"/>
-      <x:c r="D391" s="82"/>
-      <x:c r="E391" s="82"/>
-      <x:c r="F391" s="82"/>
-      <x:c r="G391" s="82"/>
-      <x:c r="H391" s="82"/>
-      <x:c r="I391" s="82"/>
-      <x:c r="J391" s="82"/>
-    </x:row>
-    <x:row r="392">
-      <x:c r="A392" s="84"/>
-      <x:c r="B392" s="83"/>
-      <x:c r="C392" s="82"/>
-      <x:c r="D392" s="82"/>
-      <x:c r="E392" s="82"/>
-      <x:c r="F392" s="82"/>
-      <x:c r="G392" s="82"/>
-      <x:c r="H392" s="82"/>
-      <x:c r="I392" s="82"/>
-      <x:c r="J392" s="82"/>
-    </x:row>
-    <x:row r="393">
-      <x:c r="A393" s="84"/>
-      <x:c r="B393" s="83"/>
-      <x:c r="C393" s="82"/>
-      <x:c r="D393" s="82"/>
-      <x:c r="E393" s="82"/>
-      <x:c r="F393" s="82"/>
-      <x:c r="G393" s="82"/>
-      <x:c r="H393" s="82"/>
-      <x:c r="I393" s="82"/>
-      <x:c r="J393" s="82"/>
-    </x:row>
-    <x:row r="394">
-      <x:c r="A394" s="84"/>
-      <x:c r="B394" s="83"/>
-      <x:c r="C394" s="82"/>
-      <x:c r="D394" s="82"/>
-      <x:c r="E394" s="82"/>
-      <x:c r="F394" s="82"/>
-      <x:c r="G394" s="82"/>
-      <x:c r="H394" s="82"/>
-      <x:c r="I394" s="82"/>
-      <x:c r="J394" s="82"/>
-    </x:row>
-    <x:row r="395">
-      <x:c r="A395" s="84"/>
-      <x:c r="B395" s="83"/>
-      <x:c r="C395" s="82"/>
-      <x:c r="D395" s="82"/>
-      <x:c r="E395" s="82"/>
-      <x:c r="F395" s="82"/>
-      <x:c r="G395" s="82"/>
-      <x:c r="H395" s="82"/>
-      <x:c r="I395" s="82"/>
-      <x:c r="J395" s="82"/>
-    </x:row>
-    <x:row r="396">
-      <x:c r="A396" s="84"/>
-      <x:c r="B396" s="83"/>
-      <x:c r="C396" s="82"/>
-      <x:c r="D396" s="82"/>
-      <x:c r="E396" s="82"/>
-      <x:c r="F396" s="82"/>
-      <x:c r="G396" s="82"/>
-      <x:c r="H396" s="82"/>
-      <x:c r="I396" s="82"/>
-      <x:c r="J396" s="82"/>
-    </x:row>
-    <x:row r="397">
-      <x:c r="A397" s="84"/>
-      <x:c r="B397" s="83"/>
-      <x:c r="C397" s="82"/>
-      <x:c r="D397" s="82"/>
-      <x:c r="E397" s="82"/>
-      <x:c r="F397" s="82"/>
-      <x:c r="G397" s="82"/>
-      <x:c r="H397" s="82"/>
-      <x:c r="I397" s="82"/>
-      <x:c r="J397" s="82"/>
-    </x:row>
-    <x:row r="398">
-      <x:c r="A398" s="84"/>
-      <x:c r="B398" s="83"/>
-      <x:c r="C398" s="82"/>
-      <x:c r="D398" s="82"/>
-      <x:c r="E398" s="82"/>
-      <x:c r="F398" s="82"/>
-      <x:c r="G398" s="82"/>
-      <x:c r="H398" s="82"/>
-      <x:c r="I398" s="82"/>
-      <x:c r="J398" s="82"/>
-    </x:row>
-    <x:row r="399">
-      <x:c r="A399" s="84"/>
-      <x:c r="B399" s="83"/>
-      <x:c r="C399" s="82"/>
-      <x:c r="D399" s="82"/>
-      <x:c r="E399" s="82"/>
-      <x:c r="F399" s="82"/>
-      <x:c r="G399" s="82"/>
-      <x:c r="H399" s="82"/>
-      <x:c r="I399" s="82"/>
-      <x:c r="J399" s="82"/>
-    </x:row>
-    <x:row r="400">
-      <x:c r="A400" s="84"/>
-      <x:c r="B400" s="83"/>
-      <x:c r="C400" s="82"/>
-      <x:c r="D400" s="82"/>
-      <x:c r="E400" s="82"/>
-      <x:c r="F400" s="82"/>
-      <x:c r="G400" s="82"/>
-      <x:c r="H400" s="82"/>
-      <x:c r="I400" s="82"/>
-      <x:c r="J400" s="82"/>
-    </x:row>
-    <x:row r="401">
-      <x:c r="A401" s="84"/>
-      <x:c r="B401" s="83"/>
-      <x:c r="C401" s="82"/>
-      <x:c r="D401" s="82"/>
-      <x:c r="E401" s="82"/>
-      <x:c r="F401" s="82"/>
-      <x:c r="G401" s="82"/>
-      <x:c r="H401" s="82"/>
-      <x:c r="I401" s="82"/>
-      <x:c r="J401" s="82"/>
-    </x:row>
-    <x:row r="402">
-      <x:c r="A402" s="84"/>
-      <x:c r="B402" s="83"/>
-      <x:c r="C402" s="82"/>
-      <x:c r="D402" s="82"/>
-      <x:c r="E402" s="82"/>
-      <x:c r="F402" s="82"/>
-      <x:c r="G402" s="82"/>
-      <x:c r="H402" s="82"/>
-      <x:c r="I402" s="82"/>
-      <x:c r="J402" s="82"/>
-    </x:row>
-    <x:row r="403">
-      <x:c r="A403" s="84"/>
-      <x:c r="B403" s="83"/>
-      <x:c r="C403" s="82"/>
-      <x:c r="D403" s="82"/>
-      <x:c r="E403" s="82"/>
-      <x:c r="F403" s="82"/>
-      <x:c r="G403" s="82"/>
-      <x:c r="H403" s="82"/>
-      <x:c r="I403" s="82"/>
-      <x:c r="J403" s="82"/>
-    </x:row>
-    <x:row r="404">
-      <x:c r="A404" s="84"/>
-      <x:c r="B404" s="83"/>
-      <x:c r="C404" s="82"/>
-      <x:c r="D404" s="82"/>
-      <x:c r="E404" s="82"/>
-      <x:c r="F404" s="82"/>
-      <x:c r="G404" s="82"/>
-      <x:c r="H404" s="82"/>
-      <x:c r="I404" s="82"/>
-      <x:c r="J404" s="82"/>
-    </x:row>
-    <x:row r="405">
-      <x:c r="A405" s="84"/>
-      <x:c r="B405" s="83"/>
-      <x:c r="C405" s="82"/>
-      <x:c r="D405" s="82"/>
-      <x:c r="E405" s="82"/>
-      <x:c r="F405" s="82"/>
-      <x:c r="G405" s="82"/>
-      <x:c r="H405" s="82"/>
-      <x:c r="I405" s="82"/>
-      <x:c r="J405" s="82"/>
-    </x:row>
-    <x:row r="406">
-      <x:c r="A406" s="84"/>
-      <x:c r="B406" s="83"/>
-      <x:c r="C406" s="82"/>
-      <x:c r="D406" s="82"/>
-      <x:c r="E406" s="82"/>
-      <x:c r="F406" s="82"/>
-      <x:c r="G406" s="82"/>
-      <x:c r="H406" s="82"/>
-      <x:c r="I406" s="82"/>
-      <x:c r="J406" s="82"/>
-    </x:row>
-    <x:row r="407">
-      <x:c r="A407" s="84"/>
-      <x:c r="B407" s="83"/>
-      <x:c r="C407" s="82"/>
-      <x:c r="D407" s="82"/>
-      <x:c r="E407" s="82"/>
-      <x:c r="F407" s="82"/>
-      <x:c r="G407" s="82"/>
-      <x:c r="H407" s="82"/>
-      <x:c r="I407" s="82"/>
-      <x:c r="J407" s="82"/>
-    </x:row>
-    <x:row r="408">
-      <x:c r="A408" s="84"/>
-      <x:c r="B408" s="83"/>
-      <x:c r="C408" s="82"/>
-      <x:c r="D408" s="82"/>
-      <x:c r="E408" s="82"/>
-      <x:c r="F408" s="82"/>
-      <x:c r="G408" s="82"/>
-      <x:c r="H408" s="82"/>
-      <x:c r="I408" s="82"/>
-      <x:c r="J408" s="82"/>
-    </x:row>
-    <x:row r="409">
-      <x:c r="A409" s="84"/>
-      <x:c r="B409" s="83"/>
-      <x:c r="C409" s="82"/>
-      <x:c r="D409" s="82"/>
-      <x:c r="E409" s="82"/>
-      <x:c r="F409" s="82"/>
-      <x:c r="G409" s="82"/>
-      <x:c r="H409" s="82"/>
-      <x:c r="I409" s="82"/>
-      <x:c r="J409" s="82"/>
-    </x:row>
-    <x:row r="410">
-      <x:c r="A410" s="84"/>
-      <x:c r="B410" s="83"/>
-      <x:c r="C410" s="82"/>
-      <x:c r="D410" s="82"/>
-      <x:c r="E410" s="82"/>
-      <x:c r="F410" s="82"/>
-      <x:c r="G410" s="82"/>
-      <x:c r="H410" s="82"/>
-      <x:c r="I410" s="82"/>
-      <x:c r="J410" s="82"/>
-    </x:row>
-    <x:row r="411">
-      <x:c r="A411" s="84"/>
-      <x:c r="B411" s="83"/>
-      <x:c r="C411" s="82"/>
-      <x:c r="D411" s="82"/>
-      <x:c r="E411" s="82"/>
-      <x:c r="F411" s="82"/>
-      <x:c r="G411" s="82"/>
-      <x:c r="H411" s="82"/>
-      <x:c r="I411" s="82"/>
-      <x:c r="J411" s="82"/>
-    </x:row>
-    <x:row r="412">
-      <x:c r="A412" s="84"/>
-      <x:c r="B412" s="83"/>
-      <x:c r="C412" s="82"/>
-      <x:c r="D412" s="82"/>
-      <x:c r="E412" s="82"/>
-      <x:c r="F412" s="82"/>
-      <x:c r="G412" s="82"/>
-      <x:c r="H412" s="82"/>
-      <x:c r="I412" s="82"/>
-      <x:c r="J412" s="82"/>
-    </x:row>
-    <x:row r="413">
-      <x:c r="A413" s="84"/>
-      <x:c r="B413" s="83"/>
-      <x:c r="C413" s="82"/>
-      <x:c r="D413" s="82"/>
-      <x:c r="E413" s="82"/>
-      <x:c r="F413" s="82"/>
-      <x:c r="G413" s="82"/>
-      <x:c r="H413" s="82"/>
-      <x:c r="I413" s="82"/>
-      <x:c r="J413" s="82"/>
-    </x:row>
-    <x:row r="414">
-      <x:c r="A414" s="84"/>
-      <x:c r="B414" s="83"/>
-      <x:c r="C414" s="82"/>
-      <x:c r="D414" s="82"/>
-      <x:c r="E414" s="82"/>
-      <x:c r="F414" s="82"/>
-      <x:c r="G414" s="82"/>
-      <x:c r="H414" s="82"/>
-      <x:c r="I414" s="82"/>
-      <x:c r="J414" s="82"/>
-    </x:row>
-    <x:row r="415">
-      <x:c r="A415" s="84"/>
-      <x:c r="B415" s="83"/>
-      <x:c r="C415" s="82"/>
-      <x:c r="D415" s="82"/>
-      <x:c r="E415" s="82"/>
-      <x:c r="F415" s="82"/>
-      <x:c r="G415" s="82"/>
-      <x:c r="H415" s="82"/>
-      <x:c r="I415" s="82"/>
-      <x:c r="J415" s="82"/>
-    </x:row>
-    <x:row r="416">
-      <x:c r="A416" s="84"/>
-      <x:c r="B416" s="83"/>
-      <x:c r="C416" s="82"/>
-      <x:c r="D416" s="82"/>
-      <x:c r="E416" s="82"/>
-      <x:c r="F416" s="82"/>
-      <x:c r="G416" s="82"/>
-      <x:c r="H416" s="82"/>
-      <x:c r="I416" s="82"/>
-      <x:c r="J416" s="82"/>
-    </x:row>
-    <x:row r="417">
-      <x:c r="A417" s="84"/>
-      <x:c r="B417" s="83"/>
-      <x:c r="C417" s="82"/>
-      <x:c r="D417" s="82"/>
-      <x:c r="E417" s="82"/>
-      <x:c r="F417" s="82"/>
-      <x:c r="G417" s="82"/>
-      <x:c r="H417" s="82"/>
-      <x:c r="I417" s="82"/>
-      <x:c r="J417" s="82"/>
-    </x:row>
-    <x:row r="418">
-      <x:c r="A418" s="84"/>
-      <x:c r="B418" s="83"/>
-      <x:c r="C418" s="82"/>
-      <x:c r="D418" s="82"/>
-      <x:c r="E418" s="82"/>
-      <x:c r="F418" s="82"/>
-      <x:c r="G418" s="82"/>
-      <x:c r="H418" s="82"/>
-      <x:c r="I418" s="82"/>
-      <x:c r="J418" s="82"/>
-    </x:row>
-    <x:row r="419">
-      <x:c r="A419" s="84"/>
-      <x:c r="B419" s="83"/>
-      <x:c r="C419" s="82"/>
-      <x:c r="D419" s="82"/>
-      <x:c r="E419" s="82"/>
-      <x:c r="F419" s="82"/>
-      <x:c r="G419" s="82"/>
-      <x:c r="H419" s="82"/>
-      <x:c r="I419" s="82"/>
-      <x:c r="J419" s="82"/>
-    </x:row>
-    <x:row r="420">
-      <x:c r="A420" s="84"/>
-      <x:c r="B420" s="83"/>
-      <x:c r="C420" s="82"/>
-      <x:c r="D420" s="82"/>
-      <x:c r="E420" s="82"/>
-      <x:c r="F420" s="82"/>
-      <x:c r="G420" s="82"/>
-      <x:c r="H420" s="82"/>
-      <x:c r="I420" s="82"/>
-      <x:c r="J420" s="82"/>
-    </x:row>
-    <x:row r="421">
-      <x:c r="A421" s="84"/>
-      <x:c r="B421" s="83"/>
-      <x:c r="C421" s="82"/>
-      <x:c r="D421" s="82"/>
-      <x:c r="E421" s="82"/>
-      <x:c r="F421" s="82"/>
-      <x:c r="G421" s="82"/>
-      <x:c r="H421" s="82"/>
-      <x:c r="I421" s="82"/>
-      <x:c r="J421" s="82"/>
-    </x:row>
-    <x:row r="422">
-      <x:c r="A422" s="84"/>
-      <x:c r="B422" s="83"/>
-      <x:c r="C422" s="82"/>
-      <x:c r="D422" s="82"/>
-      <x:c r="E422" s="82"/>
-      <x:c r="F422" s="82"/>
-      <x:c r="G422" s="82"/>
-      <x:c r="H422" s="82"/>
-      <x:c r="I422" s="82"/>
-      <x:c r="J422" s="82"/>
-    </x:row>
-    <x:row r="423">
-      <x:c r="A423" s="84"/>
-      <x:c r="B423" s="83"/>
-      <x:c r="C423" s="82"/>
-      <x:c r="D423" s="82"/>
-      <x:c r="E423" s="82"/>
-      <x:c r="F423" s="82"/>
-      <x:c r="G423" s="82"/>
-      <x:c r="H423" s="82"/>
-      <x:c r="I423" s="82"/>
-      <x:c r="J423" s="82"/>
-    </x:row>
-    <x:row r="424">
-      <x:c r="A424" s="84"/>
-      <x:c r="B424" s="83"/>
-      <x:c r="C424" s="82"/>
-      <x:c r="D424" s="82"/>
-      <x:c r="E424" s="82"/>
-      <x:c r="F424" s="82"/>
-      <x:c r="G424" s="82"/>
-      <x:c r="H424" s="82"/>
-      <x:c r="I424" s="82"/>
-      <x:c r="J424" s="82"/>
-    </x:row>
-    <x:row r="425">
-      <x:c r="A425" s="84"/>
-      <x:c r="B425" s="83"/>
-      <x:c r="C425" s="82"/>
-      <x:c r="D425" s="82"/>
-      <x:c r="E425" s="82"/>
-      <x:c r="F425" s="82"/>
-      <x:c r="G425" s="82"/>
-      <x:c r="H425" s="82"/>
-      <x:c r="I425" s="82"/>
-      <x:c r="J425" s="82"/>
-    </x:row>
-    <x:row r="426">
-      <x:c r="A426" s="84"/>
-      <x:c r="B426" s="83"/>
-      <x:c r="C426" s="82"/>
-      <x:c r="D426" s="82"/>
-      <x:c r="E426" s="82"/>
-      <x:c r="F426" s="82"/>
-      <x:c r="G426" s="82"/>
-      <x:c r="H426" s="82"/>
-      <x:c r="I426" s="82"/>
-      <x:c r="J426" s="82"/>
-    </x:row>
-    <x:row r="427">
-      <x:c r="A427" s="84"/>
-      <x:c r="B427" s="83"/>
-      <x:c r="C427" s="82"/>
-      <x:c r="D427" s="82"/>
-      <x:c r="E427" s="82"/>
-      <x:c r="F427" s="82"/>
-      <x:c r="G427" s="82"/>
-      <x:c r="H427" s="82"/>
-      <x:c r="I427" s="82"/>
-      <x:c r="J427" s="82"/>
-    </x:row>
-    <x:row r="428">
-      <x:c r="A428" s="84"/>
-      <x:c r="B428" s="83"/>
-      <x:c r="C428" s="82"/>
-      <x:c r="D428" s="82"/>
-      <x:c r="E428" s="82"/>
-      <x:c r="F428" s="82"/>
-      <x:c r="G428" s="82"/>
-      <x:c r="H428" s="82"/>
-      <x:c r="I428" s="82"/>
-      <x:c r="J428" s="82"/>
-    </x:row>
-    <x:row r="429">
-      <x:c r="A429" s="84"/>
-      <x:c r="B429" s="83"/>
-      <x:c r="C429" s="82"/>
-      <x:c r="D429" s="82"/>
-      <x:c r="E429" s="82"/>
-      <x:c r="F429" s="82"/>
-      <x:c r="G429" s="82"/>
-      <x:c r="H429" s="82"/>
-      <x:c r="I429" s="82"/>
-      <x:c r="J429" s="82"/>
-    </x:row>
-    <x:row r="430">
-      <x:c r="A430" s="84"/>
-      <x:c r="B430" s="83"/>
-      <x:c r="C430" s="82"/>
-      <x:c r="D430" s="82"/>
-      <x:c r="E430" s="82"/>
-      <x:c r="F430" s="82"/>
-      <x:c r="G430" s="82"/>
-      <x:c r="H430" s="82"/>
-      <x:c r="I430" s="82"/>
-      <x:c r="J430" s="82"/>
-    </x:row>
-    <x:row r="431">
-      <x:c r="A431" s="84"/>
-      <x:c r="B431" s="83"/>
-      <x:c r="C431" s="82"/>
-      <x:c r="D431" s="82"/>
-      <x:c r="E431" s="82"/>
-      <x:c r="F431" s="82"/>
-      <x:c r="G431" s="82"/>
-      <x:c r="H431" s="82"/>
-      <x:c r="I431" s="82"/>
-      <x:c r="J431" s="82"/>
-    </x:row>
-    <x:row r="432">
-      <x:c r="A432" s="84"/>
-      <x:c r="B432" s="83"/>
-      <x:c r="C432" s="82"/>
-      <x:c r="D432" s="82"/>
-      <x:c r="E432" s="82"/>
-      <x:c r="F432" s="82"/>
-      <x:c r="G432" s="82"/>
-      <x:c r="H432" s="82"/>
-      <x:c r="I432" s="82"/>
-      <x:c r="J432" s="82"/>
-    </x:row>
-    <x:row r="433">
-      <x:c r="A433" s="84"/>
-      <x:c r="B433" s="83"/>
-      <x:c r="C433" s="82"/>
-      <x:c r="D433" s="82"/>
-      <x:c r="E433" s="82"/>
-      <x:c r="F433" s="82"/>
-      <x:c r="G433" s="82"/>
-      <x:c r="H433" s="82"/>
-      <x:c r="I433" s="82"/>
-      <x:c r="J433" s="82"/>
-    </x:row>
-    <x:row r="434">
-      <x:c r="A434" s="84"/>
-      <x:c r="B434" s="83"/>
-      <x:c r="C434" s="82"/>
-      <x:c r="D434" s="82"/>
-      <x:c r="E434" s="82"/>
-      <x:c r="F434" s="82"/>
-      <x:c r="G434" s="82"/>
-      <x:c r="H434" s="82"/>
-      <x:c r="I434" s="82"/>
-      <x:c r="J434" s="82"/>
-    </x:row>
-    <x:row r="435">
-      <x:c r="A435" s="84"/>
-      <x:c r="B435" s="83"/>
-      <x:c r="C435" s="82"/>
-      <x:c r="D435" s="82"/>
-      <x:c r="E435" s="82"/>
-      <x:c r="F435" s="82"/>
-      <x:c r="G435" s="82"/>
-      <x:c r="H435" s="82"/>
-      <x:c r="I435" s="82"/>
-      <x:c r="J435" s="82"/>
-    </x:row>
-    <x:row r="436">
-      <x:c r="A436" s="84"/>
-      <x:c r="B436" s="83"/>
-      <x:c r="C436" s="82"/>
-      <x:c r="D436" s="82"/>
-      <x:c r="E436" s="82"/>
-      <x:c r="F436" s="82"/>
-      <x:c r="G436" s="82"/>
-      <x:c r="H436" s="82"/>
-      <x:c r="I436" s="82"/>
-      <x:c r="J436" s="82"/>
-    </x:row>
-    <x:row r="437">
-      <x:c r="A437" s="84"/>
-      <x:c r="B437" s="83"/>
-      <x:c r="C437" s="82"/>
-      <x:c r="D437" s="82"/>
-      <x:c r="E437" s="82"/>
-      <x:c r="F437" s="82"/>
-      <x:c r="G437" s="82"/>
-      <x:c r="H437" s="82"/>
-      <x:c r="I437" s="82"/>
-      <x:c r="J437" s="82"/>
-    </x:row>
-    <x:row r="438">
-      <x:c r="A438" s="84"/>
-      <x:c r="B438" s="83"/>
-      <x:c r="C438" s="82"/>
-      <x:c r="D438" s="82"/>
-      <x:c r="E438" s="82"/>
-      <x:c r="F438" s="82"/>
-      <x:c r="G438" s="82"/>
-      <x:c r="H438" s="82"/>
-      <x:c r="I438" s="82"/>
-      <x:c r="J438" s="82"/>
-    </x:row>
-    <x:row r="439">
-      <x:c r="A439" s="84"/>
-      <x:c r="B439" s="83"/>
-      <x:c r="C439" s="82"/>
-      <x:c r="D439" s="82"/>
-      <x:c r="E439" s="82"/>
-      <x:c r="F439" s="82"/>
-      <x:c r="G439" s="82"/>
-      <x:c r="H439" s="82"/>
-      <x:c r="I439" s="82"/>
-      <x:c r="J439" s="82"/>
-    </x:row>
-    <x:row r="440">
-      <x:c r="A440" s="84"/>
-      <x:c r="B440" s="83"/>
-      <x:c r="C440" s="82"/>
-      <x:c r="D440" s="82"/>
-      <x:c r="E440" s="82"/>
-      <x:c r="F440" s="82"/>
-      <x:c r="G440" s="82"/>
-      <x:c r="H440" s="82"/>
-      <x:c r="I440" s="82"/>
-      <x:c r="J440" s="82"/>
-    </x:row>
-    <x:row r="441">
-      <x:c r="A441" s="84"/>
-      <x:c r="B441" s="83"/>
-      <x:c r="C441" s="82"/>
-      <x:c r="D441" s="82"/>
-      <x:c r="E441" s="82"/>
-      <x:c r="F441" s="82"/>
-      <x:c r="G441" s="82"/>
-      <x:c r="H441" s="82"/>
-      <x:c r="I441" s="82"/>
-      <x:c r="J441" s="82"/>
-    </x:row>
-    <x:row r="442">
-      <x:c r="A442" s="84"/>
-      <x:c r="B442" s="83"/>
-      <x:c r="C442" s="82"/>
-      <x:c r="D442" s="82"/>
-      <x:c r="E442" s="82"/>
-      <x:c r="F442" s="82"/>
-      <x:c r="G442" s="82"/>
-      <x:c r="H442" s="82"/>
-      <x:c r="I442" s="82"/>
-      <x:c r="J442" s="82"/>
-    </x:row>
-    <x:row r="443">
-      <x:c r="A443" s="84"/>
-      <x:c r="B443" s="83"/>
-      <x:c r="C443" s="82"/>
-      <x:c r="D443" s="82"/>
-      <x:c r="E443" s="82"/>
-      <x:c r="F443" s="82"/>
-      <x:c r="G443" s="82"/>
-      <x:c r="H443" s="82"/>
-      <x:c r="I443" s="82"/>
-      <x:c r="J443" s="82"/>
-    </x:row>
-    <x:row r="444">
-      <x:c r="A444" s="84"/>
-      <x:c r="B444" s="83"/>
-      <x:c r="C444" s="82"/>
-      <x:c r="D444" s="82"/>
-      <x:c r="E444" s="82"/>
-      <x:c r="F444" s="82"/>
-      <x:c r="G444" s="82"/>
-      <x:c r="H444" s="82"/>
-      <x:c r="I444" s="82"/>
-      <x:c r="J444" s="82"/>
-    </x:row>
-    <x:row r="445">
-      <x:c r="A445" s="84"/>
-      <x:c r="B445" s="83"/>
-      <x:c r="C445" s="82"/>
-      <x:c r="D445" s="82"/>
-      <x:c r="E445" s="82"/>
-      <x:c r="F445" s="82"/>
-      <x:c r="G445" s="82"/>
-      <x:c r="H445" s="82"/>
-      <x:c r="I445" s="82"/>
-      <x:c r="J445" s="82"/>
-    </x:row>
-    <x:row r="446">
-      <x:c r="A446" s="84"/>
-      <x:c r="B446" s="83"/>
-      <x:c r="C446" s="82"/>
-      <x:c r="D446" s="82"/>
-      <x:c r="E446" s="82"/>
-      <x:c r="F446" s="82"/>
-      <x:c r="G446" s="82"/>
-      <x:c r="H446" s="82"/>
-      <x:c r="I446" s="82"/>
-      <x:c r="J446" s="82"/>
-    </x:row>
-    <x:row r="447">
-      <x:c r="A447" s="84"/>
-      <x:c r="B447" s="83"/>
-      <x:c r="C447" s="82"/>
-      <x:c r="D447" s="82"/>
-      <x:c r="E447" s="82"/>
-      <x:c r="F447" s="82"/>
-      <x:c r="G447" s="82"/>
-      <x:c r="H447" s="82"/>
-      <x:c r="I447" s="82"/>
-      <x:c r="J447" s="82"/>
-    </x:row>
-    <x:row r="448">
-      <x:c r="A448" s="84"/>
-      <x:c r="B448" s="83"/>
-      <x:c r="C448" s="82"/>
-      <x:c r="D448" s="82"/>
-      <x:c r="E448" s="82"/>
-      <x:c r="F448" s="82"/>
-      <x:c r="G448" s="82"/>
-      <x:c r="H448" s="82"/>
-      <x:c r="I448" s="82"/>
-      <x:c r="J448" s="82"/>
-    </x:row>
-    <x:row r="449">
-      <x:c r="A449" s="84"/>
-      <x:c r="B449" s="83"/>
-      <x:c r="C449" s="82"/>
-      <x:c r="D449" s="82"/>
-      <x:c r="E449" s="82"/>
-      <x:c r="F449" s="82"/>
-      <x:c r="G449" s="82"/>
-      <x:c r="H449" s="82"/>
-      <x:c r="I449" s="82"/>
-      <x:c r="J449" s="82"/>
-    </x:row>
-    <x:row r="450">
-      <x:c r="A450" s="84"/>
-      <x:c r="B450" s="83"/>
-      <x:c r="C450" s="82"/>
-      <x:c r="D450" s="82"/>
-      <x:c r="E450" s="82"/>
-      <x:c r="F450" s="82"/>
-      <x:c r="G450" s="82"/>
-      <x:c r="H450" s="82"/>
-      <x:c r="I450" s="82"/>
-      <x:c r="J450" s="82"/>
-    </x:row>
-    <x:row r="451">
-      <x:c r="A451" s="84"/>
-      <x:c r="B451" s="83"/>
-      <x:c r="C451" s="82"/>
-      <x:c r="D451" s="82"/>
-      <x:c r="E451" s="82"/>
-      <x:c r="F451" s="82"/>
-      <x:c r="G451" s="82"/>
-      <x:c r="H451" s="82"/>
-      <x:c r="I451" s="82"/>
-      <x:c r="J451" s="82"/>
-    </x:row>
-    <x:row r="452">
-      <x:c r="A452" s="84"/>
-      <x:c r="B452" s="83"/>
-      <x:c r="C452" s="82"/>
-      <x:c r="D452" s="82"/>
-      <x:c r="E452" s="82"/>
-      <x:c r="F452" s="82"/>
-      <x:c r="G452" s="82"/>
-      <x:c r="H452" s="82"/>
-      <x:c r="I452" s="82"/>
-      <x:c r="J452" s="82"/>
-    </x:row>
-    <x:row r="453">
-      <x:c r="A453" s="84"/>
-      <x:c r="B453" s="83"/>
-      <x:c r="C453" s="82"/>
-      <x:c r="D453" s="82"/>
-      <x:c r="E453" s="82"/>
-      <x:c r="F453" s="82"/>
-      <x:c r="G453" s="82"/>
-      <x:c r="H453" s="82"/>
-      <x:c r="I453" s="82"/>
-      <x:c r="J453" s="82"/>
-    </x:row>
-    <x:row r="454">
-      <x:c r="A454" s="84"/>
-      <x:c r="B454" s="83"/>
-      <x:c r="C454" s="82"/>
-      <x:c r="D454" s="82"/>
-      <x:c r="E454" s="82"/>
-      <x:c r="F454" s="82"/>
-      <x:c r="G454" s="82"/>
-      <x:c r="H454" s="82"/>
-      <x:c r="I454" s="82"/>
-      <x:c r="J454" s="82"/>
-    </x:row>
-    <x:row r="455">
-      <x:c r="A455" s="84"/>
-      <x:c r="B455" s="83"/>
-      <x:c r="C455" s="82"/>
-      <x:c r="D455" s="82"/>
-      <x:c r="E455" s="82"/>
-      <x:c r="F455" s="82"/>
-      <x:c r="G455" s="82"/>
-      <x:c r="H455" s="82"/>
-      <x:c r="I455" s="82"/>
-      <x:c r="J455" s="82"/>
-    </x:row>
-    <x:row r="456">
-      <x:c r="A456" s="84"/>
-      <x:c r="B456" s="83"/>
-      <x:c r="C456" s="82"/>
-      <x:c r="D456" s="82"/>
-      <x:c r="E456" s="82"/>
-      <x:c r="F456" s="82"/>
-      <x:c r="G456" s="82"/>
-      <x:c r="H456" s="82"/>
-      <x:c r="I456" s="82"/>
-      <x:c r="J456" s="82"/>
-    </x:row>
-    <x:row r="457">
-      <x:c r="A457" s="84"/>
-      <x:c r="B457" s="83"/>
-      <x:c r="C457" s="82"/>
-      <x:c r="D457" s="82"/>
-      <x:c r="E457" s="82"/>
-      <x:c r="F457" s="82"/>
-      <x:c r="G457" s="82"/>
-      <x:c r="H457" s="82"/>
-      <x:c r="I457" s="82"/>
-      <x:c r="J457" s="82"/>
-    </x:row>
-    <x:row r="458">
-      <x:c r="A458" s="84"/>
-      <x:c r="B458" s="83"/>
-      <x:c r="C458" s="82"/>
-      <x:c r="D458" s="82"/>
-      <x:c r="E458" s="82"/>
-      <x:c r="F458" s="82"/>
-      <x:c r="G458" s="82"/>
-      <x:c r="H458" s="82"/>
-      <x:c r="I458" s="82"/>
-      <x:c r="J458" s="82"/>
-    </x:row>
-    <x:row r="459">
-      <x:c r="A459" s="84"/>
-      <x:c r="B459" s="83"/>
-      <x:c r="C459" s="82"/>
-      <x:c r="D459" s="82"/>
-      <x:c r="E459" s="82"/>
-      <x:c r="F459" s="82"/>
-      <x:c r="G459" s="82"/>
-      <x:c r="H459" s="82"/>
-      <x:c r="I459" s="82"/>
-      <x:c r="J459" s="82"/>
-    </x:row>
-    <x:row r="460">
-      <x:c r="A460" s="84"/>
-      <x:c r="B460" s="83"/>
-      <x:c r="C460" s="82"/>
-      <x:c r="D460" s="82"/>
-      <x:c r="E460" s="82"/>
-      <x:c r="F460" s="82"/>
-      <x:c r="G460" s="82"/>
-      <x:c r="H460" s="82"/>
-      <x:c r="I460" s="82"/>
-      <x:c r="J460" s="82"/>
-    </x:row>
-    <x:row r="461">
-      <x:c r="A461" s="84"/>
-      <x:c r="B461" s="83"/>
-      <x:c r="C461" s="82"/>
-      <x:c r="D461" s="82"/>
-      <x:c r="E461" s="82"/>
-      <x:c r="F461" s="82"/>
-      <x:c r="G461" s="82"/>
-      <x:c r="H461" s="82"/>
-      <x:c r="I461" s="82"/>
-      <x:c r="J461" s="82"/>
-    </x:row>
-    <x:row r="462">
-      <x:c r="A462" s="84"/>
-      <x:c r="B462" s="83"/>
-      <x:c r="C462" s="82"/>
-      <x:c r="D462" s="82"/>
-      <x:c r="E462" s="82"/>
-      <x:c r="F462" s="82"/>
-      <x:c r="G462" s="82"/>
-      <x:c r="H462" s="82"/>
-      <x:c r="I462" s="82"/>
-      <x:c r="J462" s="82"/>
-    </x:row>
-    <x:row r="463">
-      <x:c r="A463" s="84"/>
-      <x:c r="B463" s="83"/>
-      <x:c r="C463" s="82"/>
-      <x:c r="D463" s="82"/>
-      <x:c r="E463" s="82"/>
-      <x:c r="F463" s="82"/>
-      <x:c r="G463" s="82"/>
-      <x:c r="H463" s="82"/>
-      <x:c r="I463" s="82"/>
-      <x:c r="J463" s="82"/>
-    </x:row>
-    <x:row r="464">
-      <x:c r="A464" s="84"/>
-      <x:c r="B464" s="83"/>
-      <x:c r="C464" s="82"/>
-      <x:c r="D464" s="82"/>
-      <x:c r="E464" s="82"/>
-      <x:c r="F464" s="82"/>
-      <x:c r="G464" s="82"/>
-      <x:c r="H464" s="82"/>
-      <x:c r="I464" s="82"/>
-      <x:c r="J464" s="82"/>
-    </x:row>
-    <x:row r="465">
-      <x:c r="A465" s="84"/>
-      <x:c r="B465" s="83"/>
-      <x:c r="C465" s="82"/>
-      <x:c r="D465" s="82"/>
-      <x:c r="E465" s="82"/>
-      <x:c r="F465" s="82"/>
-      <x:c r="G465" s="82"/>
-      <x:c r="H465" s="82"/>
-      <x:c r="I465" s="82"/>
-      <x:c r="J465" s="82"/>
-    </x:row>
-    <x:row r="466">
-      <x:c r="A466" s="84"/>
-      <x:c r="B466" s="83"/>
-      <x:c r="C466" s="82"/>
-      <x:c r="D466" s="82"/>
-      <x:c r="E466" s="82"/>
-      <x:c r="F466" s="82"/>
-      <x:c r="G466" s="82"/>
-      <x:c r="H466" s="82"/>
-      <x:c r="I466" s="82"/>
-      <x:c r="J466" s="82"/>
-    </x:row>
-    <x:row r="467">
-      <x:c r="A467" s="84"/>
-      <x:c r="B467" s="83"/>
-      <x:c r="C467" s="82"/>
-      <x:c r="D467" s="82"/>
-      <x:c r="E467" s="82"/>
-      <x:c r="F467" s="82"/>
-      <x:c r="G467" s="82"/>
-      <x:c r="H467" s="82"/>
-      <x:c r="I467" s="82"/>
-      <x:c r="J467" s="82"/>
-    </x:row>
-    <x:row r="468">
-      <x:c r="A468" s="84"/>
-      <x:c r="B468" s="83"/>
-      <x:c r="C468" s="82"/>
-      <x:c r="D468" s="82"/>
-      <x:c r="E468" s="82"/>
-      <x:c r="F468" s="82"/>
-      <x:c r="G468" s="82"/>
-      <x:c r="H468" s="82"/>
-      <x:c r="I468" s="82"/>
-      <x:c r="J468" s="82"/>
-    </x:row>
-    <x:row r="469">
-      <x:c r="A469" s="84"/>
-      <x:c r="B469" s="83"/>
-      <x:c r="C469" s="82"/>
-      <x:c r="D469" s="82"/>
-      <x:c r="E469" s="82"/>
-      <x:c r="F469" s="82"/>
-      <x:c r="G469" s="82"/>
-      <x:c r="H469" s="82"/>
-      <x:c r="I469" s="82"/>
-      <x:c r="J469" s="82"/>
-    </x:row>
-    <x:row r="470">
-      <x:c r="A470" s="84"/>
-      <x:c r="B470" s="83"/>
-      <x:c r="C470" s="82"/>
-      <x:c r="D470" s="82"/>
-      <x:c r="E470" s="82"/>
-      <x:c r="F470" s="82"/>
-      <x:c r="G470" s="82"/>
-      <x:c r="H470" s="82"/>
-      <x:c r="I470" s="82"/>
-      <x:c r="J470" s="82"/>
-    </x:row>
-    <x:row r="471">
-      <x:c r="A471" s="84"/>
-      <x:c r="B471" s="83"/>
-      <x:c r="C471" s="82"/>
-      <x:c r="D471" s="82"/>
-      <x:c r="E471" s="82"/>
-      <x:c r="F471" s="82"/>
-      <x:c r="G471" s="82"/>
-      <x:c r="H471" s="82"/>
-      <x:c r="I471" s="82"/>
-      <x:c r="J471" s="82"/>
-    </x:row>
-    <x:row r="472">
-      <x:c r="A472" s="84"/>
-      <x:c r="B472" s="83"/>
-      <x:c r="C472" s="82"/>
-      <x:c r="D472" s="82"/>
-      <x:c r="E472" s="82"/>
-      <x:c r="F472" s="82"/>
-      <x:c r="G472" s="82"/>
-      <x:c r="H472" s="82"/>
-      <x:c r="I472" s="82"/>
-      <x:c r="J472" s="82"/>
-    </x:row>
-    <x:row r="473">
-      <x:c r="A473" s="84"/>
-      <x:c r="B473" s="83"/>
-      <x:c r="C473" s="82"/>
-      <x:c r="D473" s="82"/>
-      <x:c r="E473" s="82"/>
-      <x:c r="F473" s="82"/>
-      <x:c r="G473" s="82"/>
-      <x:c r="H473" s="82"/>
-      <x:c r="I473" s="82"/>
-      <x:c r="J473" s="82"/>
-    </x:row>
-    <x:row r="474">
-      <x:c r="A474" s="84"/>
-      <x:c r="B474" s="83"/>
-      <x:c r="C474" s="82"/>
-      <x:c r="D474" s="82"/>
-      <x:c r="E474" s="82"/>
-      <x:c r="F474" s="82"/>
-      <x:c r="G474" s="82"/>
-      <x:c r="H474" s="82"/>
-      <x:c r="I474" s="82"/>
-      <x:c r="J474" s="82"/>
-    </x:row>
-    <x:row r="475">
-      <x:c r="A475" s="84"/>
-      <x:c r="B475" s="83"/>
-      <x:c r="C475" s="82"/>
-      <x:c r="D475" s="82"/>
-      <x:c r="E475" s="82"/>
-      <x:c r="F475" s="82"/>
-      <x:c r="G475" s="82"/>
-      <x:c r="H475" s="82"/>
-      <x:c r="I475" s="82"/>
-      <x:c r="J475" s="82"/>
-    </x:row>
-    <x:row r="476">
-      <x:c r="A476" s="84"/>
-      <x:c r="B476" s="83"/>
-      <x:c r="C476" s="82"/>
-      <x:c r="D476" s="82"/>
-      <x:c r="E476" s="82"/>
-      <x:c r="F476" s="82"/>
-      <x:c r="G476" s="82"/>
-      <x:c r="H476" s="82"/>
-      <x:c r="I476" s="82"/>
-      <x:c r="J476" s="82"/>
-    </x:row>
-    <x:row r="477">
-      <x:c r="A477" s="84"/>
-      <x:c r="B477" s="83"/>
-      <x:c r="C477" s="82"/>
-      <x:c r="D477" s="82"/>
-      <x:c r="E477" s="82"/>
-      <x:c r="F477" s="82"/>
-      <x:c r="G477" s="82"/>
-      <x:c r="H477" s="82"/>
-      <x:c r="I477" s="82"/>
-      <x:c r="J477" s="82"/>
-    </x:row>
-    <x:row r="478">
-      <x:c r="A478" s="84"/>
-      <x:c r="B478" s="83"/>
-      <x:c r="C478" s="82"/>
-      <x:c r="D478" s="82"/>
-      <x:c r="E478" s="82"/>
-      <x:c r="F478" s="82"/>
-      <x:c r="G478" s="82"/>
-      <x:c r="H478" s="82"/>
-      <x:c r="I478" s="82"/>
-      <x:c r="J478" s="82"/>
-    </x:row>
-    <x:row r="479">
-      <x:c r="A479" s="84"/>
-      <x:c r="B479" s="83"/>
-      <x:c r="C479" s="82"/>
-      <x:c r="D479" s="82"/>
-      <x:c r="E479" s="82"/>
-      <x:c r="F479" s="82"/>
-      <x:c r="G479" s="82"/>
-      <x:c r="H479" s="82"/>
-      <x:c r="I479" s="82"/>
-      <x:c r="J479" s="82"/>
-    </x:row>
-    <x:row r="480">
-      <x:c r="A480" s="84"/>
-      <x:c r="B480" s="83"/>
-      <x:c r="C480" s="82"/>
-      <x:c r="D480" s="82"/>
-      <x:c r="E480" s="82"/>
-      <x:c r="F480" s="82"/>
-      <x:c r="G480" s="82"/>
-      <x:c r="H480" s="82"/>
-      <x:c r="I480" s="82"/>
-      <x:c r="J480" s="82"/>
-    </x:row>
-    <x:row r="481">
-      <x:c r="A481" s="84"/>
-      <x:c r="B481" s="83"/>
-      <x:c r="C481" s="82"/>
-      <x:c r="D481" s="82"/>
-      <x:c r="E481" s="82"/>
-      <x:c r="F481" s="82"/>
-      <x:c r="G481" s="82"/>
-      <x:c r="H481" s="82"/>
-      <x:c r="I481" s="82"/>
-      <x:c r="J481" s="82"/>
-    </x:row>
-    <x:row r="482">
-      <x:c r="A482" s="84"/>
-      <x:c r="B482" s="83"/>
-      <x:c r="C482" s="82"/>
-      <x:c r="D482" s="82"/>
-      <x:c r="E482" s="82"/>
-      <x:c r="F482" s="82"/>
-      <x:c r="G482" s="82"/>
-      <x:c r="H482" s="82"/>
-      <x:c r="I482" s="82"/>
-      <x:c r="J482" s="82"/>
-    </x:row>
-    <x:row r="483">
-      <x:c r="A483" s="84"/>
-      <x:c r="B483" s="83"/>
-      <x:c r="C483" s="82"/>
-      <x:c r="D483" s="82"/>
-      <x:c r="E483" s="82"/>
-      <x:c r="F483" s="82"/>
-      <x:c r="G483" s="82"/>
-      <x:c r="H483" s="82"/>
-      <x:c r="I483" s="82"/>
-      <x:c r="J483" s="82"/>
-    </x:row>
-    <x:row r="484">
-      <x:c r="A484" s="84"/>
-      <x:c r="B484" s="83"/>
-      <x:c r="C484" s="82"/>
-      <x:c r="D484" s="82"/>
-      <x:c r="E484" s="82"/>
-      <x:c r="F484" s="82"/>
-      <x:c r="G484" s="82"/>
-      <x:c r="H484" s="82"/>
-      <x:c r="I484" s="82"/>
-      <x:c r="J484" s="82"/>
-    </x:row>
-    <x:row r="485">
-      <x:c r="A485" s="84"/>
-      <x:c r="B485" s="83"/>
-      <x:c r="C485" s="82"/>
-      <x:c r="D485" s="82"/>
-      <x:c r="E485" s="82"/>
-      <x:c r="F485" s="82"/>
-      <x:c r="G485" s="82"/>
-      <x:c r="H485" s="82"/>
-      <x:c r="I485" s="82"/>
-      <x:c r="J485" s="82"/>
-    </x:row>
-    <x:row r="486">
-      <x:c r="A486" s="84"/>
-      <x:c r="B486" s="83"/>
-      <x:c r="C486" s="82"/>
-      <x:c r="D486" s="82"/>
-      <x:c r="E486" s="82"/>
-      <x:c r="F486" s="82"/>
-      <x:c r="G486" s="82"/>
-      <x:c r="H486" s="82"/>
-      <x:c r="I486" s="82"/>
-      <x:c r="J486" s="82"/>
-    </x:row>
-    <x:row r="487">
-      <x:c r="A487" s="84"/>
-      <x:c r="B487" s="83"/>
-      <x:c r="C487" s="82"/>
-      <x:c r="D487" s="82"/>
-      <x:c r="E487" s="82"/>
-      <x:c r="F487" s="82"/>
-      <x:c r="G487" s="82"/>
-      <x:c r="H487" s="82"/>
-      <x:c r="I487" s="82"/>
-      <x:c r="J487" s="82"/>
-    </x:row>
-    <x:row r="488">
-      <x:c r="A488" s="84"/>
-      <x:c r="B488" s="83"/>
-      <x:c r="C488" s="82"/>
-      <x:c r="D488" s="82"/>
-      <x:c r="E488" s="82"/>
-      <x:c r="F488" s="82"/>
-      <x:c r="G488" s="82"/>
-      <x:c r="H488" s="82"/>
-      <x:c r="I488" s="82"/>
-      <x:c r="J488" s="82"/>
-    </x:row>
-    <x:row r="489">
-      <x:c r="A489" s="84"/>
-      <x:c r="B489" s="83"/>
-      <x:c r="C489" s="82"/>
-      <x:c r="D489" s="82"/>
-      <x:c r="E489" s="82"/>
-      <x:c r="F489" s="82"/>
-      <x:c r="G489" s="82"/>
-      <x:c r="H489" s="82"/>
-      <x:c r="I489" s="82"/>
-      <x:c r="J489" s="82"/>
-    </x:row>
-    <x:row r="490">
-      <x:c r="A490" s="84"/>
-      <x:c r="B490" s="83"/>
-      <x:c r="C490" s="82"/>
-      <x:c r="D490" s="82"/>
-      <x:c r="E490" s="82"/>
-      <x:c r="F490" s="82"/>
-      <x:c r="G490" s="82"/>
-      <x:c r="H490" s="82"/>
-      <x:c r="I490" s="82"/>
-      <x:c r="J490" s="82"/>
-    </x:row>
-    <x:row r="491">
-      <x:c r="A491" s="84"/>
-      <x:c r="B491" s="83"/>
-      <x:c r="C491" s="82"/>
-      <x:c r="D491" s="82"/>
-      <x:c r="E491" s="82"/>
-      <x:c r="F491" s="82"/>
-      <x:c r="G491" s="82"/>
-      <x:c r="H491" s="82"/>
-      <x:c r="I491" s="82"/>
-      <x:c r="J491" s="82"/>
-    </x:row>
-    <x:row r="492">
-      <x:c r="A492" s="84"/>
-      <x:c r="B492" s="83"/>
-      <x:c r="C492" s="82"/>
-      <x:c r="D492" s="82"/>
-      <x:c r="E492" s="82"/>
-      <x:c r="F492" s="82"/>
-      <x:c r="G492" s="82"/>
-      <x:c r="H492" s="82"/>
-      <x:c r="I492" s="82"/>
-      <x:c r="J492" s="82"/>
-    </x:row>
-    <x:row r="493">
-      <x:c r="A493" s="84"/>
-      <x:c r="B493" s="83"/>
-      <x:c r="C493" s="82"/>
-      <x:c r="D493" s="82"/>
-      <x:c r="E493" s="82"/>
-      <x:c r="F493" s="82"/>
-      <x:c r="G493" s="82"/>
-      <x:c r="H493" s="82"/>
-      <x:c r="I493" s="82"/>
-      <x:c r="J493" s="82"/>
-    </x:row>
-    <x:row r="494">
-      <x:c r="A494" s="84"/>
-      <x:c r="B494" s="83"/>
-      <x:c r="C494" s="82"/>
-      <x:c r="D494" s="82"/>
-      <x:c r="E494" s="82"/>
-      <x:c r="F494" s="82"/>
-      <x:c r="G494" s="82"/>
-      <x:c r="H494" s="82"/>
-      <x:c r="I494" s="82"/>
-      <x:c r="J494" s="82"/>
-    </x:row>
-    <x:row r="495">
-      <x:c r="A495" s="84"/>
-      <x:c r="B495" s="83"/>
-      <x:c r="C495" s="82"/>
-      <x:c r="D495" s="82"/>
-      <x:c r="E495" s="82"/>
-      <x:c r="F495" s="82"/>
-      <x:c r="G495" s="82"/>
-      <x:c r="H495" s="82"/>
-      <x:c r="I495" s="82"/>
-      <x:c r="J495" s="82"/>
-    </x:row>
-    <x:row r="496">
-      <x:c r="A496" s="84"/>
-      <x:c r="B496" s="83"/>
-      <x:c r="C496" s="82"/>
-      <x:c r="D496" s="82"/>
-      <x:c r="E496" s="82"/>
-      <x:c r="F496" s="82"/>
-      <x:c r="G496" s="82"/>
-      <x:c r="H496" s="82"/>
-      <x:c r="I496" s="82"/>
-      <x:c r="J496" s="82"/>
-    </x:row>
-    <x:row r="497">
-      <x:c r="A497" s="84"/>
-      <x:c r="B497" s="83"/>
-      <x:c r="C497" s="82"/>
-      <x:c r="D497" s="82"/>
-      <x:c r="E497" s="82"/>
-      <x:c r="F497" s="82"/>
-      <x:c r="G497" s="82"/>
-      <x:c r="H497" s="82"/>
-      <x:c r="I497" s="82"/>
-      <x:c r="J497" s="82"/>
-    </x:row>
-    <x:row r="498">
-      <x:c r="A498" s="84"/>
-      <x:c r="B498" s="83"/>
-      <x:c r="C498" s="82"/>
-      <x:c r="D498" s="82"/>
-      <x:c r="E498" s="82"/>
-      <x:c r="F498" s="82"/>
-      <x:c r="G498" s="82"/>
-      <x:c r="H498" s="82"/>
-      <x:c r="I498" s="82"/>
-      <x:c r="J498" s="82"/>
-    </x:row>
-    <x:row r="499">
-      <x:c r="A499" s="84"/>
-      <x:c r="B499" s="83"/>
-      <x:c r="C499" s="82"/>
-      <x:c r="D499" s="82"/>
-      <x:c r="E499" s="82"/>
-      <x:c r="F499" s="82"/>
-      <x:c r="G499" s="82"/>
-      <x:c r="H499" s="82"/>
-      <x:c r="I499" s="82"/>
-      <x:c r="J499" s="82"/>
-    </x:row>
-    <x:row r="500">
-      <x:c r="A500" s="84"/>
-      <x:c r="B500" s="83"/>
-      <x:c r="C500" s="82"/>
-      <x:c r="D500" s="82"/>
-      <x:c r="E500" s="82"/>
-      <x:c r="F500" s="82"/>
-      <x:c r="G500" s="82"/>
-      <x:c r="H500" s="82"/>
-      <x:c r="I500" s="82"/>
-      <x:c r="J500" s="82"/>
-    </x:row>
-  </x:sheetData>
-  <x:conditionalFormatting sqref="I2:I500">
-    <x:cfRule type="expression" dxfId="7" priority="1">
-      <x:formula>I2="ROT"</x:formula>
-    </x:cfRule>
-    <x:cfRule type="expression" dxfId="8" priority="2">
-      <x:formula>I2="GELB"</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="A2:A201">
-    <x:cfRule type="containsText" dxfId="85" priority="3" operator="containsText" text="GRUEN"/>
-    <x:cfRule type="containsText" dxfId="86" priority="4" operator="containsText" text="GELB"/>
-    <x:cfRule type="containsText" dxfId="87" priority="5" operator="containsText" text="ROT"/>
-    <x:cfRule type="containsText" dxfId="88" priority="6" operator="containsText" text="NICHT_PRUEFBAR"/>
-  </x:conditionalFormatting>
-  <x:dataValidations count="4">
-    <x:dataValidation type="list" sqref="I2:I500">
-      <x:formula1>"GELB,ROT"</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="list" sqref="J2:J500">
-      <x:formula1>"Offen,In Bearbeitung,Erledigt"</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="list" sqref="J2:J201">
-      <x:formula1>"Offen,In Bearbeitung,Erledigt"</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="list" sqref="A2:A201">
-      <x:formula1>"GRUEN,GELB,ROT,NICHT_PRUEFBAR"</x:formula1>
-    </x:dataValidation>
-  </x:dataValidations>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="10" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="68" hidden="0" customWidth="1"/>
@@ -34595,4 +28636,3290 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="13" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="15" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="19" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="24" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="30" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="34" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="26" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="55" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="21" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="28" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="42" customHeight="1">
+      <x:c r="A1" s="187" t="str">
+        <x:v>Ampel</x:v>
+      </x:c>
+      <x:c r="B1" s="187" t="str">
+        <x:v>Datum</x:v>
+      </x:c>
+      <x:c r="C1" s="187" t="str">
+        <x:v>Betrag</x:v>
+      </x:c>
+      <x:c r="D1" s="187" t="str">
+        <x:v>Alter in Monaten</x:v>
+      </x:c>
+      <x:c r="E1" s="187" t="str">
+        <x:v>Konto</x:v>
+      </x:c>
+      <x:c r="F1" s="187" t="str">
+        <x:v>Gegenkonto</x:v>
+      </x:c>
+      <x:c r="G1" s="187" t="str">
+        <x:v>Zahlungsrichtung</x:v>
+      </x:c>
+      <x:c r="H1" s="187" t="str">
+        <x:v>Zahlungspartner</x:v>
+      </x:c>
+      <x:c r="I1" s="187" t="str">
+        <x:v>Vorgang/Leistungsbezug</x:v>
+      </x:c>
+      <x:c r="J1" s="187" t="str">
+        <x:v>Buchungstext DATEV</x:v>
+      </x:c>
+      <x:c r="K1" s="187" t="str">
+        <x:v>Beanstandung</x:v>
+      </x:c>
+      <x:c r="L1" s="187" t="str">
+        <x:v>Versandfertiger Mandantentext</x:v>
+      </x:c>
+      <x:c r="M1" s="187" t="str">
+        <x:v>Bearbeitungsstatus</x:v>
+      </x:c>
+      <x:c r="N1" s="187" t="str">
+        <x:v>Kommentar</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="206"/>
+      <x:c r="B2" s="188"/>
+      <x:c r="C2" s="191"/>
+      <x:c r="D2" s="194"/>
+      <x:c r="E2" s="174"/>
+      <x:c r="F2" s="174"/>
+      <x:c r="G2" s="197"/>
+      <x:c r="H2" s="197"/>
+      <x:c r="I2" s="197"/>
+      <x:c r="J2" s="197"/>
+      <x:c r="K2" s="197"/>
+      <x:c r="L2" s="197"/>
+      <x:c r="M2" s="197"/>
+      <x:c r="N2" s="203"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="207"/>
+      <x:c r="B3" s="189"/>
+      <x:c r="C3" s="192"/>
+      <x:c r="D3" s="195"/>
+      <x:c r="E3" s="177"/>
+      <x:c r="F3" s="177"/>
+      <x:c r="G3" s="199"/>
+      <x:c r="H3" s="199"/>
+      <x:c r="I3" s="199"/>
+      <x:c r="J3" s="199"/>
+      <x:c r="K3" s="199"/>
+      <x:c r="L3" s="199"/>
+      <x:c r="M3" s="199"/>
+      <x:c r="N3" s="204"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="207"/>
+      <x:c r="B4" s="189"/>
+      <x:c r="C4" s="192"/>
+      <x:c r="D4" s="195"/>
+      <x:c r="E4" s="177"/>
+      <x:c r="F4" s="177"/>
+      <x:c r="G4" s="199"/>
+      <x:c r="H4" s="199"/>
+      <x:c r="I4" s="199"/>
+      <x:c r="J4" s="199"/>
+      <x:c r="K4" s="199"/>
+      <x:c r="L4" s="199"/>
+      <x:c r="M4" s="199"/>
+      <x:c r="N4" s="204"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="207"/>
+      <x:c r="B5" s="189"/>
+      <x:c r="C5" s="192"/>
+      <x:c r="D5" s="195"/>
+      <x:c r="E5" s="177"/>
+      <x:c r="F5" s="177"/>
+      <x:c r="G5" s="199"/>
+      <x:c r="H5" s="199"/>
+      <x:c r="I5" s="199"/>
+      <x:c r="J5" s="199"/>
+      <x:c r="K5" s="199"/>
+      <x:c r="L5" s="199"/>
+      <x:c r="M5" s="199"/>
+      <x:c r="N5" s="204"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="207"/>
+      <x:c r="B6" s="189"/>
+      <x:c r="C6" s="192"/>
+      <x:c r="D6" s="195"/>
+      <x:c r="E6" s="177"/>
+      <x:c r="F6" s="177"/>
+      <x:c r="G6" s="199"/>
+      <x:c r="H6" s="199"/>
+      <x:c r="I6" s="199"/>
+      <x:c r="J6" s="199"/>
+      <x:c r="K6" s="199"/>
+      <x:c r="L6" s="199"/>
+      <x:c r="M6" s="199"/>
+      <x:c r="N6" s="204"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="207"/>
+      <x:c r="B7" s="189"/>
+      <x:c r="C7" s="192"/>
+      <x:c r="D7" s="195"/>
+      <x:c r="E7" s="177"/>
+      <x:c r="F7" s="177"/>
+      <x:c r="G7" s="199"/>
+      <x:c r="H7" s="199"/>
+      <x:c r="I7" s="199"/>
+      <x:c r="J7" s="199"/>
+      <x:c r="K7" s="199"/>
+      <x:c r="L7" s="199"/>
+      <x:c r="M7" s="199"/>
+      <x:c r="N7" s="204"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="207"/>
+      <x:c r="B8" s="189"/>
+      <x:c r="C8" s="192"/>
+      <x:c r="D8" s="195"/>
+      <x:c r="E8" s="177"/>
+      <x:c r="F8" s="177"/>
+      <x:c r="G8" s="199"/>
+      <x:c r="H8" s="199"/>
+      <x:c r="I8" s="199"/>
+      <x:c r="J8" s="199"/>
+      <x:c r="K8" s="199"/>
+      <x:c r="L8" s="199"/>
+      <x:c r="M8" s="199"/>
+      <x:c r="N8" s="204"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="207"/>
+      <x:c r="B9" s="189"/>
+      <x:c r="C9" s="192"/>
+      <x:c r="D9" s="195"/>
+      <x:c r="E9" s="177"/>
+      <x:c r="F9" s="177"/>
+      <x:c r="G9" s="199"/>
+      <x:c r="H9" s="199"/>
+      <x:c r="I9" s="199"/>
+      <x:c r="J9" s="199"/>
+      <x:c r="K9" s="199"/>
+      <x:c r="L9" s="199"/>
+      <x:c r="M9" s="199"/>
+      <x:c r="N9" s="204"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="207"/>
+      <x:c r="B10" s="189"/>
+      <x:c r="C10" s="192"/>
+      <x:c r="D10" s="195"/>
+      <x:c r="E10" s="177"/>
+      <x:c r="F10" s="177"/>
+      <x:c r="G10" s="199"/>
+      <x:c r="H10" s="199"/>
+      <x:c r="I10" s="199"/>
+      <x:c r="J10" s="199"/>
+      <x:c r="K10" s="199"/>
+      <x:c r="L10" s="199"/>
+      <x:c r="M10" s="199"/>
+      <x:c r="N10" s="204"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="207"/>
+      <x:c r="B11" s="189"/>
+      <x:c r="C11" s="192"/>
+      <x:c r="D11" s="195"/>
+      <x:c r="E11" s="177"/>
+      <x:c r="F11" s="177"/>
+      <x:c r="G11" s="199"/>
+      <x:c r="H11" s="199"/>
+      <x:c r="I11" s="199"/>
+      <x:c r="J11" s="199"/>
+      <x:c r="K11" s="199"/>
+      <x:c r="L11" s="199"/>
+      <x:c r="M11" s="199"/>
+      <x:c r="N11" s="204"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="207"/>
+      <x:c r="B12" s="189"/>
+      <x:c r="C12" s="192"/>
+      <x:c r="D12" s="195"/>
+      <x:c r="E12" s="177"/>
+      <x:c r="F12" s="177"/>
+      <x:c r="G12" s="199"/>
+      <x:c r="H12" s="199"/>
+      <x:c r="I12" s="199"/>
+      <x:c r="J12" s="199"/>
+      <x:c r="K12" s="199"/>
+      <x:c r="L12" s="199"/>
+      <x:c r="M12" s="199"/>
+      <x:c r="N12" s="204"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="207"/>
+      <x:c r="B13" s="189"/>
+      <x:c r="C13" s="192"/>
+      <x:c r="D13" s="195"/>
+      <x:c r="E13" s="177"/>
+      <x:c r="F13" s="177"/>
+      <x:c r="G13" s="199"/>
+      <x:c r="H13" s="199"/>
+      <x:c r="I13" s="199"/>
+      <x:c r="J13" s="199"/>
+      <x:c r="K13" s="199"/>
+      <x:c r="L13" s="199"/>
+      <x:c r="M13" s="199"/>
+      <x:c r="N13" s="204"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="207"/>
+      <x:c r="B14" s="189"/>
+      <x:c r="C14" s="192"/>
+      <x:c r="D14" s="195"/>
+      <x:c r="E14" s="177"/>
+      <x:c r="F14" s="177"/>
+      <x:c r="G14" s="199"/>
+      <x:c r="H14" s="199"/>
+      <x:c r="I14" s="199"/>
+      <x:c r="J14" s="199"/>
+      <x:c r="K14" s="199"/>
+      <x:c r="L14" s="199"/>
+      <x:c r="M14" s="199"/>
+      <x:c r="N14" s="204"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="207"/>
+      <x:c r="B15" s="189"/>
+      <x:c r="C15" s="192"/>
+      <x:c r="D15" s="195"/>
+      <x:c r="E15" s="177"/>
+      <x:c r="F15" s="177"/>
+      <x:c r="G15" s="199"/>
+      <x:c r="H15" s="199"/>
+      <x:c r="I15" s="199"/>
+      <x:c r="J15" s="199"/>
+      <x:c r="K15" s="199"/>
+      <x:c r="L15" s="199"/>
+      <x:c r="M15" s="199"/>
+      <x:c r="N15" s="204"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="207"/>
+      <x:c r="B16" s="189"/>
+      <x:c r="C16" s="192"/>
+      <x:c r="D16" s="195"/>
+      <x:c r="E16" s="177"/>
+      <x:c r="F16" s="177"/>
+      <x:c r="G16" s="199"/>
+      <x:c r="H16" s="199"/>
+      <x:c r="I16" s="199"/>
+      <x:c r="J16" s="199"/>
+      <x:c r="K16" s="199"/>
+      <x:c r="L16" s="199"/>
+      <x:c r="M16" s="199"/>
+      <x:c r="N16" s="204"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="207"/>
+      <x:c r="B17" s="189"/>
+      <x:c r="C17" s="192"/>
+      <x:c r="D17" s="195"/>
+      <x:c r="E17" s="177"/>
+      <x:c r="F17" s="177"/>
+      <x:c r="G17" s="199"/>
+      <x:c r="H17" s="199"/>
+      <x:c r="I17" s="199"/>
+      <x:c r="J17" s="199"/>
+      <x:c r="K17" s="199"/>
+      <x:c r="L17" s="199"/>
+      <x:c r="M17" s="199"/>
+      <x:c r="N17" s="204"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="207"/>
+      <x:c r="B18" s="189"/>
+      <x:c r="C18" s="192"/>
+      <x:c r="D18" s="195"/>
+      <x:c r="E18" s="177"/>
+      <x:c r="F18" s="177"/>
+      <x:c r="G18" s="199"/>
+      <x:c r="H18" s="199"/>
+      <x:c r="I18" s="199"/>
+      <x:c r="J18" s="199"/>
+      <x:c r="K18" s="199"/>
+      <x:c r="L18" s="199"/>
+      <x:c r="M18" s="199"/>
+      <x:c r="N18" s="204"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="207"/>
+      <x:c r="B19" s="189"/>
+      <x:c r="C19" s="192"/>
+      <x:c r="D19" s="195"/>
+      <x:c r="E19" s="177"/>
+      <x:c r="F19" s="177"/>
+      <x:c r="G19" s="199"/>
+      <x:c r="H19" s="199"/>
+      <x:c r="I19" s="199"/>
+      <x:c r="J19" s="199"/>
+      <x:c r="K19" s="199"/>
+      <x:c r="L19" s="199"/>
+      <x:c r="M19" s="199"/>
+      <x:c r="N19" s="204"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="207"/>
+      <x:c r="B20" s="189"/>
+      <x:c r="C20" s="192"/>
+      <x:c r="D20" s="195"/>
+      <x:c r="E20" s="177"/>
+      <x:c r="F20" s="177"/>
+      <x:c r="G20" s="199"/>
+      <x:c r="H20" s="199"/>
+      <x:c r="I20" s="199"/>
+      <x:c r="J20" s="199"/>
+      <x:c r="K20" s="199"/>
+      <x:c r="L20" s="199"/>
+      <x:c r="M20" s="199"/>
+      <x:c r="N20" s="204"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="207"/>
+      <x:c r="B21" s="189"/>
+      <x:c r="C21" s="192"/>
+      <x:c r="D21" s="195"/>
+      <x:c r="E21" s="177"/>
+      <x:c r="F21" s="177"/>
+      <x:c r="G21" s="199"/>
+      <x:c r="H21" s="199"/>
+      <x:c r="I21" s="199"/>
+      <x:c r="J21" s="199"/>
+      <x:c r="K21" s="199"/>
+      <x:c r="L21" s="199"/>
+      <x:c r="M21" s="199"/>
+      <x:c r="N21" s="204"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="207"/>
+      <x:c r="B22" s="189"/>
+      <x:c r="C22" s="192"/>
+      <x:c r="D22" s="195"/>
+      <x:c r="E22" s="177"/>
+      <x:c r="F22" s="177"/>
+      <x:c r="G22" s="199"/>
+      <x:c r="H22" s="199"/>
+      <x:c r="I22" s="199"/>
+      <x:c r="J22" s="199"/>
+      <x:c r="K22" s="199"/>
+      <x:c r="L22" s="199"/>
+      <x:c r="M22" s="199"/>
+      <x:c r="N22" s="204"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="207"/>
+      <x:c r="B23" s="189"/>
+      <x:c r="C23" s="192"/>
+      <x:c r="D23" s="195"/>
+      <x:c r="E23" s="177"/>
+      <x:c r="F23" s="177"/>
+      <x:c r="G23" s="199"/>
+      <x:c r="H23" s="199"/>
+      <x:c r="I23" s="199"/>
+      <x:c r="J23" s="199"/>
+      <x:c r="K23" s="199"/>
+      <x:c r="L23" s="199"/>
+      <x:c r="M23" s="199"/>
+      <x:c r="N23" s="204"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="207"/>
+      <x:c r="B24" s="189"/>
+      <x:c r="C24" s="192"/>
+      <x:c r="D24" s="195"/>
+      <x:c r="E24" s="177"/>
+      <x:c r="F24" s="177"/>
+      <x:c r="G24" s="199"/>
+      <x:c r="H24" s="199"/>
+      <x:c r="I24" s="199"/>
+      <x:c r="J24" s="199"/>
+      <x:c r="K24" s="199"/>
+      <x:c r="L24" s="199"/>
+      <x:c r="M24" s="199"/>
+      <x:c r="N24" s="204"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="207"/>
+      <x:c r="B25" s="189"/>
+      <x:c r="C25" s="192"/>
+      <x:c r="D25" s="195"/>
+      <x:c r="E25" s="177"/>
+      <x:c r="F25" s="177"/>
+      <x:c r="G25" s="199"/>
+      <x:c r="H25" s="199"/>
+      <x:c r="I25" s="199"/>
+      <x:c r="J25" s="199"/>
+      <x:c r="K25" s="199"/>
+      <x:c r="L25" s="199"/>
+      <x:c r="M25" s="199"/>
+      <x:c r="N25" s="204"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="207"/>
+      <x:c r="B26" s="189"/>
+      <x:c r="C26" s="192"/>
+      <x:c r="D26" s="195"/>
+      <x:c r="E26" s="177"/>
+      <x:c r="F26" s="177"/>
+      <x:c r="G26" s="199"/>
+      <x:c r="H26" s="199"/>
+      <x:c r="I26" s="199"/>
+      <x:c r="J26" s="199"/>
+      <x:c r="K26" s="199"/>
+      <x:c r="L26" s="199"/>
+      <x:c r="M26" s="199"/>
+      <x:c r="N26" s="204"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="207"/>
+      <x:c r="B27" s="189"/>
+      <x:c r="C27" s="192"/>
+      <x:c r="D27" s="195"/>
+      <x:c r="E27" s="177"/>
+      <x:c r="F27" s="177"/>
+      <x:c r="G27" s="199"/>
+      <x:c r="H27" s="199"/>
+      <x:c r="I27" s="199"/>
+      <x:c r="J27" s="199"/>
+      <x:c r="K27" s="199"/>
+      <x:c r="L27" s="199"/>
+      <x:c r="M27" s="199"/>
+      <x:c r="N27" s="204"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="207"/>
+      <x:c r="B28" s="189"/>
+      <x:c r="C28" s="192"/>
+      <x:c r="D28" s="195"/>
+      <x:c r="E28" s="177"/>
+      <x:c r="F28" s="177"/>
+      <x:c r="G28" s="199"/>
+      <x:c r="H28" s="199"/>
+      <x:c r="I28" s="199"/>
+      <x:c r="J28" s="199"/>
+      <x:c r="K28" s="199"/>
+      <x:c r="L28" s="199"/>
+      <x:c r="M28" s="199"/>
+      <x:c r="N28" s="204"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="207"/>
+      <x:c r="B29" s="189"/>
+      <x:c r="C29" s="192"/>
+      <x:c r="D29" s="195"/>
+      <x:c r="E29" s="177"/>
+      <x:c r="F29" s="177"/>
+      <x:c r="G29" s="199"/>
+      <x:c r="H29" s="199"/>
+      <x:c r="I29" s="199"/>
+      <x:c r="J29" s="199"/>
+      <x:c r="K29" s="199"/>
+      <x:c r="L29" s="199"/>
+      <x:c r="M29" s="199"/>
+      <x:c r="N29" s="204"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="207"/>
+      <x:c r="B30" s="189"/>
+      <x:c r="C30" s="192"/>
+      <x:c r="D30" s="195"/>
+      <x:c r="E30" s="177"/>
+      <x:c r="F30" s="177"/>
+      <x:c r="G30" s="199"/>
+      <x:c r="H30" s="199"/>
+      <x:c r="I30" s="199"/>
+      <x:c r="J30" s="199"/>
+      <x:c r="K30" s="199"/>
+      <x:c r="L30" s="199"/>
+      <x:c r="M30" s="199"/>
+      <x:c r="N30" s="204"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="207"/>
+      <x:c r="B31" s="189"/>
+      <x:c r="C31" s="192"/>
+      <x:c r="D31" s="195"/>
+      <x:c r="E31" s="177"/>
+      <x:c r="F31" s="177"/>
+      <x:c r="G31" s="199"/>
+      <x:c r="H31" s="199"/>
+      <x:c r="I31" s="199"/>
+      <x:c r="J31" s="199"/>
+      <x:c r="K31" s="199"/>
+      <x:c r="L31" s="199"/>
+      <x:c r="M31" s="199"/>
+      <x:c r="N31" s="204"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="207"/>
+      <x:c r="B32" s="189"/>
+      <x:c r="C32" s="192"/>
+      <x:c r="D32" s="195"/>
+      <x:c r="E32" s="177"/>
+      <x:c r="F32" s="177"/>
+      <x:c r="G32" s="199"/>
+      <x:c r="H32" s="199"/>
+      <x:c r="I32" s="199"/>
+      <x:c r="J32" s="199"/>
+      <x:c r="K32" s="199"/>
+      <x:c r="L32" s="199"/>
+      <x:c r="M32" s="199"/>
+      <x:c r="N32" s="204"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="207"/>
+      <x:c r="B33" s="189"/>
+      <x:c r="C33" s="192"/>
+      <x:c r="D33" s="195"/>
+      <x:c r="E33" s="177"/>
+      <x:c r="F33" s="177"/>
+      <x:c r="G33" s="199"/>
+      <x:c r="H33" s="199"/>
+      <x:c r="I33" s="199"/>
+      <x:c r="J33" s="199"/>
+      <x:c r="K33" s="199"/>
+      <x:c r="L33" s="199"/>
+      <x:c r="M33" s="199"/>
+      <x:c r="N33" s="204"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="207"/>
+      <x:c r="B34" s="189"/>
+      <x:c r="C34" s="192"/>
+      <x:c r="D34" s="195"/>
+      <x:c r="E34" s="177"/>
+      <x:c r="F34" s="177"/>
+      <x:c r="G34" s="199"/>
+      <x:c r="H34" s="199"/>
+      <x:c r="I34" s="199"/>
+      <x:c r="J34" s="199"/>
+      <x:c r="K34" s="199"/>
+      <x:c r="L34" s="199"/>
+      <x:c r="M34" s="199"/>
+      <x:c r="N34" s="204"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="207"/>
+      <x:c r="B35" s="189"/>
+      <x:c r="C35" s="192"/>
+      <x:c r="D35" s="195"/>
+      <x:c r="E35" s="177"/>
+      <x:c r="F35" s="177"/>
+      <x:c r="G35" s="199"/>
+      <x:c r="H35" s="199"/>
+      <x:c r="I35" s="199"/>
+      <x:c r="J35" s="199"/>
+      <x:c r="K35" s="199"/>
+      <x:c r="L35" s="199"/>
+      <x:c r="M35" s="199"/>
+      <x:c r="N35" s="204"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="207"/>
+      <x:c r="B36" s="189"/>
+      <x:c r="C36" s="192"/>
+      <x:c r="D36" s="195"/>
+      <x:c r="E36" s="177"/>
+      <x:c r="F36" s="177"/>
+      <x:c r="G36" s="199"/>
+      <x:c r="H36" s="199"/>
+      <x:c r="I36" s="199"/>
+      <x:c r="J36" s="199"/>
+      <x:c r="K36" s="199"/>
+      <x:c r="L36" s="199"/>
+      <x:c r="M36" s="199"/>
+      <x:c r="N36" s="204"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="207"/>
+      <x:c r="B37" s="189"/>
+      <x:c r="C37" s="192"/>
+      <x:c r="D37" s="195"/>
+      <x:c r="E37" s="177"/>
+      <x:c r="F37" s="177"/>
+      <x:c r="G37" s="199"/>
+      <x:c r="H37" s="199"/>
+      <x:c r="I37" s="199"/>
+      <x:c r="J37" s="199"/>
+      <x:c r="K37" s="199"/>
+      <x:c r="L37" s="199"/>
+      <x:c r="M37" s="199"/>
+      <x:c r="N37" s="204"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="207"/>
+      <x:c r="B38" s="189"/>
+      <x:c r="C38" s="192"/>
+      <x:c r="D38" s="195"/>
+      <x:c r="E38" s="177"/>
+      <x:c r="F38" s="177"/>
+      <x:c r="G38" s="199"/>
+      <x:c r="H38" s="199"/>
+      <x:c r="I38" s="199"/>
+      <x:c r="J38" s="199"/>
+      <x:c r="K38" s="199"/>
+      <x:c r="L38" s="199"/>
+      <x:c r="M38" s="199"/>
+      <x:c r="N38" s="204"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="207"/>
+      <x:c r="B39" s="189"/>
+      <x:c r="C39" s="192"/>
+      <x:c r="D39" s="195"/>
+      <x:c r="E39" s="177"/>
+      <x:c r="F39" s="177"/>
+      <x:c r="G39" s="199"/>
+      <x:c r="H39" s="199"/>
+      <x:c r="I39" s="199"/>
+      <x:c r="J39" s="199"/>
+      <x:c r="K39" s="199"/>
+      <x:c r="L39" s="199"/>
+      <x:c r="M39" s="199"/>
+      <x:c r="N39" s="204"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="207"/>
+      <x:c r="B40" s="189"/>
+      <x:c r="C40" s="192"/>
+      <x:c r="D40" s="195"/>
+      <x:c r="E40" s="177"/>
+      <x:c r="F40" s="177"/>
+      <x:c r="G40" s="199"/>
+      <x:c r="H40" s="199"/>
+      <x:c r="I40" s="199"/>
+      <x:c r="J40" s="199"/>
+      <x:c r="K40" s="199"/>
+      <x:c r="L40" s="199"/>
+      <x:c r="M40" s="199"/>
+      <x:c r="N40" s="204"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="207"/>
+      <x:c r="B41" s="189"/>
+      <x:c r="C41" s="192"/>
+      <x:c r="D41" s="195"/>
+      <x:c r="E41" s="177"/>
+      <x:c r="F41" s="177"/>
+      <x:c r="G41" s="199"/>
+      <x:c r="H41" s="199"/>
+      <x:c r="I41" s="199"/>
+      <x:c r="J41" s="199"/>
+      <x:c r="K41" s="199"/>
+      <x:c r="L41" s="199"/>
+      <x:c r="M41" s="199"/>
+      <x:c r="N41" s="204"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="207"/>
+      <x:c r="B42" s="189"/>
+      <x:c r="C42" s="192"/>
+      <x:c r="D42" s="195"/>
+      <x:c r="E42" s="177"/>
+      <x:c r="F42" s="177"/>
+      <x:c r="G42" s="199"/>
+      <x:c r="H42" s="199"/>
+      <x:c r="I42" s="199"/>
+      <x:c r="J42" s="199"/>
+      <x:c r="K42" s="199"/>
+      <x:c r="L42" s="199"/>
+      <x:c r="M42" s="199"/>
+      <x:c r="N42" s="204"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="207"/>
+      <x:c r="B43" s="189"/>
+      <x:c r="C43" s="192"/>
+      <x:c r="D43" s="195"/>
+      <x:c r="E43" s="177"/>
+      <x:c r="F43" s="177"/>
+      <x:c r="G43" s="199"/>
+      <x:c r="H43" s="199"/>
+      <x:c r="I43" s="199"/>
+      <x:c r="J43" s="199"/>
+      <x:c r="K43" s="199"/>
+      <x:c r="L43" s="199"/>
+      <x:c r="M43" s="199"/>
+      <x:c r="N43" s="204"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="207"/>
+      <x:c r="B44" s="189"/>
+      <x:c r="C44" s="192"/>
+      <x:c r="D44" s="195"/>
+      <x:c r="E44" s="177"/>
+      <x:c r="F44" s="177"/>
+      <x:c r="G44" s="199"/>
+      <x:c r="H44" s="199"/>
+      <x:c r="I44" s="199"/>
+      <x:c r="J44" s="199"/>
+      <x:c r="K44" s="199"/>
+      <x:c r="L44" s="199"/>
+      <x:c r="M44" s="199"/>
+      <x:c r="N44" s="204"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="207"/>
+      <x:c r="B45" s="189"/>
+      <x:c r="C45" s="192"/>
+      <x:c r="D45" s="195"/>
+      <x:c r="E45" s="177"/>
+      <x:c r="F45" s="177"/>
+      <x:c r="G45" s="199"/>
+      <x:c r="H45" s="199"/>
+      <x:c r="I45" s="199"/>
+      <x:c r="J45" s="199"/>
+      <x:c r="K45" s="199"/>
+      <x:c r="L45" s="199"/>
+      <x:c r="M45" s="199"/>
+      <x:c r="N45" s="204"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="207"/>
+      <x:c r="B46" s="189"/>
+      <x:c r="C46" s="192"/>
+      <x:c r="D46" s="195"/>
+      <x:c r="E46" s="177"/>
+      <x:c r="F46" s="177"/>
+      <x:c r="G46" s="199"/>
+      <x:c r="H46" s="199"/>
+      <x:c r="I46" s="199"/>
+      <x:c r="J46" s="199"/>
+      <x:c r="K46" s="199"/>
+      <x:c r="L46" s="199"/>
+      <x:c r="M46" s="199"/>
+      <x:c r="N46" s="204"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="207"/>
+      <x:c r="B47" s="189"/>
+      <x:c r="C47" s="192"/>
+      <x:c r="D47" s="195"/>
+      <x:c r="E47" s="177"/>
+      <x:c r="F47" s="177"/>
+      <x:c r="G47" s="199"/>
+      <x:c r="H47" s="199"/>
+      <x:c r="I47" s="199"/>
+      <x:c r="J47" s="199"/>
+      <x:c r="K47" s="199"/>
+      <x:c r="L47" s="199"/>
+      <x:c r="M47" s="199"/>
+      <x:c r="N47" s="204"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="207"/>
+      <x:c r="B48" s="189"/>
+      <x:c r="C48" s="192"/>
+      <x:c r="D48" s="195"/>
+      <x:c r="E48" s="177"/>
+      <x:c r="F48" s="177"/>
+      <x:c r="G48" s="199"/>
+      <x:c r="H48" s="199"/>
+      <x:c r="I48" s="199"/>
+      <x:c r="J48" s="199"/>
+      <x:c r="K48" s="199"/>
+      <x:c r="L48" s="199"/>
+      <x:c r="M48" s="199"/>
+      <x:c r="N48" s="204"/>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="207"/>
+      <x:c r="B49" s="189"/>
+      <x:c r="C49" s="192"/>
+      <x:c r="D49" s="195"/>
+      <x:c r="E49" s="177"/>
+      <x:c r="F49" s="177"/>
+      <x:c r="G49" s="199"/>
+      <x:c r="H49" s="199"/>
+      <x:c r="I49" s="199"/>
+      <x:c r="J49" s="199"/>
+      <x:c r="K49" s="199"/>
+      <x:c r="L49" s="199"/>
+      <x:c r="M49" s="199"/>
+      <x:c r="N49" s="204"/>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="207"/>
+      <x:c r="B50" s="189"/>
+      <x:c r="C50" s="192"/>
+      <x:c r="D50" s="195"/>
+      <x:c r="E50" s="177"/>
+      <x:c r="F50" s="177"/>
+      <x:c r="G50" s="199"/>
+      <x:c r="H50" s="199"/>
+      <x:c r="I50" s="199"/>
+      <x:c r="J50" s="199"/>
+      <x:c r="K50" s="199"/>
+      <x:c r="L50" s="199"/>
+      <x:c r="M50" s="199"/>
+      <x:c r="N50" s="204"/>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="207"/>
+      <x:c r="B51" s="189"/>
+      <x:c r="C51" s="192"/>
+      <x:c r="D51" s="195"/>
+      <x:c r="E51" s="177"/>
+      <x:c r="F51" s="177"/>
+      <x:c r="G51" s="199"/>
+      <x:c r="H51" s="199"/>
+      <x:c r="I51" s="199"/>
+      <x:c r="J51" s="199"/>
+      <x:c r="K51" s="199"/>
+      <x:c r="L51" s="199"/>
+      <x:c r="M51" s="199"/>
+      <x:c r="N51" s="204"/>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="207"/>
+      <x:c r="B52" s="189"/>
+      <x:c r="C52" s="192"/>
+      <x:c r="D52" s="195"/>
+      <x:c r="E52" s="177"/>
+      <x:c r="F52" s="177"/>
+      <x:c r="G52" s="199"/>
+      <x:c r="H52" s="199"/>
+      <x:c r="I52" s="199"/>
+      <x:c r="J52" s="199"/>
+      <x:c r="K52" s="199"/>
+      <x:c r="L52" s="199"/>
+      <x:c r="M52" s="199"/>
+      <x:c r="N52" s="204"/>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="207"/>
+      <x:c r="B53" s="189"/>
+      <x:c r="C53" s="192"/>
+      <x:c r="D53" s="195"/>
+      <x:c r="E53" s="177"/>
+      <x:c r="F53" s="177"/>
+      <x:c r="G53" s="199"/>
+      <x:c r="H53" s="199"/>
+      <x:c r="I53" s="199"/>
+      <x:c r="J53" s="199"/>
+      <x:c r="K53" s="199"/>
+      <x:c r="L53" s="199"/>
+      <x:c r="M53" s="199"/>
+      <x:c r="N53" s="204"/>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="207"/>
+      <x:c r="B54" s="189"/>
+      <x:c r="C54" s="192"/>
+      <x:c r="D54" s="195"/>
+      <x:c r="E54" s="177"/>
+      <x:c r="F54" s="177"/>
+      <x:c r="G54" s="199"/>
+      <x:c r="H54" s="199"/>
+      <x:c r="I54" s="199"/>
+      <x:c r="J54" s="199"/>
+      <x:c r="K54" s="199"/>
+      <x:c r="L54" s="199"/>
+      <x:c r="M54" s="199"/>
+      <x:c r="N54" s="204"/>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="207"/>
+      <x:c r="B55" s="189"/>
+      <x:c r="C55" s="192"/>
+      <x:c r="D55" s="195"/>
+      <x:c r="E55" s="177"/>
+      <x:c r="F55" s="177"/>
+      <x:c r="G55" s="199"/>
+      <x:c r="H55" s="199"/>
+      <x:c r="I55" s="199"/>
+      <x:c r="J55" s="199"/>
+      <x:c r="K55" s="199"/>
+      <x:c r="L55" s="199"/>
+      <x:c r="M55" s="199"/>
+      <x:c r="N55" s="204"/>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="207"/>
+      <x:c r="B56" s="189"/>
+      <x:c r="C56" s="192"/>
+      <x:c r="D56" s="195"/>
+      <x:c r="E56" s="177"/>
+      <x:c r="F56" s="177"/>
+      <x:c r="G56" s="199"/>
+      <x:c r="H56" s="199"/>
+      <x:c r="I56" s="199"/>
+      <x:c r="J56" s="199"/>
+      <x:c r="K56" s="199"/>
+      <x:c r="L56" s="199"/>
+      <x:c r="M56" s="199"/>
+      <x:c r="N56" s="204"/>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" s="207"/>
+      <x:c r="B57" s="189"/>
+      <x:c r="C57" s="192"/>
+      <x:c r="D57" s="195"/>
+      <x:c r="E57" s="177"/>
+      <x:c r="F57" s="177"/>
+      <x:c r="G57" s="199"/>
+      <x:c r="H57" s="199"/>
+      <x:c r="I57" s="199"/>
+      <x:c r="J57" s="199"/>
+      <x:c r="K57" s="199"/>
+      <x:c r="L57" s="199"/>
+      <x:c r="M57" s="199"/>
+      <x:c r="N57" s="204"/>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" s="207"/>
+      <x:c r="B58" s="189"/>
+      <x:c r="C58" s="192"/>
+      <x:c r="D58" s="195"/>
+      <x:c r="E58" s="177"/>
+      <x:c r="F58" s="177"/>
+      <x:c r="G58" s="199"/>
+      <x:c r="H58" s="199"/>
+      <x:c r="I58" s="199"/>
+      <x:c r="J58" s="199"/>
+      <x:c r="K58" s="199"/>
+      <x:c r="L58" s="199"/>
+      <x:c r="M58" s="199"/>
+      <x:c r="N58" s="204"/>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" s="207"/>
+      <x:c r="B59" s="189"/>
+      <x:c r="C59" s="192"/>
+      <x:c r="D59" s="195"/>
+      <x:c r="E59" s="177"/>
+      <x:c r="F59" s="177"/>
+      <x:c r="G59" s="199"/>
+      <x:c r="H59" s="199"/>
+      <x:c r="I59" s="199"/>
+      <x:c r="J59" s="199"/>
+      <x:c r="K59" s="199"/>
+      <x:c r="L59" s="199"/>
+      <x:c r="M59" s="199"/>
+      <x:c r="N59" s="204"/>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="207"/>
+      <x:c r="B60" s="189"/>
+      <x:c r="C60" s="192"/>
+      <x:c r="D60" s="195"/>
+      <x:c r="E60" s="177"/>
+      <x:c r="F60" s="177"/>
+      <x:c r="G60" s="199"/>
+      <x:c r="H60" s="199"/>
+      <x:c r="I60" s="199"/>
+      <x:c r="J60" s="199"/>
+      <x:c r="K60" s="199"/>
+      <x:c r="L60" s="199"/>
+      <x:c r="M60" s="199"/>
+      <x:c r="N60" s="204"/>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" s="207"/>
+      <x:c r="B61" s="189"/>
+      <x:c r="C61" s="192"/>
+      <x:c r="D61" s="195"/>
+      <x:c r="E61" s="177"/>
+      <x:c r="F61" s="177"/>
+      <x:c r="G61" s="199"/>
+      <x:c r="H61" s="199"/>
+      <x:c r="I61" s="199"/>
+      <x:c r="J61" s="199"/>
+      <x:c r="K61" s="199"/>
+      <x:c r="L61" s="199"/>
+      <x:c r="M61" s="199"/>
+      <x:c r="N61" s="204"/>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" s="207"/>
+      <x:c r="B62" s="189"/>
+      <x:c r="C62" s="192"/>
+      <x:c r="D62" s="195"/>
+      <x:c r="E62" s="177"/>
+      <x:c r="F62" s="177"/>
+      <x:c r="G62" s="199"/>
+      <x:c r="H62" s="199"/>
+      <x:c r="I62" s="199"/>
+      <x:c r="J62" s="199"/>
+      <x:c r="K62" s="199"/>
+      <x:c r="L62" s="199"/>
+      <x:c r="M62" s="199"/>
+      <x:c r="N62" s="204"/>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" s="207"/>
+      <x:c r="B63" s="189"/>
+      <x:c r="C63" s="192"/>
+      <x:c r="D63" s="195"/>
+      <x:c r="E63" s="177"/>
+      <x:c r="F63" s="177"/>
+      <x:c r="G63" s="199"/>
+      <x:c r="H63" s="199"/>
+      <x:c r="I63" s="199"/>
+      <x:c r="J63" s="199"/>
+      <x:c r="K63" s="199"/>
+      <x:c r="L63" s="199"/>
+      <x:c r="M63" s="199"/>
+      <x:c r="N63" s="204"/>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" s="207"/>
+      <x:c r="B64" s="189"/>
+      <x:c r="C64" s="192"/>
+      <x:c r="D64" s="195"/>
+      <x:c r="E64" s="177"/>
+      <x:c r="F64" s="177"/>
+      <x:c r="G64" s="199"/>
+      <x:c r="H64" s="199"/>
+      <x:c r="I64" s="199"/>
+      <x:c r="J64" s="199"/>
+      <x:c r="K64" s="199"/>
+      <x:c r="L64" s="199"/>
+      <x:c r="M64" s="199"/>
+      <x:c r="N64" s="204"/>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" s="207"/>
+      <x:c r="B65" s="189"/>
+      <x:c r="C65" s="192"/>
+      <x:c r="D65" s="195"/>
+      <x:c r="E65" s="177"/>
+      <x:c r="F65" s="177"/>
+      <x:c r="G65" s="199"/>
+      <x:c r="H65" s="199"/>
+      <x:c r="I65" s="199"/>
+      <x:c r="J65" s="199"/>
+      <x:c r="K65" s="199"/>
+      <x:c r="L65" s="199"/>
+      <x:c r="M65" s="199"/>
+      <x:c r="N65" s="204"/>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" s="207"/>
+      <x:c r="B66" s="189"/>
+      <x:c r="C66" s="192"/>
+      <x:c r="D66" s="195"/>
+      <x:c r="E66" s="177"/>
+      <x:c r="F66" s="177"/>
+      <x:c r="G66" s="199"/>
+      <x:c r="H66" s="199"/>
+      <x:c r="I66" s="199"/>
+      <x:c r="J66" s="199"/>
+      <x:c r="K66" s="199"/>
+      <x:c r="L66" s="199"/>
+      <x:c r="M66" s="199"/>
+      <x:c r="N66" s="204"/>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" s="207"/>
+      <x:c r="B67" s="189"/>
+      <x:c r="C67" s="192"/>
+      <x:c r="D67" s="195"/>
+      <x:c r="E67" s="177"/>
+      <x:c r="F67" s="177"/>
+      <x:c r="G67" s="199"/>
+      <x:c r="H67" s="199"/>
+      <x:c r="I67" s="199"/>
+      <x:c r="J67" s="199"/>
+      <x:c r="K67" s="199"/>
+      <x:c r="L67" s="199"/>
+      <x:c r="M67" s="199"/>
+      <x:c r="N67" s="204"/>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" s="207"/>
+      <x:c r="B68" s="189"/>
+      <x:c r="C68" s="192"/>
+      <x:c r="D68" s="195"/>
+      <x:c r="E68" s="177"/>
+      <x:c r="F68" s="177"/>
+      <x:c r="G68" s="199"/>
+      <x:c r="H68" s="199"/>
+      <x:c r="I68" s="199"/>
+      <x:c r="J68" s="199"/>
+      <x:c r="K68" s="199"/>
+      <x:c r="L68" s="199"/>
+      <x:c r="M68" s="199"/>
+      <x:c r="N68" s="204"/>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" s="207"/>
+      <x:c r="B69" s="189"/>
+      <x:c r="C69" s="192"/>
+      <x:c r="D69" s="195"/>
+      <x:c r="E69" s="177"/>
+      <x:c r="F69" s="177"/>
+      <x:c r="G69" s="199"/>
+      <x:c r="H69" s="199"/>
+      <x:c r="I69" s="199"/>
+      <x:c r="J69" s="199"/>
+      <x:c r="K69" s="199"/>
+      <x:c r="L69" s="199"/>
+      <x:c r="M69" s="199"/>
+      <x:c r="N69" s="204"/>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" s="207"/>
+      <x:c r="B70" s="189"/>
+      <x:c r="C70" s="192"/>
+      <x:c r="D70" s="195"/>
+      <x:c r="E70" s="177"/>
+      <x:c r="F70" s="177"/>
+      <x:c r="G70" s="199"/>
+      <x:c r="H70" s="199"/>
+      <x:c r="I70" s="199"/>
+      <x:c r="J70" s="199"/>
+      <x:c r="K70" s="199"/>
+      <x:c r="L70" s="199"/>
+      <x:c r="M70" s="199"/>
+      <x:c r="N70" s="204"/>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" s="207"/>
+      <x:c r="B71" s="189"/>
+      <x:c r="C71" s="192"/>
+      <x:c r="D71" s="195"/>
+      <x:c r="E71" s="177"/>
+      <x:c r="F71" s="177"/>
+      <x:c r="G71" s="199"/>
+      <x:c r="H71" s="199"/>
+      <x:c r="I71" s="199"/>
+      <x:c r="J71" s="199"/>
+      <x:c r="K71" s="199"/>
+      <x:c r="L71" s="199"/>
+      <x:c r="M71" s="199"/>
+      <x:c r="N71" s="204"/>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" s="207"/>
+      <x:c r="B72" s="189"/>
+      <x:c r="C72" s="192"/>
+      <x:c r="D72" s="195"/>
+      <x:c r="E72" s="177"/>
+      <x:c r="F72" s="177"/>
+      <x:c r="G72" s="199"/>
+      <x:c r="H72" s="199"/>
+      <x:c r="I72" s="199"/>
+      <x:c r="J72" s="199"/>
+      <x:c r="K72" s="199"/>
+      <x:c r="L72" s="199"/>
+      <x:c r="M72" s="199"/>
+      <x:c r="N72" s="204"/>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" s="207"/>
+      <x:c r="B73" s="189"/>
+      <x:c r="C73" s="192"/>
+      <x:c r="D73" s="195"/>
+      <x:c r="E73" s="177"/>
+      <x:c r="F73" s="177"/>
+      <x:c r="G73" s="199"/>
+      <x:c r="H73" s="199"/>
+      <x:c r="I73" s="199"/>
+      <x:c r="J73" s="199"/>
+      <x:c r="K73" s="199"/>
+      <x:c r="L73" s="199"/>
+      <x:c r="M73" s="199"/>
+      <x:c r="N73" s="204"/>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" s="207"/>
+      <x:c r="B74" s="189"/>
+      <x:c r="C74" s="192"/>
+      <x:c r="D74" s="195"/>
+      <x:c r="E74" s="177"/>
+      <x:c r="F74" s="177"/>
+      <x:c r="G74" s="199"/>
+      <x:c r="H74" s="199"/>
+      <x:c r="I74" s="199"/>
+      <x:c r="J74" s="199"/>
+      <x:c r="K74" s="199"/>
+      <x:c r="L74" s="199"/>
+      <x:c r="M74" s="199"/>
+      <x:c r="N74" s="204"/>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" s="207"/>
+      <x:c r="B75" s="189"/>
+      <x:c r="C75" s="192"/>
+      <x:c r="D75" s="195"/>
+      <x:c r="E75" s="177"/>
+      <x:c r="F75" s="177"/>
+      <x:c r="G75" s="199"/>
+      <x:c r="H75" s="199"/>
+      <x:c r="I75" s="199"/>
+      <x:c r="J75" s="199"/>
+      <x:c r="K75" s="199"/>
+      <x:c r="L75" s="199"/>
+      <x:c r="M75" s="199"/>
+      <x:c r="N75" s="204"/>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" s="207"/>
+      <x:c r="B76" s="189"/>
+      <x:c r="C76" s="192"/>
+      <x:c r="D76" s="195"/>
+      <x:c r="E76" s="177"/>
+      <x:c r="F76" s="177"/>
+      <x:c r="G76" s="199"/>
+      <x:c r="H76" s="199"/>
+      <x:c r="I76" s="199"/>
+      <x:c r="J76" s="199"/>
+      <x:c r="K76" s="199"/>
+      <x:c r="L76" s="199"/>
+      <x:c r="M76" s="199"/>
+      <x:c r="N76" s="204"/>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" s="207"/>
+      <x:c r="B77" s="189"/>
+      <x:c r="C77" s="192"/>
+      <x:c r="D77" s="195"/>
+      <x:c r="E77" s="177"/>
+      <x:c r="F77" s="177"/>
+      <x:c r="G77" s="199"/>
+      <x:c r="H77" s="199"/>
+      <x:c r="I77" s="199"/>
+      <x:c r="J77" s="199"/>
+      <x:c r="K77" s="199"/>
+      <x:c r="L77" s="199"/>
+      <x:c r="M77" s="199"/>
+      <x:c r="N77" s="204"/>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78" s="207"/>
+      <x:c r="B78" s="189"/>
+      <x:c r="C78" s="192"/>
+      <x:c r="D78" s="195"/>
+      <x:c r="E78" s="177"/>
+      <x:c r="F78" s="177"/>
+      <x:c r="G78" s="199"/>
+      <x:c r="H78" s="199"/>
+      <x:c r="I78" s="199"/>
+      <x:c r="J78" s="199"/>
+      <x:c r="K78" s="199"/>
+      <x:c r="L78" s="199"/>
+      <x:c r="M78" s="199"/>
+      <x:c r="N78" s="204"/>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79" s="207"/>
+      <x:c r="B79" s="189"/>
+      <x:c r="C79" s="192"/>
+      <x:c r="D79" s="195"/>
+      <x:c r="E79" s="177"/>
+      <x:c r="F79" s="177"/>
+      <x:c r="G79" s="199"/>
+      <x:c r="H79" s="199"/>
+      <x:c r="I79" s="199"/>
+      <x:c r="J79" s="199"/>
+      <x:c r="K79" s="199"/>
+      <x:c r="L79" s="199"/>
+      <x:c r="M79" s="199"/>
+      <x:c r="N79" s="204"/>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80" s="207"/>
+      <x:c r="B80" s="189"/>
+      <x:c r="C80" s="192"/>
+      <x:c r="D80" s="195"/>
+      <x:c r="E80" s="177"/>
+      <x:c r="F80" s="177"/>
+      <x:c r="G80" s="199"/>
+      <x:c r="H80" s="199"/>
+      <x:c r="I80" s="199"/>
+      <x:c r="J80" s="199"/>
+      <x:c r="K80" s="199"/>
+      <x:c r="L80" s="199"/>
+      <x:c r="M80" s="199"/>
+      <x:c r="N80" s="204"/>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81" s="207"/>
+      <x:c r="B81" s="189"/>
+      <x:c r="C81" s="192"/>
+      <x:c r="D81" s="195"/>
+      <x:c r="E81" s="177"/>
+      <x:c r="F81" s="177"/>
+      <x:c r="G81" s="199"/>
+      <x:c r="H81" s="199"/>
+      <x:c r="I81" s="199"/>
+      <x:c r="J81" s="199"/>
+      <x:c r="K81" s="199"/>
+      <x:c r="L81" s="199"/>
+      <x:c r="M81" s="199"/>
+      <x:c r="N81" s="204"/>
+    </x:row>
+    <x:row r="82">
+      <x:c r="A82" s="207"/>
+      <x:c r="B82" s="189"/>
+      <x:c r="C82" s="192"/>
+      <x:c r="D82" s="195"/>
+      <x:c r="E82" s="177"/>
+      <x:c r="F82" s="177"/>
+      <x:c r="G82" s="199"/>
+      <x:c r="H82" s="199"/>
+      <x:c r="I82" s="199"/>
+      <x:c r="J82" s="199"/>
+      <x:c r="K82" s="199"/>
+      <x:c r="L82" s="199"/>
+      <x:c r="M82" s="199"/>
+      <x:c r="N82" s="204"/>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83" s="207"/>
+      <x:c r="B83" s="189"/>
+      <x:c r="C83" s="192"/>
+      <x:c r="D83" s="195"/>
+      <x:c r="E83" s="177"/>
+      <x:c r="F83" s="177"/>
+      <x:c r="G83" s="199"/>
+      <x:c r="H83" s="199"/>
+      <x:c r="I83" s="199"/>
+      <x:c r="J83" s="199"/>
+      <x:c r="K83" s="199"/>
+      <x:c r="L83" s="199"/>
+      <x:c r="M83" s="199"/>
+      <x:c r="N83" s="204"/>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84" s="207"/>
+      <x:c r="B84" s="189"/>
+      <x:c r="C84" s="192"/>
+      <x:c r="D84" s="195"/>
+      <x:c r="E84" s="177"/>
+      <x:c r="F84" s="177"/>
+      <x:c r="G84" s="199"/>
+      <x:c r="H84" s="199"/>
+      <x:c r="I84" s="199"/>
+      <x:c r="J84" s="199"/>
+      <x:c r="K84" s="199"/>
+      <x:c r="L84" s="199"/>
+      <x:c r="M84" s="199"/>
+      <x:c r="N84" s="204"/>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85" s="207"/>
+      <x:c r="B85" s="189"/>
+      <x:c r="C85" s="192"/>
+      <x:c r="D85" s="195"/>
+      <x:c r="E85" s="177"/>
+      <x:c r="F85" s="177"/>
+      <x:c r="G85" s="199"/>
+      <x:c r="H85" s="199"/>
+      <x:c r="I85" s="199"/>
+      <x:c r="J85" s="199"/>
+      <x:c r="K85" s="199"/>
+      <x:c r="L85" s="199"/>
+      <x:c r="M85" s="199"/>
+      <x:c r="N85" s="204"/>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86" s="207"/>
+      <x:c r="B86" s="189"/>
+      <x:c r="C86" s="192"/>
+      <x:c r="D86" s="195"/>
+      <x:c r="E86" s="177"/>
+      <x:c r="F86" s="177"/>
+      <x:c r="G86" s="199"/>
+      <x:c r="H86" s="199"/>
+      <x:c r="I86" s="199"/>
+      <x:c r="J86" s="199"/>
+      <x:c r="K86" s="199"/>
+      <x:c r="L86" s="199"/>
+      <x:c r="M86" s="199"/>
+      <x:c r="N86" s="204"/>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87" s="207"/>
+      <x:c r="B87" s="189"/>
+      <x:c r="C87" s="192"/>
+      <x:c r="D87" s="195"/>
+      <x:c r="E87" s="177"/>
+      <x:c r="F87" s="177"/>
+      <x:c r="G87" s="199"/>
+      <x:c r="H87" s="199"/>
+      <x:c r="I87" s="199"/>
+      <x:c r="J87" s="199"/>
+      <x:c r="K87" s="199"/>
+      <x:c r="L87" s="199"/>
+      <x:c r="M87" s="199"/>
+      <x:c r="N87" s="204"/>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88" s="207"/>
+      <x:c r="B88" s="189"/>
+      <x:c r="C88" s="192"/>
+      <x:c r="D88" s="195"/>
+      <x:c r="E88" s="177"/>
+      <x:c r="F88" s="177"/>
+      <x:c r="G88" s="199"/>
+      <x:c r="H88" s="199"/>
+      <x:c r="I88" s="199"/>
+      <x:c r="J88" s="199"/>
+      <x:c r="K88" s="199"/>
+      <x:c r="L88" s="199"/>
+      <x:c r="M88" s="199"/>
+      <x:c r="N88" s="204"/>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" s="207"/>
+      <x:c r="B89" s="189"/>
+      <x:c r="C89" s="192"/>
+      <x:c r="D89" s="195"/>
+      <x:c r="E89" s="177"/>
+      <x:c r="F89" s="177"/>
+      <x:c r="G89" s="199"/>
+      <x:c r="H89" s="199"/>
+      <x:c r="I89" s="199"/>
+      <x:c r="J89" s="199"/>
+      <x:c r="K89" s="199"/>
+      <x:c r="L89" s="199"/>
+      <x:c r="M89" s="199"/>
+      <x:c r="N89" s="204"/>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" s="207"/>
+      <x:c r="B90" s="189"/>
+      <x:c r="C90" s="192"/>
+      <x:c r="D90" s="195"/>
+      <x:c r="E90" s="177"/>
+      <x:c r="F90" s="177"/>
+      <x:c r="G90" s="199"/>
+      <x:c r="H90" s="199"/>
+      <x:c r="I90" s="199"/>
+      <x:c r="J90" s="199"/>
+      <x:c r="K90" s="199"/>
+      <x:c r="L90" s="199"/>
+      <x:c r="M90" s="199"/>
+      <x:c r="N90" s="204"/>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" s="207"/>
+      <x:c r="B91" s="189"/>
+      <x:c r="C91" s="192"/>
+      <x:c r="D91" s="195"/>
+      <x:c r="E91" s="177"/>
+      <x:c r="F91" s="177"/>
+      <x:c r="G91" s="199"/>
+      <x:c r="H91" s="199"/>
+      <x:c r="I91" s="199"/>
+      <x:c r="J91" s="199"/>
+      <x:c r="K91" s="199"/>
+      <x:c r="L91" s="199"/>
+      <x:c r="M91" s="199"/>
+      <x:c r="N91" s="204"/>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92" s="207"/>
+      <x:c r="B92" s="189"/>
+      <x:c r="C92" s="192"/>
+      <x:c r="D92" s="195"/>
+      <x:c r="E92" s="177"/>
+      <x:c r="F92" s="177"/>
+      <x:c r="G92" s="199"/>
+      <x:c r="H92" s="199"/>
+      <x:c r="I92" s="199"/>
+      <x:c r="J92" s="199"/>
+      <x:c r="K92" s="199"/>
+      <x:c r="L92" s="199"/>
+      <x:c r="M92" s="199"/>
+      <x:c r="N92" s="204"/>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93" s="207"/>
+      <x:c r="B93" s="189"/>
+      <x:c r="C93" s="192"/>
+      <x:c r="D93" s="195"/>
+      <x:c r="E93" s="177"/>
+      <x:c r="F93" s="177"/>
+      <x:c r="G93" s="199"/>
+      <x:c r="H93" s="199"/>
+      <x:c r="I93" s="199"/>
+      <x:c r="J93" s="199"/>
+      <x:c r="K93" s="199"/>
+      <x:c r="L93" s="199"/>
+      <x:c r="M93" s="199"/>
+      <x:c r="N93" s="204"/>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" s="207"/>
+      <x:c r="B94" s="189"/>
+      <x:c r="C94" s="192"/>
+      <x:c r="D94" s="195"/>
+      <x:c r="E94" s="177"/>
+      <x:c r="F94" s="177"/>
+      <x:c r="G94" s="199"/>
+      <x:c r="H94" s="199"/>
+      <x:c r="I94" s="199"/>
+      <x:c r="J94" s="199"/>
+      <x:c r="K94" s="199"/>
+      <x:c r="L94" s="199"/>
+      <x:c r="M94" s="199"/>
+      <x:c r="N94" s="204"/>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" s="207"/>
+      <x:c r="B95" s="189"/>
+      <x:c r="C95" s="192"/>
+      <x:c r="D95" s="195"/>
+      <x:c r="E95" s="177"/>
+      <x:c r="F95" s="177"/>
+      <x:c r="G95" s="199"/>
+      <x:c r="H95" s="199"/>
+      <x:c r="I95" s="199"/>
+      <x:c r="J95" s="199"/>
+      <x:c r="K95" s="199"/>
+      <x:c r="L95" s="199"/>
+      <x:c r="M95" s="199"/>
+      <x:c r="N95" s="204"/>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" s="207"/>
+      <x:c r="B96" s="189"/>
+      <x:c r="C96" s="192"/>
+      <x:c r="D96" s="195"/>
+      <x:c r="E96" s="177"/>
+      <x:c r="F96" s="177"/>
+      <x:c r="G96" s="199"/>
+      <x:c r="H96" s="199"/>
+      <x:c r="I96" s="199"/>
+      <x:c r="J96" s="199"/>
+      <x:c r="K96" s="199"/>
+      <x:c r="L96" s="199"/>
+      <x:c r="M96" s="199"/>
+      <x:c r="N96" s="204"/>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97" s="207"/>
+      <x:c r="B97" s="189"/>
+      <x:c r="C97" s="192"/>
+      <x:c r="D97" s="195"/>
+      <x:c r="E97" s="177"/>
+      <x:c r="F97" s="177"/>
+      <x:c r="G97" s="199"/>
+      <x:c r="H97" s="199"/>
+      <x:c r="I97" s="199"/>
+      <x:c r="J97" s="199"/>
+      <x:c r="K97" s="199"/>
+      <x:c r="L97" s="199"/>
+      <x:c r="M97" s="199"/>
+      <x:c r="N97" s="204"/>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98" s="207"/>
+      <x:c r="B98" s="189"/>
+      <x:c r="C98" s="192"/>
+      <x:c r="D98" s="195"/>
+      <x:c r="E98" s="177"/>
+      <x:c r="F98" s="177"/>
+      <x:c r="G98" s="199"/>
+      <x:c r="H98" s="199"/>
+      <x:c r="I98" s="199"/>
+      <x:c r="J98" s="199"/>
+      <x:c r="K98" s="199"/>
+      <x:c r="L98" s="199"/>
+      <x:c r="M98" s="199"/>
+      <x:c r="N98" s="204"/>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" s="207"/>
+      <x:c r="B99" s="189"/>
+      <x:c r="C99" s="192"/>
+      <x:c r="D99" s="195"/>
+      <x:c r="E99" s="177"/>
+      <x:c r="F99" s="177"/>
+      <x:c r="G99" s="199"/>
+      <x:c r="H99" s="199"/>
+      <x:c r="I99" s="199"/>
+      <x:c r="J99" s="199"/>
+      <x:c r="K99" s="199"/>
+      <x:c r="L99" s="199"/>
+      <x:c r="M99" s="199"/>
+      <x:c r="N99" s="204"/>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100" s="207"/>
+      <x:c r="B100" s="189"/>
+      <x:c r="C100" s="192"/>
+      <x:c r="D100" s="195"/>
+      <x:c r="E100" s="177"/>
+      <x:c r="F100" s="177"/>
+      <x:c r="G100" s="199"/>
+      <x:c r="H100" s="199"/>
+      <x:c r="I100" s="199"/>
+      <x:c r="J100" s="199"/>
+      <x:c r="K100" s="199"/>
+      <x:c r="L100" s="199"/>
+      <x:c r="M100" s="199"/>
+      <x:c r="N100" s="204"/>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101" s="207"/>
+      <x:c r="B101" s="189"/>
+      <x:c r="C101" s="192"/>
+      <x:c r="D101" s="195"/>
+      <x:c r="E101" s="177"/>
+      <x:c r="F101" s="177"/>
+      <x:c r="G101" s="199"/>
+      <x:c r="H101" s="199"/>
+      <x:c r="I101" s="199"/>
+      <x:c r="J101" s="199"/>
+      <x:c r="K101" s="199"/>
+      <x:c r="L101" s="199"/>
+      <x:c r="M101" s="199"/>
+      <x:c r="N101" s="204"/>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102" s="207"/>
+      <x:c r="B102" s="189"/>
+      <x:c r="C102" s="192"/>
+      <x:c r="D102" s="195"/>
+      <x:c r="E102" s="177"/>
+      <x:c r="F102" s="177"/>
+      <x:c r="G102" s="199"/>
+      <x:c r="H102" s="199"/>
+      <x:c r="I102" s="199"/>
+      <x:c r="J102" s="199"/>
+      <x:c r="K102" s="199"/>
+      <x:c r="L102" s="199"/>
+      <x:c r="M102" s="199"/>
+      <x:c r="N102" s="204"/>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103" s="207"/>
+      <x:c r="B103" s="189"/>
+      <x:c r="C103" s="192"/>
+      <x:c r="D103" s="195"/>
+      <x:c r="E103" s="177"/>
+      <x:c r="F103" s="177"/>
+      <x:c r="G103" s="199"/>
+      <x:c r="H103" s="199"/>
+      <x:c r="I103" s="199"/>
+      <x:c r="J103" s="199"/>
+      <x:c r="K103" s="199"/>
+      <x:c r="L103" s="199"/>
+      <x:c r="M103" s="199"/>
+      <x:c r="N103" s="204"/>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" s="207"/>
+      <x:c r="B104" s="189"/>
+      <x:c r="C104" s="192"/>
+      <x:c r="D104" s="195"/>
+      <x:c r="E104" s="177"/>
+      <x:c r="F104" s="177"/>
+      <x:c r="G104" s="199"/>
+      <x:c r="H104" s="199"/>
+      <x:c r="I104" s="199"/>
+      <x:c r="J104" s="199"/>
+      <x:c r="K104" s="199"/>
+      <x:c r="L104" s="199"/>
+      <x:c r="M104" s="199"/>
+      <x:c r="N104" s="204"/>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105" s="207"/>
+      <x:c r="B105" s="189"/>
+      <x:c r="C105" s="192"/>
+      <x:c r="D105" s="195"/>
+      <x:c r="E105" s="177"/>
+      <x:c r="F105" s="177"/>
+      <x:c r="G105" s="199"/>
+      <x:c r="H105" s="199"/>
+      <x:c r="I105" s="199"/>
+      <x:c r="J105" s="199"/>
+      <x:c r="K105" s="199"/>
+      <x:c r="L105" s="199"/>
+      <x:c r="M105" s="199"/>
+      <x:c r="N105" s="204"/>
+    </x:row>
+    <x:row r="106">
+      <x:c r="A106" s="207"/>
+      <x:c r="B106" s="189"/>
+      <x:c r="C106" s="192"/>
+      <x:c r="D106" s="195"/>
+      <x:c r="E106" s="177"/>
+      <x:c r="F106" s="177"/>
+      <x:c r="G106" s="199"/>
+      <x:c r="H106" s="199"/>
+      <x:c r="I106" s="199"/>
+      <x:c r="J106" s="199"/>
+      <x:c r="K106" s="199"/>
+      <x:c r="L106" s="199"/>
+      <x:c r="M106" s="199"/>
+      <x:c r="N106" s="204"/>
+    </x:row>
+    <x:row r="107">
+      <x:c r="A107" s="207"/>
+      <x:c r="B107" s="189"/>
+      <x:c r="C107" s="192"/>
+      <x:c r="D107" s="195"/>
+      <x:c r="E107" s="177"/>
+      <x:c r="F107" s="177"/>
+      <x:c r="G107" s="199"/>
+      <x:c r="H107" s="199"/>
+      <x:c r="I107" s="199"/>
+      <x:c r="J107" s="199"/>
+      <x:c r="K107" s="199"/>
+      <x:c r="L107" s="199"/>
+      <x:c r="M107" s="199"/>
+      <x:c r="N107" s="204"/>
+    </x:row>
+    <x:row r="108">
+      <x:c r="A108" s="207"/>
+      <x:c r="B108" s="189"/>
+      <x:c r="C108" s="192"/>
+      <x:c r="D108" s="195"/>
+      <x:c r="E108" s="177"/>
+      <x:c r="F108" s="177"/>
+      <x:c r="G108" s="199"/>
+      <x:c r="H108" s="199"/>
+      <x:c r="I108" s="199"/>
+      <x:c r="J108" s="199"/>
+      <x:c r="K108" s="199"/>
+      <x:c r="L108" s="199"/>
+      <x:c r="M108" s="199"/>
+      <x:c r="N108" s="204"/>
+    </x:row>
+    <x:row r="109">
+      <x:c r="A109" s="207"/>
+      <x:c r="B109" s="189"/>
+      <x:c r="C109" s="192"/>
+      <x:c r="D109" s="195"/>
+      <x:c r="E109" s="177"/>
+      <x:c r="F109" s="177"/>
+      <x:c r="G109" s="199"/>
+      <x:c r="H109" s="199"/>
+      <x:c r="I109" s="199"/>
+      <x:c r="J109" s="199"/>
+      <x:c r="K109" s="199"/>
+      <x:c r="L109" s="199"/>
+      <x:c r="M109" s="199"/>
+      <x:c r="N109" s="204"/>
+    </x:row>
+    <x:row r="110">
+      <x:c r="A110" s="207"/>
+      <x:c r="B110" s="189"/>
+      <x:c r="C110" s="192"/>
+      <x:c r="D110" s="195"/>
+      <x:c r="E110" s="177"/>
+      <x:c r="F110" s="177"/>
+      <x:c r="G110" s="199"/>
+      <x:c r="H110" s="199"/>
+      <x:c r="I110" s="199"/>
+      <x:c r="J110" s="199"/>
+      <x:c r="K110" s="199"/>
+      <x:c r="L110" s="199"/>
+      <x:c r="M110" s="199"/>
+      <x:c r="N110" s="204"/>
+    </x:row>
+    <x:row r="111">
+      <x:c r="A111" s="207"/>
+      <x:c r="B111" s="189"/>
+      <x:c r="C111" s="192"/>
+      <x:c r="D111" s="195"/>
+      <x:c r="E111" s="177"/>
+      <x:c r="F111" s="177"/>
+      <x:c r="G111" s="199"/>
+      <x:c r="H111" s="199"/>
+      <x:c r="I111" s="199"/>
+      <x:c r="J111" s="199"/>
+      <x:c r="K111" s="199"/>
+      <x:c r="L111" s="199"/>
+      <x:c r="M111" s="199"/>
+      <x:c r="N111" s="204"/>
+    </x:row>
+    <x:row r="112">
+      <x:c r="A112" s="207"/>
+      <x:c r="B112" s="189"/>
+      <x:c r="C112" s="192"/>
+      <x:c r="D112" s="195"/>
+      <x:c r="E112" s="177"/>
+      <x:c r="F112" s="177"/>
+      <x:c r="G112" s="199"/>
+      <x:c r="H112" s="199"/>
+      <x:c r="I112" s="199"/>
+      <x:c r="J112" s="199"/>
+      <x:c r="K112" s="199"/>
+      <x:c r="L112" s="199"/>
+      <x:c r="M112" s="199"/>
+      <x:c r="N112" s="204"/>
+    </x:row>
+    <x:row r="113">
+      <x:c r="A113" s="207"/>
+      <x:c r="B113" s="189"/>
+      <x:c r="C113" s="192"/>
+      <x:c r="D113" s="195"/>
+      <x:c r="E113" s="177"/>
+      <x:c r="F113" s="177"/>
+      <x:c r="G113" s="199"/>
+      <x:c r="H113" s="199"/>
+      <x:c r="I113" s="199"/>
+      <x:c r="J113" s="199"/>
+      <x:c r="K113" s="199"/>
+      <x:c r="L113" s="199"/>
+      <x:c r="M113" s="199"/>
+      <x:c r="N113" s="204"/>
+    </x:row>
+    <x:row r="114">
+      <x:c r="A114" s="207"/>
+      <x:c r="B114" s="189"/>
+      <x:c r="C114" s="192"/>
+      <x:c r="D114" s="195"/>
+      <x:c r="E114" s="177"/>
+      <x:c r="F114" s="177"/>
+      <x:c r="G114" s="199"/>
+      <x:c r="H114" s="199"/>
+      <x:c r="I114" s="199"/>
+      <x:c r="J114" s="199"/>
+      <x:c r="K114" s="199"/>
+      <x:c r="L114" s="199"/>
+      <x:c r="M114" s="199"/>
+      <x:c r="N114" s="204"/>
+    </x:row>
+    <x:row r="115">
+      <x:c r="A115" s="207"/>
+      <x:c r="B115" s="189"/>
+      <x:c r="C115" s="192"/>
+      <x:c r="D115" s="195"/>
+      <x:c r="E115" s="177"/>
+      <x:c r="F115" s="177"/>
+      <x:c r="G115" s="199"/>
+      <x:c r="H115" s="199"/>
+      <x:c r="I115" s="199"/>
+      <x:c r="J115" s="199"/>
+      <x:c r="K115" s="199"/>
+      <x:c r="L115" s="199"/>
+      <x:c r="M115" s="199"/>
+      <x:c r="N115" s="204"/>
+    </x:row>
+    <x:row r="116">
+      <x:c r="A116" s="207"/>
+      <x:c r="B116" s="189"/>
+      <x:c r="C116" s="192"/>
+      <x:c r="D116" s="195"/>
+      <x:c r="E116" s="177"/>
+      <x:c r="F116" s="177"/>
+      <x:c r="G116" s="199"/>
+      <x:c r="H116" s="199"/>
+      <x:c r="I116" s="199"/>
+      <x:c r="J116" s="199"/>
+      <x:c r="K116" s="199"/>
+      <x:c r="L116" s="199"/>
+      <x:c r="M116" s="199"/>
+      <x:c r="N116" s="204"/>
+    </x:row>
+    <x:row r="117">
+      <x:c r="A117" s="207"/>
+      <x:c r="B117" s="189"/>
+      <x:c r="C117" s="192"/>
+      <x:c r="D117" s="195"/>
+      <x:c r="E117" s="177"/>
+      <x:c r="F117" s="177"/>
+      <x:c r="G117" s="199"/>
+      <x:c r="H117" s="199"/>
+      <x:c r="I117" s="199"/>
+      <x:c r="J117" s="199"/>
+      <x:c r="K117" s="199"/>
+      <x:c r="L117" s="199"/>
+      <x:c r="M117" s="199"/>
+      <x:c r="N117" s="204"/>
+    </x:row>
+    <x:row r="118">
+      <x:c r="A118" s="207"/>
+      <x:c r="B118" s="189"/>
+      <x:c r="C118" s="192"/>
+      <x:c r="D118" s="195"/>
+      <x:c r="E118" s="177"/>
+      <x:c r="F118" s="177"/>
+      <x:c r="G118" s="199"/>
+      <x:c r="H118" s="199"/>
+      <x:c r="I118" s="199"/>
+      <x:c r="J118" s="199"/>
+      <x:c r="K118" s="199"/>
+      <x:c r="L118" s="199"/>
+      <x:c r="M118" s="199"/>
+      <x:c r="N118" s="204"/>
+    </x:row>
+    <x:row r="119">
+      <x:c r="A119" s="207"/>
+      <x:c r="B119" s="189"/>
+      <x:c r="C119" s="192"/>
+      <x:c r="D119" s="195"/>
+      <x:c r="E119" s="177"/>
+      <x:c r="F119" s="177"/>
+      <x:c r="G119" s="199"/>
+      <x:c r="H119" s="199"/>
+      <x:c r="I119" s="199"/>
+      <x:c r="J119" s="199"/>
+      <x:c r="K119" s="199"/>
+      <x:c r="L119" s="199"/>
+      <x:c r="M119" s="199"/>
+      <x:c r="N119" s="204"/>
+    </x:row>
+    <x:row r="120">
+      <x:c r="A120" s="207"/>
+      <x:c r="B120" s="189"/>
+      <x:c r="C120" s="192"/>
+      <x:c r="D120" s="195"/>
+      <x:c r="E120" s="177"/>
+      <x:c r="F120" s="177"/>
+      <x:c r="G120" s="199"/>
+      <x:c r="H120" s="199"/>
+      <x:c r="I120" s="199"/>
+      <x:c r="J120" s="199"/>
+      <x:c r="K120" s="199"/>
+      <x:c r="L120" s="199"/>
+      <x:c r="M120" s="199"/>
+      <x:c r="N120" s="204"/>
+    </x:row>
+    <x:row r="121">
+      <x:c r="A121" s="207"/>
+      <x:c r="B121" s="189"/>
+      <x:c r="C121" s="192"/>
+      <x:c r="D121" s="195"/>
+      <x:c r="E121" s="177"/>
+      <x:c r="F121" s="177"/>
+      <x:c r="G121" s="199"/>
+      <x:c r="H121" s="199"/>
+      <x:c r="I121" s="199"/>
+      <x:c r="J121" s="199"/>
+      <x:c r="K121" s="199"/>
+      <x:c r="L121" s="199"/>
+      <x:c r="M121" s="199"/>
+      <x:c r="N121" s="204"/>
+    </x:row>
+    <x:row r="122">
+      <x:c r="A122" s="207"/>
+      <x:c r="B122" s="189"/>
+      <x:c r="C122" s="192"/>
+      <x:c r="D122" s="195"/>
+      <x:c r="E122" s="177"/>
+      <x:c r="F122" s="177"/>
+      <x:c r="G122" s="199"/>
+      <x:c r="H122" s="199"/>
+      <x:c r="I122" s="199"/>
+      <x:c r="J122" s="199"/>
+      <x:c r="K122" s="199"/>
+      <x:c r="L122" s="199"/>
+      <x:c r="M122" s="199"/>
+      <x:c r="N122" s="204"/>
+    </x:row>
+    <x:row r="123">
+      <x:c r="A123" s="207"/>
+      <x:c r="B123" s="189"/>
+      <x:c r="C123" s="192"/>
+      <x:c r="D123" s="195"/>
+      <x:c r="E123" s="177"/>
+      <x:c r="F123" s="177"/>
+      <x:c r="G123" s="199"/>
+      <x:c r="H123" s="199"/>
+      <x:c r="I123" s="199"/>
+      <x:c r="J123" s="199"/>
+      <x:c r="K123" s="199"/>
+      <x:c r="L123" s="199"/>
+      <x:c r="M123" s="199"/>
+      <x:c r="N123" s="204"/>
+    </x:row>
+    <x:row r="124">
+      <x:c r="A124" s="207"/>
+      <x:c r="B124" s="189"/>
+      <x:c r="C124" s="192"/>
+      <x:c r="D124" s="195"/>
+      <x:c r="E124" s="177"/>
+      <x:c r="F124" s="177"/>
+      <x:c r="G124" s="199"/>
+      <x:c r="H124" s="199"/>
+      <x:c r="I124" s="199"/>
+      <x:c r="J124" s="199"/>
+      <x:c r="K124" s="199"/>
+      <x:c r="L124" s="199"/>
+      <x:c r="M124" s="199"/>
+      <x:c r="N124" s="204"/>
+    </x:row>
+    <x:row r="125">
+      <x:c r="A125" s="207"/>
+      <x:c r="B125" s="189"/>
+      <x:c r="C125" s="192"/>
+      <x:c r="D125" s="195"/>
+      <x:c r="E125" s="177"/>
+      <x:c r="F125" s="177"/>
+      <x:c r="G125" s="199"/>
+      <x:c r="H125" s="199"/>
+      <x:c r="I125" s="199"/>
+      <x:c r="J125" s="199"/>
+      <x:c r="K125" s="199"/>
+      <x:c r="L125" s="199"/>
+      <x:c r="M125" s="199"/>
+      <x:c r="N125" s="204"/>
+    </x:row>
+    <x:row r="126">
+      <x:c r="A126" s="207"/>
+      <x:c r="B126" s="189"/>
+      <x:c r="C126" s="192"/>
+      <x:c r="D126" s="195"/>
+      <x:c r="E126" s="177"/>
+      <x:c r="F126" s="177"/>
+      <x:c r="G126" s="199"/>
+      <x:c r="H126" s="199"/>
+      <x:c r="I126" s="199"/>
+      <x:c r="J126" s="199"/>
+      <x:c r="K126" s="199"/>
+      <x:c r="L126" s="199"/>
+      <x:c r="M126" s="199"/>
+      <x:c r="N126" s="204"/>
+    </x:row>
+    <x:row r="127">
+      <x:c r="A127" s="207"/>
+      <x:c r="B127" s="189"/>
+      <x:c r="C127" s="192"/>
+      <x:c r="D127" s="195"/>
+      <x:c r="E127" s="177"/>
+      <x:c r="F127" s="177"/>
+      <x:c r="G127" s="199"/>
+      <x:c r="H127" s="199"/>
+      <x:c r="I127" s="199"/>
+      <x:c r="J127" s="199"/>
+      <x:c r="K127" s="199"/>
+      <x:c r="L127" s="199"/>
+      <x:c r="M127" s="199"/>
+      <x:c r="N127" s="204"/>
+    </x:row>
+    <x:row r="128">
+      <x:c r="A128" s="207"/>
+      <x:c r="B128" s="189"/>
+      <x:c r="C128" s="192"/>
+      <x:c r="D128" s="195"/>
+      <x:c r="E128" s="177"/>
+      <x:c r="F128" s="177"/>
+      <x:c r="G128" s="199"/>
+      <x:c r="H128" s="199"/>
+      <x:c r="I128" s="199"/>
+      <x:c r="J128" s="199"/>
+      <x:c r="K128" s="199"/>
+      <x:c r="L128" s="199"/>
+      <x:c r="M128" s="199"/>
+      <x:c r="N128" s="204"/>
+    </x:row>
+    <x:row r="129">
+      <x:c r="A129" s="207"/>
+      <x:c r="B129" s="189"/>
+      <x:c r="C129" s="192"/>
+      <x:c r="D129" s="195"/>
+      <x:c r="E129" s="177"/>
+      <x:c r="F129" s="177"/>
+      <x:c r="G129" s="199"/>
+      <x:c r="H129" s="199"/>
+      <x:c r="I129" s="199"/>
+      <x:c r="J129" s="199"/>
+      <x:c r="K129" s="199"/>
+      <x:c r="L129" s="199"/>
+      <x:c r="M129" s="199"/>
+      <x:c r="N129" s="204"/>
+    </x:row>
+    <x:row r="130">
+      <x:c r="A130" s="207"/>
+      <x:c r="B130" s="189"/>
+      <x:c r="C130" s="192"/>
+      <x:c r="D130" s="195"/>
+      <x:c r="E130" s="177"/>
+      <x:c r="F130" s="177"/>
+      <x:c r="G130" s="199"/>
+      <x:c r="H130" s="199"/>
+      <x:c r="I130" s="199"/>
+      <x:c r="J130" s="199"/>
+      <x:c r="K130" s="199"/>
+      <x:c r="L130" s="199"/>
+      <x:c r="M130" s="199"/>
+      <x:c r="N130" s="204"/>
+    </x:row>
+    <x:row r="131">
+      <x:c r="A131" s="207"/>
+      <x:c r="B131" s="189"/>
+      <x:c r="C131" s="192"/>
+      <x:c r="D131" s="195"/>
+      <x:c r="E131" s="177"/>
+      <x:c r="F131" s="177"/>
+      <x:c r="G131" s="199"/>
+      <x:c r="H131" s="199"/>
+      <x:c r="I131" s="199"/>
+      <x:c r="J131" s="199"/>
+      <x:c r="K131" s="199"/>
+      <x:c r="L131" s="199"/>
+      <x:c r="M131" s="199"/>
+      <x:c r="N131" s="204"/>
+    </x:row>
+    <x:row r="132">
+      <x:c r="A132" s="207"/>
+      <x:c r="B132" s="189"/>
+      <x:c r="C132" s="192"/>
+      <x:c r="D132" s="195"/>
+      <x:c r="E132" s="177"/>
+      <x:c r="F132" s="177"/>
+      <x:c r="G132" s="199"/>
+      <x:c r="H132" s="199"/>
+      <x:c r="I132" s="199"/>
+      <x:c r="J132" s="199"/>
+      <x:c r="K132" s="199"/>
+      <x:c r="L132" s="199"/>
+      <x:c r="M132" s="199"/>
+      <x:c r="N132" s="204"/>
+    </x:row>
+    <x:row r="133">
+      <x:c r="A133" s="207"/>
+      <x:c r="B133" s="189"/>
+      <x:c r="C133" s="192"/>
+      <x:c r="D133" s="195"/>
+      <x:c r="E133" s="177"/>
+      <x:c r="F133" s="177"/>
+      <x:c r="G133" s="199"/>
+      <x:c r="H133" s="199"/>
+      <x:c r="I133" s="199"/>
+      <x:c r="J133" s="199"/>
+      <x:c r="K133" s="199"/>
+      <x:c r="L133" s="199"/>
+      <x:c r="M133" s="199"/>
+      <x:c r="N133" s="204"/>
+    </x:row>
+    <x:row r="134">
+      <x:c r="A134" s="207"/>
+      <x:c r="B134" s="189"/>
+      <x:c r="C134" s="192"/>
+      <x:c r="D134" s="195"/>
+      <x:c r="E134" s="177"/>
+      <x:c r="F134" s="177"/>
+      <x:c r="G134" s="199"/>
+      <x:c r="H134" s="199"/>
+      <x:c r="I134" s="199"/>
+      <x:c r="J134" s="199"/>
+      <x:c r="K134" s="199"/>
+      <x:c r="L134" s="199"/>
+      <x:c r="M134" s="199"/>
+      <x:c r="N134" s="204"/>
+    </x:row>
+    <x:row r="135">
+      <x:c r="A135" s="207"/>
+      <x:c r="B135" s="189"/>
+      <x:c r="C135" s="192"/>
+      <x:c r="D135" s="195"/>
+      <x:c r="E135" s="177"/>
+      <x:c r="F135" s="177"/>
+      <x:c r="G135" s="199"/>
+      <x:c r="H135" s="199"/>
+      <x:c r="I135" s="199"/>
+      <x:c r="J135" s="199"/>
+      <x:c r="K135" s="199"/>
+      <x:c r="L135" s="199"/>
+      <x:c r="M135" s="199"/>
+      <x:c r="N135" s="204"/>
+    </x:row>
+    <x:row r="136">
+      <x:c r="A136" s="207"/>
+      <x:c r="B136" s="189"/>
+      <x:c r="C136" s="192"/>
+      <x:c r="D136" s="195"/>
+      <x:c r="E136" s="177"/>
+      <x:c r="F136" s="177"/>
+      <x:c r="G136" s="199"/>
+      <x:c r="H136" s="199"/>
+      <x:c r="I136" s="199"/>
+      <x:c r="J136" s="199"/>
+      <x:c r="K136" s="199"/>
+      <x:c r="L136" s="199"/>
+      <x:c r="M136" s="199"/>
+      <x:c r="N136" s="204"/>
+    </x:row>
+    <x:row r="137">
+      <x:c r="A137" s="207"/>
+      <x:c r="B137" s="189"/>
+      <x:c r="C137" s="192"/>
+      <x:c r="D137" s="195"/>
+      <x:c r="E137" s="177"/>
+      <x:c r="F137" s="177"/>
+      <x:c r="G137" s="199"/>
+      <x:c r="H137" s="199"/>
+      <x:c r="I137" s="199"/>
+      <x:c r="J137" s="199"/>
+      <x:c r="K137" s="199"/>
+      <x:c r="L137" s="199"/>
+      <x:c r="M137" s="199"/>
+      <x:c r="N137" s="204"/>
+    </x:row>
+    <x:row r="138">
+      <x:c r="A138" s="207"/>
+      <x:c r="B138" s="189"/>
+      <x:c r="C138" s="192"/>
+      <x:c r="D138" s="195"/>
+      <x:c r="E138" s="177"/>
+      <x:c r="F138" s="177"/>
+      <x:c r="G138" s="199"/>
+      <x:c r="H138" s="199"/>
+      <x:c r="I138" s="199"/>
+      <x:c r="J138" s="199"/>
+      <x:c r="K138" s="199"/>
+      <x:c r="L138" s="199"/>
+      <x:c r="M138" s="199"/>
+      <x:c r="N138" s="204"/>
+    </x:row>
+    <x:row r="139">
+      <x:c r="A139" s="207"/>
+      <x:c r="B139" s="189"/>
+      <x:c r="C139" s="192"/>
+      <x:c r="D139" s="195"/>
+      <x:c r="E139" s="177"/>
+      <x:c r="F139" s="177"/>
+      <x:c r="G139" s="199"/>
+      <x:c r="H139" s="199"/>
+      <x:c r="I139" s="199"/>
+      <x:c r="J139" s="199"/>
+      <x:c r="K139" s="199"/>
+      <x:c r="L139" s="199"/>
+      <x:c r="M139" s="199"/>
+      <x:c r="N139" s="204"/>
+    </x:row>
+    <x:row r="140">
+      <x:c r="A140" s="207"/>
+      <x:c r="B140" s="189"/>
+      <x:c r="C140" s="192"/>
+      <x:c r="D140" s="195"/>
+      <x:c r="E140" s="177"/>
+      <x:c r="F140" s="177"/>
+      <x:c r="G140" s="199"/>
+      <x:c r="H140" s="199"/>
+      <x:c r="I140" s="199"/>
+      <x:c r="J140" s="199"/>
+      <x:c r="K140" s="199"/>
+      <x:c r="L140" s="199"/>
+      <x:c r="M140" s="199"/>
+      <x:c r="N140" s="204"/>
+    </x:row>
+    <x:row r="141">
+      <x:c r="A141" s="207"/>
+      <x:c r="B141" s="189"/>
+      <x:c r="C141" s="192"/>
+      <x:c r="D141" s="195"/>
+      <x:c r="E141" s="177"/>
+      <x:c r="F141" s="177"/>
+      <x:c r="G141" s="199"/>
+      <x:c r="H141" s="199"/>
+      <x:c r="I141" s="199"/>
+      <x:c r="J141" s="199"/>
+      <x:c r="K141" s="199"/>
+      <x:c r="L141" s="199"/>
+      <x:c r="M141" s="199"/>
+      <x:c r="N141" s="204"/>
+    </x:row>
+    <x:row r="142">
+      <x:c r="A142" s="207"/>
+      <x:c r="B142" s="189"/>
+      <x:c r="C142" s="192"/>
+      <x:c r="D142" s="195"/>
+      <x:c r="E142" s="177"/>
+      <x:c r="F142" s="177"/>
+      <x:c r="G142" s="199"/>
+      <x:c r="H142" s="199"/>
+      <x:c r="I142" s="199"/>
+      <x:c r="J142" s="199"/>
+      <x:c r="K142" s="199"/>
+      <x:c r="L142" s="199"/>
+      <x:c r="M142" s="199"/>
+      <x:c r="N142" s="204"/>
+    </x:row>
+    <x:row r="143">
+      <x:c r="A143" s="207"/>
+      <x:c r="B143" s="189"/>
+      <x:c r="C143" s="192"/>
+      <x:c r="D143" s="195"/>
+      <x:c r="E143" s="177"/>
+      <x:c r="F143" s="177"/>
+      <x:c r="G143" s="199"/>
+      <x:c r="H143" s="199"/>
+      <x:c r="I143" s="199"/>
+      <x:c r="J143" s="199"/>
+      <x:c r="K143" s="199"/>
+      <x:c r="L143" s="199"/>
+      <x:c r="M143" s="199"/>
+      <x:c r="N143" s="204"/>
+    </x:row>
+    <x:row r="144">
+      <x:c r="A144" s="207"/>
+      <x:c r="B144" s="189"/>
+      <x:c r="C144" s="192"/>
+      <x:c r="D144" s="195"/>
+      <x:c r="E144" s="177"/>
+      <x:c r="F144" s="177"/>
+      <x:c r="G144" s="199"/>
+      <x:c r="H144" s="199"/>
+      <x:c r="I144" s="199"/>
+      <x:c r="J144" s="199"/>
+      <x:c r="K144" s="199"/>
+      <x:c r="L144" s="199"/>
+      <x:c r="M144" s="199"/>
+      <x:c r="N144" s="204"/>
+    </x:row>
+    <x:row r="145">
+      <x:c r="A145" s="207"/>
+      <x:c r="B145" s="189"/>
+      <x:c r="C145" s="192"/>
+      <x:c r="D145" s="195"/>
+      <x:c r="E145" s="177"/>
+      <x:c r="F145" s="177"/>
+      <x:c r="G145" s="199"/>
+      <x:c r="H145" s="199"/>
+      <x:c r="I145" s="199"/>
+      <x:c r="J145" s="199"/>
+      <x:c r="K145" s="199"/>
+      <x:c r="L145" s="199"/>
+      <x:c r="M145" s="199"/>
+      <x:c r="N145" s="204"/>
+    </x:row>
+    <x:row r="146">
+      <x:c r="A146" s="207"/>
+      <x:c r="B146" s="189"/>
+      <x:c r="C146" s="192"/>
+      <x:c r="D146" s="195"/>
+      <x:c r="E146" s="177"/>
+      <x:c r="F146" s="177"/>
+      <x:c r="G146" s="199"/>
+      <x:c r="H146" s="199"/>
+      <x:c r="I146" s="199"/>
+      <x:c r="J146" s="199"/>
+      <x:c r="K146" s="199"/>
+      <x:c r="L146" s="199"/>
+      <x:c r="M146" s="199"/>
+      <x:c r="N146" s="204"/>
+    </x:row>
+    <x:row r="147">
+      <x:c r="A147" s="207"/>
+      <x:c r="B147" s="189"/>
+      <x:c r="C147" s="192"/>
+      <x:c r="D147" s="195"/>
+      <x:c r="E147" s="177"/>
+      <x:c r="F147" s="177"/>
+      <x:c r="G147" s="199"/>
+      <x:c r="H147" s="199"/>
+      <x:c r="I147" s="199"/>
+      <x:c r="J147" s="199"/>
+      <x:c r="K147" s="199"/>
+      <x:c r="L147" s="199"/>
+      <x:c r="M147" s="199"/>
+      <x:c r="N147" s="204"/>
+    </x:row>
+    <x:row r="148">
+      <x:c r="A148" s="207"/>
+      <x:c r="B148" s="189"/>
+      <x:c r="C148" s="192"/>
+      <x:c r="D148" s="195"/>
+      <x:c r="E148" s="177"/>
+      <x:c r="F148" s="177"/>
+      <x:c r="G148" s="199"/>
+      <x:c r="H148" s="199"/>
+      <x:c r="I148" s="199"/>
+      <x:c r="J148" s="199"/>
+      <x:c r="K148" s="199"/>
+      <x:c r="L148" s="199"/>
+      <x:c r="M148" s="199"/>
+      <x:c r="N148" s="204"/>
+    </x:row>
+    <x:row r="149">
+      <x:c r="A149" s="207"/>
+      <x:c r="B149" s="189"/>
+      <x:c r="C149" s="192"/>
+      <x:c r="D149" s="195"/>
+      <x:c r="E149" s="177"/>
+      <x:c r="F149" s="177"/>
+      <x:c r="G149" s="199"/>
+      <x:c r="H149" s="199"/>
+      <x:c r="I149" s="199"/>
+      <x:c r="J149" s="199"/>
+      <x:c r="K149" s="199"/>
+      <x:c r="L149" s="199"/>
+      <x:c r="M149" s="199"/>
+      <x:c r="N149" s="204"/>
+    </x:row>
+    <x:row r="150">
+      <x:c r="A150" s="207"/>
+      <x:c r="B150" s="189"/>
+      <x:c r="C150" s="192"/>
+      <x:c r="D150" s="195"/>
+      <x:c r="E150" s="177"/>
+      <x:c r="F150" s="177"/>
+      <x:c r="G150" s="199"/>
+      <x:c r="H150" s="199"/>
+      <x:c r="I150" s="199"/>
+      <x:c r="J150" s="199"/>
+      <x:c r="K150" s="199"/>
+      <x:c r="L150" s="199"/>
+      <x:c r="M150" s="199"/>
+      <x:c r="N150" s="204"/>
+    </x:row>
+    <x:row r="151">
+      <x:c r="A151" s="207"/>
+      <x:c r="B151" s="189"/>
+      <x:c r="C151" s="192"/>
+      <x:c r="D151" s="195"/>
+      <x:c r="E151" s="177"/>
+      <x:c r="F151" s="177"/>
+      <x:c r="G151" s="199"/>
+      <x:c r="H151" s="199"/>
+      <x:c r="I151" s="199"/>
+      <x:c r="J151" s="199"/>
+      <x:c r="K151" s="199"/>
+      <x:c r="L151" s="199"/>
+      <x:c r="M151" s="199"/>
+      <x:c r="N151" s="204"/>
+    </x:row>
+    <x:row r="152">
+      <x:c r="A152" s="207"/>
+      <x:c r="B152" s="189"/>
+      <x:c r="C152" s="192"/>
+      <x:c r="D152" s="195"/>
+      <x:c r="E152" s="177"/>
+      <x:c r="F152" s="177"/>
+      <x:c r="G152" s="199"/>
+      <x:c r="H152" s="199"/>
+      <x:c r="I152" s="199"/>
+      <x:c r="J152" s="199"/>
+      <x:c r="K152" s="199"/>
+      <x:c r="L152" s="199"/>
+      <x:c r="M152" s="199"/>
+      <x:c r="N152" s="204"/>
+    </x:row>
+    <x:row r="153">
+      <x:c r="A153" s="207"/>
+      <x:c r="B153" s="189"/>
+      <x:c r="C153" s="192"/>
+      <x:c r="D153" s="195"/>
+      <x:c r="E153" s="177"/>
+      <x:c r="F153" s="177"/>
+      <x:c r="G153" s="199"/>
+      <x:c r="H153" s="199"/>
+      <x:c r="I153" s="199"/>
+      <x:c r="J153" s="199"/>
+      <x:c r="K153" s="199"/>
+      <x:c r="L153" s="199"/>
+      <x:c r="M153" s="199"/>
+      <x:c r="N153" s="204"/>
+    </x:row>
+    <x:row r="154">
+      <x:c r="A154" s="207"/>
+      <x:c r="B154" s="189"/>
+      <x:c r="C154" s="192"/>
+      <x:c r="D154" s="195"/>
+      <x:c r="E154" s="177"/>
+      <x:c r="F154" s="177"/>
+      <x:c r="G154" s="199"/>
+      <x:c r="H154" s="199"/>
+      <x:c r="I154" s="199"/>
+      <x:c r="J154" s="199"/>
+      <x:c r="K154" s="199"/>
+      <x:c r="L154" s="199"/>
+      <x:c r="M154" s="199"/>
+      <x:c r="N154" s="204"/>
+    </x:row>
+    <x:row r="155">
+      <x:c r="A155" s="207"/>
+      <x:c r="B155" s="189"/>
+      <x:c r="C155" s="192"/>
+      <x:c r="D155" s="195"/>
+      <x:c r="E155" s="177"/>
+      <x:c r="F155" s="177"/>
+      <x:c r="G155" s="199"/>
+      <x:c r="H155" s="199"/>
+      <x:c r="I155" s="199"/>
+      <x:c r="J155" s="199"/>
+      <x:c r="K155" s="199"/>
+      <x:c r="L155" s="199"/>
+      <x:c r="M155" s="199"/>
+      <x:c r="N155" s="204"/>
+    </x:row>
+    <x:row r="156">
+      <x:c r="A156" s="207"/>
+      <x:c r="B156" s="189"/>
+      <x:c r="C156" s="192"/>
+      <x:c r="D156" s="195"/>
+      <x:c r="E156" s="177"/>
+      <x:c r="F156" s="177"/>
+      <x:c r="G156" s="199"/>
+      <x:c r="H156" s="199"/>
+      <x:c r="I156" s="199"/>
+      <x:c r="J156" s="199"/>
+      <x:c r="K156" s="199"/>
+      <x:c r="L156" s="199"/>
+      <x:c r="M156" s="199"/>
+      <x:c r="N156" s="204"/>
+    </x:row>
+    <x:row r="157">
+      <x:c r="A157" s="207"/>
+      <x:c r="B157" s="189"/>
+      <x:c r="C157" s="192"/>
+      <x:c r="D157" s="195"/>
+      <x:c r="E157" s="177"/>
+      <x:c r="F157" s="177"/>
+      <x:c r="G157" s="199"/>
+      <x:c r="H157" s="199"/>
+      <x:c r="I157" s="199"/>
+      <x:c r="J157" s="199"/>
+      <x:c r="K157" s="199"/>
+      <x:c r="L157" s="199"/>
+      <x:c r="M157" s="199"/>
+      <x:c r="N157" s="204"/>
+    </x:row>
+    <x:row r="158">
+      <x:c r="A158" s="207"/>
+      <x:c r="B158" s="189"/>
+      <x:c r="C158" s="192"/>
+      <x:c r="D158" s="195"/>
+      <x:c r="E158" s="177"/>
+      <x:c r="F158" s="177"/>
+      <x:c r="G158" s="199"/>
+      <x:c r="H158" s="199"/>
+      <x:c r="I158" s="199"/>
+      <x:c r="J158" s="199"/>
+      <x:c r="K158" s="199"/>
+      <x:c r="L158" s="199"/>
+      <x:c r="M158" s="199"/>
+      <x:c r="N158" s="204"/>
+    </x:row>
+    <x:row r="159">
+      <x:c r="A159" s="207"/>
+      <x:c r="B159" s="189"/>
+      <x:c r="C159" s="192"/>
+      <x:c r="D159" s="195"/>
+      <x:c r="E159" s="177"/>
+      <x:c r="F159" s="177"/>
+      <x:c r="G159" s="199"/>
+      <x:c r="H159" s="199"/>
+      <x:c r="I159" s="199"/>
+      <x:c r="J159" s="199"/>
+      <x:c r="K159" s="199"/>
+      <x:c r="L159" s="199"/>
+      <x:c r="M159" s="199"/>
+      <x:c r="N159" s="204"/>
+    </x:row>
+    <x:row r="160">
+      <x:c r="A160" s="207"/>
+      <x:c r="B160" s="189"/>
+      <x:c r="C160" s="192"/>
+      <x:c r="D160" s="195"/>
+      <x:c r="E160" s="177"/>
+      <x:c r="F160" s="177"/>
+      <x:c r="G160" s="199"/>
+      <x:c r="H160" s="199"/>
+      <x:c r="I160" s="199"/>
+      <x:c r="J160" s="199"/>
+      <x:c r="K160" s="199"/>
+      <x:c r="L160" s="199"/>
+      <x:c r="M160" s="199"/>
+      <x:c r="N160" s="204"/>
+    </x:row>
+    <x:row r="161">
+      <x:c r="A161" s="207"/>
+      <x:c r="B161" s="189"/>
+      <x:c r="C161" s="192"/>
+      <x:c r="D161" s="195"/>
+      <x:c r="E161" s="177"/>
+      <x:c r="F161" s="177"/>
+      <x:c r="G161" s="199"/>
+      <x:c r="H161" s="199"/>
+      <x:c r="I161" s="199"/>
+      <x:c r="J161" s="199"/>
+      <x:c r="K161" s="199"/>
+      <x:c r="L161" s="199"/>
+      <x:c r="M161" s="199"/>
+      <x:c r="N161" s="204"/>
+    </x:row>
+    <x:row r="162">
+      <x:c r="A162" s="207"/>
+      <x:c r="B162" s="189"/>
+      <x:c r="C162" s="192"/>
+      <x:c r="D162" s="195"/>
+      <x:c r="E162" s="177"/>
+      <x:c r="F162" s="177"/>
+      <x:c r="G162" s="199"/>
+      <x:c r="H162" s="199"/>
+      <x:c r="I162" s="199"/>
+      <x:c r="J162" s="199"/>
+      <x:c r="K162" s="199"/>
+      <x:c r="L162" s="199"/>
+      <x:c r="M162" s="199"/>
+      <x:c r="N162" s="204"/>
+    </x:row>
+    <x:row r="163">
+      <x:c r="A163" s="207"/>
+      <x:c r="B163" s="189"/>
+      <x:c r="C163" s="192"/>
+      <x:c r="D163" s="195"/>
+      <x:c r="E163" s="177"/>
+      <x:c r="F163" s="177"/>
+      <x:c r="G163" s="199"/>
+      <x:c r="H163" s="199"/>
+      <x:c r="I163" s="199"/>
+      <x:c r="J163" s="199"/>
+      <x:c r="K163" s="199"/>
+      <x:c r="L163" s="199"/>
+      <x:c r="M163" s="199"/>
+      <x:c r="N163" s="204"/>
+    </x:row>
+    <x:row r="164">
+      <x:c r="A164" s="207"/>
+      <x:c r="B164" s="189"/>
+      <x:c r="C164" s="192"/>
+      <x:c r="D164" s="195"/>
+      <x:c r="E164" s="177"/>
+      <x:c r="F164" s="177"/>
+      <x:c r="G164" s="199"/>
+      <x:c r="H164" s="199"/>
+      <x:c r="I164" s="199"/>
+      <x:c r="J164" s="199"/>
+      <x:c r="K164" s="199"/>
+      <x:c r="L164" s="199"/>
+      <x:c r="M164" s="199"/>
+      <x:c r="N164" s="204"/>
+    </x:row>
+    <x:row r="165">
+      <x:c r="A165" s="207"/>
+      <x:c r="B165" s="189"/>
+      <x:c r="C165" s="192"/>
+      <x:c r="D165" s="195"/>
+      <x:c r="E165" s="177"/>
+      <x:c r="F165" s="177"/>
+      <x:c r="G165" s="199"/>
+      <x:c r="H165" s="199"/>
+      <x:c r="I165" s="199"/>
+      <x:c r="J165" s="199"/>
+      <x:c r="K165" s="199"/>
+      <x:c r="L165" s="199"/>
+      <x:c r="M165" s="199"/>
+      <x:c r="N165" s="204"/>
+    </x:row>
+    <x:row r="166">
+      <x:c r="A166" s="207"/>
+      <x:c r="B166" s="189"/>
+      <x:c r="C166" s="192"/>
+      <x:c r="D166" s="195"/>
+      <x:c r="E166" s="177"/>
+      <x:c r="F166" s="177"/>
+      <x:c r="G166" s="199"/>
+      <x:c r="H166" s="199"/>
+      <x:c r="I166" s="199"/>
+      <x:c r="J166" s="199"/>
+      <x:c r="K166" s="199"/>
+      <x:c r="L166" s="199"/>
+      <x:c r="M166" s="199"/>
+      <x:c r="N166" s="204"/>
+    </x:row>
+    <x:row r="167">
+      <x:c r="A167" s="207"/>
+      <x:c r="B167" s="189"/>
+      <x:c r="C167" s="192"/>
+      <x:c r="D167" s="195"/>
+      <x:c r="E167" s="177"/>
+      <x:c r="F167" s="177"/>
+      <x:c r="G167" s="199"/>
+      <x:c r="H167" s="199"/>
+      <x:c r="I167" s="199"/>
+      <x:c r="J167" s="199"/>
+      <x:c r="K167" s="199"/>
+      <x:c r="L167" s="199"/>
+      <x:c r="M167" s="199"/>
+      <x:c r="N167" s="204"/>
+    </x:row>
+    <x:row r="168">
+      <x:c r="A168" s="207"/>
+      <x:c r="B168" s="189"/>
+      <x:c r="C168" s="192"/>
+      <x:c r="D168" s="195"/>
+      <x:c r="E168" s="177"/>
+      <x:c r="F168" s="177"/>
+      <x:c r="G168" s="199"/>
+      <x:c r="H168" s="199"/>
+      <x:c r="I168" s="199"/>
+      <x:c r="J168" s="199"/>
+      <x:c r="K168" s="199"/>
+      <x:c r="L168" s="199"/>
+      <x:c r="M168" s="199"/>
+      <x:c r="N168" s="204"/>
+    </x:row>
+    <x:row r="169">
+      <x:c r="A169" s="207"/>
+      <x:c r="B169" s="189"/>
+      <x:c r="C169" s="192"/>
+      <x:c r="D169" s="195"/>
+      <x:c r="E169" s="177"/>
+      <x:c r="F169" s="177"/>
+      <x:c r="G169" s="199"/>
+      <x:c r="H169" s="199"/>
+      <x:c r="I169" s="199"/>
+      <x:c r="J169" s="199"/>
+      <x:c r="K169" s="199"/>
+      <x:c r="L169" s="199"/>
+      <x:c r="M169" s="199"/>
+      <x:c r="N169" s="204"/>
+    </x:row>
+    <x:row r="170">
+      <x:c r="A170" s="207"/>
+      <x:c r="B170" s="189"/>
+      <x:c r="C170" s="192"/>
+      <x:c r="D170" s="195"/>
+      <x:c r="E170" s="177"/>
+      <x:c r="F170" s="177"/>
+      <x:c r="G170" s="199"/>
+      <x:c r="H170" s="199"/>
+      <x:c r="I170" s="199"/>
+      <x:c r="J170" s="199"/>
+      <x:c r="K170" s="199"/>
+      <x:c r="L170" s="199"/>
+      <x:c r="M170" s="199"/>
+      <x:c r="N170" s="204"/>
+    </x:row>
+    <x:row r="171">
+      <x:c r="A171" s="207"/>
+      <x:c r="B171" s="189"/>
+      <x:c r="C171" s="192"/>
+      <x:c r="D171" s="195"/>
+      <x:c r="E171" s="177"/>
+      <x:c r="F171" s="177"/>
+      <x:c r="G171" s="199"/>
+      <x:c r="H171" s="199"/>
+      <x:c r="I171" s="199"/>
+      <x:c r="J171" s="199"/>
+      <x:c r="K171" s="199"/>
+      <x:c r="L171" s="199"/>
+      <x:c r="M171" s="199"/>
+      <x:c r="N171" s="204"/>
+    </x:row>
+    <x:row r="172">
+      <x:c r="A172" s="207"/>
+      <x:c r="B172" s="189"/>
+      <x:c r="C172" s="192"/>
+      <x:c r="D172" s="195"/>
+      <x:c r="E172" s="177"/>
+      <x:c r="F172" s="177"/>
+      <x:c r="G172" s="199"/>
+      <x:c r="H172" s="199"/>
+      <x:c r="I172" s="199"/>
+      <x:c r="J172" s="199"/>
+      <x:c r="K172" s="199"/>
+      <x:c r="L172" s="199"/>
+      <x:c r="M172" s="199"/>
+      <x:c r="N172" s="204"/>
+    </x:row>
+    <x:row r="173">
+      <x:c r="A173" s="207"/>
+      <x:c r="B173" s="189"/>
+      <x:c r="C173" s="192"/>
+      <x:c r="D173" s="195"/>
+      <x:c r="E173" s="177"/>
+      <x:c r="F173" s="177"/>
+      <x:c r="G173" s="199"/>
+      <x:c r="H173" s="199"/>
+      <x:c r="I173" s="199"/>
+      <x:c r="J173" s="199"/>
+      <x:c r="K173" s="199"/>
+      <x:c r="L173" s="199"/>
+      <x:c r="M173" s="199"/>
+      <x:c r="N173" s="204"/>
+    </x:row>
+    <x:row r="174">
+      <x:c r="A174" s="207"/>
+      <x:c r="B174" s="189"/>
+      <x:c r="C174" s="192"/>
+      <x:c r="D174" s="195"/>
+      <x:c r="E174" s="177"/>
+      <x:c r="F174" s="177"/>
+      <x:c r="G174" s="199"/>
+      <x:c r="H174" s="199"/>
+      <x:c r="I174" s="199"/>
+      <x:c r="J174" s="199"/>
+      <x:c r="K174" s="199"/>
+      <x:c r="L174" s="199"/>
+      <x:c r="M174" s="199"/>
+      <x:c r="N174" s="204"/>
+    </x:row>
+    <x:row r="175">
+      <x:c r="A175" s="207"/>
+      <x:c r="B175" s="189"/>
+      <x:c r="C175" s="192"/>
+      <x:c r="D175" s="195"/>
+      <x:c r="E175" s="177"/>
+      <x:c r="F175" s="177"/>
+      <x:c r="G175" s="199"/>
+      <x:c r="H175" s="199"/>
+      <x:c r="I175" s="199"/>
+      <x:c r="J175" s="199"/>
+      <x:c r="K175" s="199"/>
+      <x:c r="L175" s="199"/>
+      <x:c r="M175" s="199"/>
+      <x:c r="N175" s="204"/>
+    </x:row>
+    <x:row r="176">
+      <x:c r="A176" s="207"/>
+      <x:c r="B176" s="189"/>
+      <x:c r="C176" s="192"/>
+      <x:c r="D176" s="195"/>
+      <x:c r="E176" s="177"/>
+      <x:c r="F176" s="177"/>
+      <x:c r="G176" s="199"/>
+      <x:c r="H176" s="199"/>
+      <x:c r="I176" s="199"/>
+      <x:c r="J176" s="199"/>
+      <x:c r="K176" s="199"/>
+      <x:c r="L176" s="199"/>
+      <x:c r="M176" s="199"/>
+      <x:c r="N176" s="204"/>
+    </x:row>
+    <x:row r="177">
+      <x:c r="A177" s="207"/>
+      <x:c r="B177" s="189"/>
+      <x:c r="C177" s="192"/>
+      <x:c r="D177" s="195"/>
+      <x:c r="E177" s="177"/>
+      <x:c r="F177" s="177"/>
+      <x:c r="G177" s="199"/>
+      <x:c r="H177" s="199"/>
+      <x:c r="I177" s="199"/>
+      <x:c r="J177" s="199"/>
+      <x:c r="K177" s="199"/>
+      <x:c r="L177" s="199"/>
+      <x:c r="M177" s="199"/>
+      <x:c r="N177" s="204"/>
+    </x:row>
+    <x:row r="178">
+      <x:c r="A178" s="207"/>
+      <x:c r="B178" s="189"/>
+      <x:c r="C178" s="192"/>
+      <x:c r="D178" s="195"/>
+      <x:c r="E178" s="177"/>
+      <x:c r="F178" s="177"/>
+      <x:c r="G178" s="199"/>
+      <x:c r="H178" s="199"/>
+      <x:c r="I178" s="199"/>
+      <x:c r="J178" s="199"/>
+      <x:c r="K178" s="199"/>
+      <x:c r="L178" s="199"/>
+      <x:c r="M178" s="199"/>
+      <x:c r="N178" s="204"/>
+    </x:row>
+    <x:row r="179">
+      <x:c r="A179" s="207"/>
+      <x:c r="B179" s="189"/>
+      <x:c r="C179" s="192"/>
+      <x:c r="D179" s="195"/>
+      <x:c r="E179" s="177"/>
+      <x:c r="F179" s="177"/>
+      <x:c r="G179" s="199"/>
+      <x:c r="H179" s="199"/>
+      <x:c r="I179" s="199"/>
+      <x:c r="J179" s="199"/>
+      <x:c r="K179" s="199"/>
+      <x:c r="L179" s="199"/>
+      <x:c r="M179" s="199"/>
+      <x:c r="N179" s="204"/>
+    </x:row>
+    <x:row r="180">
+      <x:c r="A180" s="207"/>
+      <x:c r="B180" s="189"/>
+      <x:c r="C180" s="192"/>
+      <x:c r="D180" s="195"/>
+      <x:c r="E180" s="177"/>
+      <x:c r="F180" s="177"/>
+      <x:c r="G180" s="199"/>
+      <x:c r="H180" s="199"/>
+      <x:c r="I180" s="199"/>
+      <x:c r="J180" s="199"/>
+      <x:c r="K180" s="199"/>
+      <x:c r="L180" s="199"/>
+      <x:c r="M180" s="199"/>
+      <x:c r="N180" s="204"/>
+    </x:row>
+    <x:row r="181">
+      <x:c r="A181" s="207"/>
+      <x:c r="B181" s="189"/>
+      <x:c r="C181" s="192"/>
+      <x:c r="D181" s="195"/>
+      <x:c r="E181" s="177"/>
+      <x:c r="F181" s="177"/>
+      <x:c r="G181" s="199"/>
+      <x:c r="H181" s="199"/>
+      <x:c r="I181" s="199"/>
+      <x:c r="J181" s="199"/>
+      <x:c r="K181" s="199"/>
+      <x:c r="L181" s="199"/>
+      <x:c r="M181" s="199"/>
+      <x:c r="N181" s="204"/>
+    </x:row>
+    <x:row r="182">
+      <x:c r="A182" s="207"/>
+      <x:c r="B182" s="189"/>
+      <x:c r="C182" s="192"/>
+      <x:c r="D182" s="195"/>
+      <x:c r="E182" s="177"/>
+      <x:c r="F182" s="177"/>
+      <x:c r="G182" s="199"/>
+      <x:c r="H182" s="199"/>
+      <x:c r="I182" s="199"/>
+      <x:c r="J182" s="199"/>
+      <x:c r="K182" s="199"/>
+      <x:c r="L182" s="199"/>
+      <x:c r="M182" s="199"/>
+      <x:c r="N182" s="204"/>
+    </x:row>
+    <x:row r="183">
+      <x:c r="A183" s="207"/>
+      <x:c r="B183" s="189"/>
+      <x:c r="C183" s="192"/>
+      <x:c r="D183" s="195"/>
+      <x:c r="E183" s="177"/>
+      <x:c r="F183" s="177"/>
+      <x:c r="G183" s="199"/>
+      <x:c r="H183" s="199"/>
+      <x:c r="I183" s="199"/>
+      <x:c r="J183" s="199"/>
+      <x:c r="K183" s="199"/>
+      <x:c r="L183" s="199"/>
+      <x:c r="M183" s="199"/>
+      <x:c r="N183" s="204"/>
+    </x:row>
+    <x:row r="184">
+      <x:c r="A184" s="207"/>
+      <x:c r="B184" s="189"/>
+      <x:c r="C184" s="192"/>
+      <x:c r="D184" s="195"/>
+      <x:c r="E184" s="177"/>
+      <x:c r="F184" s="177"/>
+      <x:c r="G184" s="199"/>
+      <x:c r="H184" s="199"/>
+      <x:c r="I184" s="199"/>
+      <x:c r="J184" s="199"/>
+      <x:c r="K184" s="199"/>
+      <x:c r="L184" s="199"/>
+      <x:c r="M184" s="199"/>
+      <x:c r="N184" s="204"/>
+    </x:row>
+    <x:row r="185">
+      <x:c r="A185" s="207"/>
+      <x:c r="B185" s="189"/>
+      <x:c r="C185" s="192"/>
+      <x:c r="D185" s="195"/>
+      <x:c r="E185" s="177"/>
+      <x:c r="F185" s="177"/>
+      <x:c r="G185" s="199"/>
+      <x:c r="H185" s="199"/>
+      <x:c r="I185" s="199"/>
+      <x:c r="J185" s="199"/>
+      <x:c r="K185" s="199"/>
+      <x:c r="L185" s="199"/>
+      <x:c r="M185" s="199"/>
+      <x:c r="N185" s="204"/>
+    </x:row>
+    <x:row r="186">
+      <x:c r="A186" s="207"/>
+      <x:c r="B186" s="189"/>
+      <x:c r="C186" s="192"/>
+      <x:c r="D186" s="195"/>
+      <x:c r="E186" s="177"/>
+      <x:c r="F186" s="177"/>
+      <x:c r="G186" s="199"/>
+      <x:c r="H186" s="199"/>
+      <x:c r="I186" s="199"/>
+      <x:c r="J186" s="199"/>
+      <x:c r="K186" s="199"/>
+      <x:c r="L186" s="199"/>
+      <x:c r="M186" s="199"/>
+      <x:c r="N186" s="204"/>
+    </x:row>
+    <x:row r="187">
+      <x:c r="A187" s="207"/>
+      <x:c r="B187" s="189"/>
+      <x:c r="C187" s="192"/>
+      <x:c r="D187" s="195"/>
+      <x:c r="E187" s="177"/>
+      <x:c r="F187" s="177"/>
+      <x:c r="G187" s="199"/>
+      <x:c r="H187" s="199"/>
+      <x:c r="I187" s="199"/>
+      <x:c r="J187" s="199"/>
+      <x:c r="K187" s="199"/>
+      <x:c r="L187" s="199"/>
+      <x:c r="M187" s="199"/>
+      <x:c r="N187" s="204"/>
+    </x:row>
+    <x:row r="188">
+      <x:c r="A188" s="207"/>
+      <x:c r="B188" s="189"/>
+      <x:c r="C188" s="192"/>
+      <x:c r="D188" s="195"/>
+      <x:c r="E188" s="177"/>
+      <x:c r="F188" s="177"/>
+      <x:c r="G188" s="199"/>
+      <x:c r="H188" s="199"/>
+      <x:c r="I188" s="199"/>
+      <x:c r="J188" s="199"/>
+      <x:c r="K188" s="199"/>
+      <x:c r="L188" s="199"/>
+      <x:c r="M188" s="199"/>
+      <x:c r="N188" s="204"/>
+    </x:row>
+    <x:row r="189">
+      <x:c r="A189" s="207"/>
+      <x:c r="B189" s="189"/>
+      <x:c r="C189" s="192"/>
+      <x:c r="D189" s="195"/>
+      <x:c r="E189" s="177"/>
+      <x:c r="F189" s="177"/>
+      <x:c r="G189" s="199"/>
+      <x:c r="H189" s="199"/>
+      <x:c r="I189" s="199"/>
+      <x:c r="J189" s="199"/>
+      <x:c r="K189" s="199"/>
+      <x:c r="L189" s="199"/>
+      <x:c r="M189" s="199"/>
+      <x:c r="N189" s="204"/>
+    </x:row>
+    <x:row r="190">
+      <x:c r="A190" s="207"/>
+      <x:c r="B190" s="189"/>
+      <x:c r="C190" s="192"/>
+      <x:c r="D190" s="195"/>
+      <x:c r="E190" s="177"/>
+      <x:c r="F190" s="177"/>
+      <x:c r="G190" s="199"/>
+      <x:c r="H190" s="199"/>
+      <x:c r="I190" s="199"/>
+      <x:c r="J190" s="199"/>
+      <x:c r="K190" s="199"/>
+      <x:c r="L190" s="199"/>
+      <x:c r="M190" s="199"/>
+      <x:c r="N190" s="204"/>
+    </x:row>
+    <x:row r="191">
+      <x:c r="A191" s="207"/>
+      <x:c r="B191" s="189"/>
+      <x:c r="C191" s="192"/>
+      <x:c r="D191" s="195"/>
+      <x:c r="E191" s="177"/>
+      <x:c r="F191" s="177"/>
+      <x:c r="G191" s="199"/>
+      <x:c r="H191" s="199"/>
+      <x:c r="I191" s="199"/>
+      <x:c r="J191" s="199"/>
+      <x:c r="K191" s="199"/>
+      <x:c r="L191" s="199"/>
+      <x:c r="M191" s="199"/>
+      <x:c r="N191" s="204"/>
+    </x:row>
+    <x:row r="192">
+      <x:c r="A192" s="207"/>
+      <x:c r="B192" s="189"/>
+      <x:c r="C192" s="192"/>
+      <x:c r="D192" s="195"/>
+      <x:c r="E192" s="177"/>
+      <x:c r="F192" s="177"/>
+      <x:c r="G192" s="199"/>
+      <x:c r="H192" s="199"/>
+      <x:c r="I192" s="199"/>
+      <x:c r="J192" s="199"/>
+      <x:c r="K192" s="199"/>
+      <x:c r="L192" s="199"/>
+      <x:c r="M192" s="199"/>
+      <x:c r="N192" s="204"/>
+    </x:row>
+    <x:row r="193">
+      <x:c r="A193" s="207"/>
+      <x:c r="B193" s="189"/>
+      <x:c r="C193" s="192"/>
+      <x:c r="D193" s="195"/>
+      <x:c r="E193" s="177"/>
+      <x:c r="F193" s="177"/>
+      <x:c r="G193" s="199"/>
+      <x:c r="H193" s="199"/>
+      <x:c r="I193" s="199"/>
+      <x:c r="J193" s="199"/>
+      <x:c r="K193" s="199"/>
+      <x:c r="L193" s="199"/>
+      <x:c r="M193" s="199"/>
+      <x:c r="N193" s="204"/>
+    </x:row>
+    <x:row r="194">
+      <x:c r="A194" s="207"/>
+      <x:c r="B194" s="189"/>
+      <x:c r="C194" s="192"/>
+      <x:c r="D194" s="195"/>
+      <x:c r="E194" s="177"/>
+      <x:c r="F194" s="177"/>
+      <x:c r="G194" s="199"/>
+      <x:c r="H194" s="199"/>
+      <x:c r="I194" s="199"/>
+      <x:c r="J194" s="199"/>
+      <x:c r="K194" s="199"/>
+      <x:c r="L194" s="199"/>
+      <x:c r="M194" s="199"/>
+      <x:c r="N194" s="204"/>
+    </x:row>
+    <x:row r="195">
+      <x:c r="A195" s="207"/>
+      <x:c r="B195" s="189"/>
+      <x:c r="C195" s="192"/>
+      <x:c r="D195" s="195"/>
+      <x:c r="E195" s="177"/>
+      <x:c r="F195" s="177"/>
+      <x:c r="G195" s="199"/>
+      <x:c r="H195" s="199"/>
+      <x:c r="I195" s="199"/>
+      <x:c r="J195" s="199"/>
+      <x:c r="K195" s="199"/>
+      <x:c r="L195" s="199"/>
+      <x:c r="M195" s="199"/>
+      <x:c r="N195" s="204"/>
+    </x:row>
+    <x:row r="196">
+      <x:c r="A196" s="207"/>
+      <x:c r="B196" s="189"/>
+      <x:c r="C196" s="192"/>
+      <x:c r="D196" s="195"/>
+      <x:c r="E196" s="177"/>
+      <x:c r="F196" s="177"/>
+      <x:c r="G196" s="199"/>
+      <x:c r="H196" s="199"/>
+      <x:c r="I196" s="199"/>
+      <x:c r="J196" s="199"/>
+      <x:c r="K196" s="199"/>
+      <x:c r="L196" s="199"/>
+      <x:c r="M196" s="199"/>
+      <x:c r="N196" s="204"/>
+    </x:row>
+    <x:row r="197">
+      <x:c r="A197" s="207"/>
+      <x:c r="B197" s="189"/>
+      <x:c r="C197" s="192"/>
+      <x:c r="D197" s="195"/>
+      <x:c r="E197" s="177"/>
+      <x:c r="F197" s="177"/>
+      <x:c r="G197" s="199"/>
+      <x:c r="H197" s="199"/>
+      <x:c r="I197" s="199"/>
+      <x:c r="J197" s="199"/>
+      <x:c r="K197" s="199"/>
+      <x:c r="L197" s="199"/>
+      <x:c r="M197" s="199"/>
+      <x:c r="N197" s="204"/>
+    </x:row>
+    <x:row r="198">
+      <x:c r="A198" s="207"/>
+      <x:c r="B198" s="189"/>
+      <x:c r="C198" s="192"/>
+      <x:c r="D198" s="195"/>
+      <x:c r="E198" s="177"/>
+      <x:c r="F198" s="177"/>
+      <x:c r="G198" s="199"/>
+      <x:c r="H198" s="199"/>
+      <x:c r="I198" s="199"/>
+      <x:c r="J198" s="199"/>
+      <x:c r="K198" s="199"/>
+      <x:c r="L198" s="199"/>
+      <x:c r="M198" s="199"/>
+      <x:c r="N198" s="204"/>
+    </x:row>
+    <x:row r="199">
+      <x:c r="A199" s="207"/>
+      <x:c r="B199" s="189"/>
+      <x:c r="C199" s="192"/>
+      <x:c r="D199" s="195"/>
+      <x:c r="E199" s="177"/>
+      <x:c r="F199" s="177"/>
+      <x:c r="G199" s="199"/>
+      <x:c r="H199" s="199"/>
+      <x:c r="I199" s="199"/>
+      <x:c r="J199" s="199"/>
+      <x:c r="K199" s="199"/>
+      <x:c r="L199" s="199"/>
+      <x:c r="M199" s="199"/>
+      <x:c r="N199" s="204"/>
+    </x:row>
+    <x:row r="200">
+      <x:c r="A200" s="207"/>
+      <x:c r="B200" s="189"/>
+      <x:c r="C200" s="192"/>
+      <x:c r="D200" s="195"/>
+      <x:c r="E200" s="177"/>
+      <x:c r="F200" s="177"/>
+      <x:c r="G200" s="199"/>
+      <x:c r="H200" s="199"/>
+      <x:c r="I200" s="199"/>
+      <x:c r="J200" s="199"/>
+      <x:c r="K200" s="199"/>
+      <x:c r="L200" s="199"/>
+      <x:c r="M200" s="199"/>
+      <x:c r="N200" s="204"/>
+    </x:row>
+    <x:row r="201">
+      <x:c r="A201" s="208"/>
+      <x:c r="B201" s="190"/>
+      <x:c r="C201" s="193"/>
+      <x:c r="D201" s="196"/>
+      <x:c r="E201" s="180"/>
+      <x:c r="F201" s="180"/>
+      <x:c r="G201" s="201"/>
+      <x:c r="H201" s="201"/>
+      <x:c r="I201" s="201"/>
+      <x:c r="J201" s="201"/>
+      <x:c r="K201" s="201"/>
+      <x:c r="L201" s="201"/>
+      <x:c r="M201" s="201"/>
+      <x:c r="N201" s="205"/>
+    </x:row>
+  </x:sheetData>
+  <x:conditionalFormatting sqref="A2:A201">
+    <x:cfRule type="containsText" dxfId="93" priority="1" operator="containsText" text="ROT"/>
+    <x:cfRule type="containsText" dxfId="94" priority="2" operator="containsText" text="GELB"/>
+    <x:cfRule type="containsText" dxfId="95" priority="3" operator="containsText" text="GRUEN"/>
+    <x:cfRule type="containsText" dxfId="96" priority="4" operator="containsText" text="NICHT_PRUEFBAR"/>
+  </x:conditionalFormatting>
+  <x:dataValidations count="3">
+    <x:dataValidation type="list" sqref="A2:A201">
+      <x:formula1>"GRUEN,GELB,ROT,NICHT_PRUEFBAR"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="G2:G201">
+      <x:formula1>"Zahlungseingang von,Zahlungsausgang an"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="M2:M201">
+      <x:formula1>"Offen,In Bearbeitung,Erledigt"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>